--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A976CE-D413-49B9-BD0D-076B1F44B7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C06359-78AF-4661-B397-B49FA40B98BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="SALES BY SKU" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>SALES BY SKU</t>
   </si>
@@ -43,27 +43,15 @@
     <t>DASHBOARD</t>
   </si>
   <si>
-    <t>TOTAL UNITS SALES GROSS</t>
-  </si>
-  <si>
-    <t>TOTAL UNITS SALES NET</t>
-  </si>
-  <si>
     <t>PROMD VTA DIA</t>
   </si>
   <si>
-    <t>PRONOST VTA MES</t>
-  </si>
-  <si>
     <t>FORECAST</t>
   </si>
   <si>
     <t>FORECAST EFFICIENCY</t>
   </si>
   <si>
-    <t>DIF UNITS</t>
-  </si>
-  <si>
     <t>REFERENCIA INTERNA</t>
   </si>
   <si>
@@ -79,24 +67,12 @@
     <t>Cremosillo Tradicional 150g</t>
   </si>
   <si>
-    <t>UNITS RETURN</t>
-  </si>
-  <si>
     <t>INICIO DE VENTA</t>
   </si>
   <si>
-    <t>TRANSC. VENTA</t>
-  </si>
-  <si>
     <t>FINAL DE VENTA</t>
   </si>
   <si>
-    <t>DIAS VENTA EFECT.</t>
-  </si>
-  <si>
-    <t>DIAS VENTA RESTA.</t>
-  </si>
-  <si>
     <t>Cremosillo Coco 150g</t>
   </si>
   <si>
@@ -224,6 +200,33 @@
   </si>
   <si>
     <t>Cremigurt Griego Natural 4 Kg</t>
+  </si>
+  <si>
+    <t>TOTAL UNIDADES VENTA BRUTA</t>
+  </si>
+  <si>
+    <t>TOTAL UNIDADES VENTA NETA</t>
+  </si>
+  <si>
+    <t>PROMEDIO VENTA DIARIA</t>
+  </si>
+  <si>
+    <t>PRONOSTICO VENTA MENSUAL</t>
+  </si>
+  <si>
+    <t>DIFERENCIA ALCANCE FORCAST</t>
+  </si>
+  <si>
+    <t>UNIDADES DEVOLUCION</t>
+  </si>
+  <si>
+    <t>DIAS VENTAS EFECTIVOS</t>
+  </si>
+  <si>
+    <t>DIAS VENTA RESTANTES</t>
+  </si>
+  <si>
+    <t>TRANSCURSO DE VENTA</t>
   </si>
 </sst>
 </file>
@@ -778,19 +781,19 @@
     </row>
     <row r="3" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -798,7 +801,7 @@
         <v>110150</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4" s="10">
         <v>8524</v>
@@ -815,7 +818,7 @@
         <v>110151</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C5" s="10">
         <v>614</v>
@@ -832,7 +835,7 @@
         <v>110230</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C6" s="10">
         <v>3756</v>
@@ -849,7 +852,7 @@
         <v>110400</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C7" s="10">
         <v>730</v>
@@ -866,7 +869,7 @@
         <v>111000</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C8" s="10">
         <v>126</v>
@@ -883,7 +886,7 @@
         <v>120130</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9" s="10">
         <v>8995</v>
@@ -900,7 +903,7 @@
         <v>120131</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C10" s="10">
         <v>842</v>
@@ -917,7 +920,7 @@
         <v>120132</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C11" s="10">
         <v>2040</v>
@@ -934,7 +937,7 @@
         <v>130150</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C12" s="10">
         <v>4552</v>
@@ -951,7 +954,7 @@
         <v>130151</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C13" s="10">
         <v>2674</v>
@@ -968,7 +971,7 @@
         <v>130152</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C14" s="10">
         <v>22079</v>
@@ -985,7 +988,7 @@
         <v>130153</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C15" s="10">
         <v>15067</v>
@@ -1002,7 +1005,7 @@
         <v>130154</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C16" s="10">
         <v>14849</v>
@@ -1019,7 +1022,7 @@
         <v>130155</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C17" s="10">
         <v>16205</v>
@@ -1036,7 +1039,7 @@
         <v>130156</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C18" s="10">
         <v>904</v>
@@ -1053,7 +1056,7 @@
         <v>130700</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C19" s="10">
         <v>1356</v>
@@ -1070,7 +1073,7 @@
         <v>130701</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C20" s="10">
         <v>1315</v>
@@ -1087,7 +1090,7 @@
         <v>130702</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C21" s="10">
         <v>3298</v>
@@ -1104,7 +1107,7 @@
         <v>130703</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C22" s="10">
         <v>5480</v>
@@ -1121,7 +1124,7 @@
         <v>130704</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C23" s="10">
         <v>101</v>
@@ -1138,7 +1141,7 @@
         <v>130707</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C24" s="10">
         <v>250</v>
@@ -1155,7 +1158,7 @@
         <v>131150</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C25" s="10">
         <v>4456</v>
@@ -1172,7 +1175,7 @@
         <v>131151</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C26" s="10">
         <v>7473</v>
@@ -1189,7 +1192,7 @@
         <v>131152</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C27" s="10">
         <v>3212</v>
@@ -1206,7 +1209,7 @@
         <v>131153</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C28" s="10">
         <v>2446</v>
@@ -1223,7 +1226,7 @@
         <v>131700</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C29" s="10">
         <v>833</v>
@@ -1240,7 +1243,7 @@
         <v>131701</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C30" s="10">
         <v>935</v>
@@ -1257,7 +1260,7 @@
         <v>132150</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C31" s="10">
         <v>5820</v>
@@ -1274,7 +1277,7 @@
         <v>132151</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C32" s="10">
         <v>4858</v>
@@ -1291,7 +1294,7 @@
         <v>132152</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C33" s="10">
         <v>6305</v>
@@ -1308,7 +1311,7 @@
         <v>132153</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C34" s="10">
         <v>4172</v>
@@ -1325,7 +1328,7 @@
         <v>140230</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C35" s="10">
         <v>1515</v>
@@ -1342,7 +1345,7 @@
         <v>140231</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C36" s="10">
         <v>195</v>
@@ -1359,7 +1362,7 @@
         <v>140232</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C37" s="10">
         <v>2555</v>
@@ -1376,7 +1379,7 @@
         <v>150360</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C38" s="10">
         <v>1707</v>
@@ -1393,7 +1396,7 @@
         <v>150361</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C39" s="10">
         <v>3440</v>
@@ -1410,7 +1413,7 @@
         <v>150362</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C40" s="10">
         <v>1847</v>
@@ -1427,7 +1430,7 @@
         <v>150363</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C41" s="10">
         <v>2289</v>
@@ -1444,7 +1447,7 @@
         <v>151500</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C42" s="10">
         <v>537</v>
@@ -1461,7 +1464,7 @@
         <v>151501</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C43" s="10">
         <v>445</v>
@@ -1478,7 +1481,7 @@
         <v>151502</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C44" s="10">
         <v>382</v>
@@ -1495,7 +1498,7 @@
         <v>151503</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C45" s="10">
         <v>222</v>
@@ -1510,7 +1513,7 @@
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C46" s="10">
         <v>4</v>
@@ -1525,7 +1528,7 @@
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
       <c r="B47" s="9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C47" s="10">
         <v>25</v>
@@ -1569,27 +1572,27 @@
       <c r="F1" s="19"/>
       <c r="G1" s="19"/>
     </row>
-    <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
@@ -1617,22 +1620,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C06359-78AF-4661-B397-B49FA40B98BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DBB6D9-3925-4C00-BD57-7BD385F0DAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
-    <sheet name="SALES BY SKU" sheetId="1" r:id="rId1"/>
+    <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
     <sheet name="DASHBOARD" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>SALES BY SKU</t>
   </si>
@@ -43,9 +43,6 @@
     <t>DASHBOARD</t>
   </si>
   <si>
-    <t>PROMD VTA DIA</t>
-  </si>
-  <si>
     <t>FORECAST</t>
   </si>
   <si>
@@ -58,12 +55,6 @@
     <t>PRODUCTO</t>
   </si>
   <si>
-    <t>CANTIDAD</t>
-  </si>
-  <si>
-    <t>PROMD VTA 10 DIAS</t>
-  </si>
-  <si>
     <t>Cremosillo Tradicional 150g</t>
   </si>
   <si>
@@ -227,6 +218,12 @@
   </si>
   <si>
     <t>TRANSCURSO DE VENTA</t>
+  </si>
+  <si>
+    <t>PROMEDIO DE VENTA DIARIA</t>
+  </si>
+  <si>
+    <t>VENTA BRUTA</t>
   </si>
 </sst>
 </file>
@@ -433,13 +430,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -757,51 +754,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="50.7109375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-    </row>
-    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-    </row>
-    <row r="3" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+    </row>
+    <row r="3" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>110150</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="10">
         <v>8524</v>
@@ -809,16 +803,13 @@
       <c r="D4" s="10">
         <v>1065.5</v>
       </c>
-      <c r="E4" s="10">
-        <v>10655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>110151</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" s="10">
         <v>614</v>
@@ -826,16 +817,13 @@
       <c r="D5" s="10">
         <v>76.75</v>
       </c>
-      <c r="E5" s="10">
-        <v>767.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>110230</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="10">
         <v>3756</v>
@@ -843,16 +831,13 @@
       <c r="D6" s="10">
         <v>469.5</v>
       </c>
-      <c r="E6" s="10">
-        <v>4695</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>110400</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" s="10">
         <v>730</v>
@@ -860,16 +845,13 @@
       <c r="D7" s="10">
         <v>91.25</v>
       </c>
-      <c r="E7" s="10">
-        <v>912.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>111000</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C8" s="10">
         <v>126</v>
@@ -877,16 +859,13 @@
       <c r="D8" s="10">
         <v>15.75</v>
       </c>
-      <c r="E8" s="10">
-        <v>157.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>120130</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="10">
         <v>8995</v>
@@ -894,16 +873,13 @@
       <c r="D9" s="10">
         <v>1124.375</v>
       </c>
-      <c r="E9" s="10">
-        <v>11243.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>120131</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C10" s="10">
         <v>842</v>
@@ -911,16 +887,13 @@
       <c r="D10" s="10">
         <v>105.25</v>
       </c>
-      <c r="E10" s="10">
-        <v>1052.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>120132</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C11" s="10">
         <v>2040</v>
@@ -928,16 +901,13 @@
       <c r="D11" s="10">
         <v>255</v>
       </c>
-      <c r="E11" s="10">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>130150</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C12" s="10">
         <v>4552</v>
@@ -945,16 +915,13 @@
       <c r="D12" s="10">
         <v>569</v>
       </c>
-      <c r="E12" s="10">
-        <v>5690</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>130151</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C13" s="10">
         <v>2674</v>
@@ -962,16 +929,13 @@
       <c r="D13" s="10">
         <v>334.25</v>
       </c>
-      <c r="E13" s="10">
-        <v>3342.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>130152</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C14" s="10">
         <v>22079</v>
@@ -979,16 +943,13 @@
       <c r="D14" s="10">
         <v>2759.875</v>
       </c>
-      <c r="E14" s="10">
-        <v>27598.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>130153</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C15" s="10">
         <v>15067</v>
@@ -996,16 +957,13 @@
       <c r="D15" s="10">
         <v>1883.375</v>
       </c>
-      <c r="E15" s="10">
-        <v>18833.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>130154</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C16" s="10">
         <v>14849</v>
@@ -1013,16 +971,13 @@
       <c r="D16" s="10">
         <v>1856.125</v>
       </c>
-      <c r="E16" s="10">
-        <v>18561.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>130155</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C17" s="10">
         <v>16205</v>
@@ -1030,16 +985,13 @@
       <c r="D17" s="10">
         <v>2025.625</v>
       </c>
-      <c r="E17" s="10">
-        <v>20256.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>130156</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C18" s="10">
         <v>904</v>
@@ -1047,16 +999,13 @@
       <c r="D18" s="10">
         <v>113</v>
       </c>
-      <c r="E18" s="10">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>130700</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C19" s="10">
         <v>1356</v>
@@ -1064,16 +1013,13 @@
       <c r="D19" s="10">
         <v>169.5</v>
       </c>
-      <c r="E19" s="10">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>130701</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C20" s="10">
         <v>1315</v>
@@ -1081,16 +1027,13 @@
       <c r="D20" s="10">
         <v>164.375</v>
       </c>
-      <c r="E20" s="10">
-        <v>1643.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>130702</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C21" s="10">
         <v>3298</v>
@@ -1098,16 +1041,13 @@
       <c r="D21" s="10">
         <v>412.25</v>
       </c>
-      <c r="E21" s="10">
-        <v>4122.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>130703</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C22" s="10">
         <v>5480</v>
@@ -1115,16 +1055,13 @@
       <c r="D22" s="10">
         <v>685</v>
       </c>
-      <c r="E22" s="10">
-        <v>6850</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>130704</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C23" s="10">
         <v>101</v>
@@ -1132,16 +1069,13 @@
       <c r="D23" s="10">
         <v>12.625</v>
       </c>
-      <c r="E23" s="10">
-        <v>126.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>130707</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C24" s="10">
         <v>250</v>
@@ -1149,16 +1083,13 @@
       <c r="D24" s="10">
         <v>31.25</v>
       </c>
-      <c r="E24" s="10">
-        <v>312.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>131150</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C25" s="10">
         <v>4456</v>
@@ -1166,16 +1097,13 @@
       <c r="D25" s="10">
         <v>557</v>
       </c>
-      <c r="E25" s="10">
-        <v>5570</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>131151</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C26" s="10">
         <v>7473</v>
@@ -1183,16 +1111,13 @@
       <c r="D26" s="10">
         <v>934.125</v>
       </c>
-      <c r="E26" s="10">
-        <v>9341.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>131152</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C27" s="10">
         <v>3212</v>
@@ -1200,16 +1125,13 @@
       <c r="D27" s="10">
         <v>401.5</v>
       </c>
-      <c r="E27" s="10">
-        <v>4015</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>131153</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C28" s="10">
         <v>2446</v>
@@ -1217,16 +1139,13 @@
       <c r="D28" s="10">
         <v>305.75</v>
       </c>
-      <c r="E28" s="10">
-        <v>3057.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>131700</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C29" s="10">
         <v>833</v>
@@ -1234,16 +1153,13 @@
       <c r="D29" s="10">
         <v>104.125</v>
       </c>
-      <c r="E29" s="10">
-        <v>1041.25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>131701</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C30" s="10">
         <v>935</v>
@@ -1251,16 +1167,13 @@
       <c r="D30" s="10">
         <v>116.875</v>
       </c>
-      <c r="E30" s="10">
-        <v>1168.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>132150</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C31" s="10">
         <v>5820</v>
@@ -1268,16 +1181,13 @@
       <c r="D31" s="10">
         <v>727.5</v>
       </c>
-      <c r="E31" s="10">
-        <v>7275</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>132151</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C32" s="10">
         <v>4858</v>
@@ -1285,16 +1195,13 @@
       <c r="D32" s="10">
         <v>607.25</v>
       </c>
-      <c r="E32" s="10">
-        <v>6072.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>132152</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C33" s="10">
         <v>6305</v>
@@ -1302,16 +1209,13 @@
       <c r="D33" s="10">
         <v>788.125</v>
       </c>
-      <c r="E33" s="10">
-        <v>7881.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>132153</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C34" s="10">
         <v>4172</v>
@@ -1319,16 +1223,13 @@
       <c r="D34" s="10">
         <v>521.5</v>
       </c>
-      <c r="E34" s="10">
-        <v>5215</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>140230</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C35" s="10">
         <v>1515</v>
@@ -1336,16 +1237,13 @@
       <c r="D35" s="10">
         <v>189.375</v>
       </c>
-      <c r="E35" s="10">
-        <v>1893.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>140231</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C36" s="10">
         <v>195</v>
@@ -1353,16 +1251,13 @@
       <c r="D36" s="10">
         <v>24.375</v>
       </c>
-      <c r="E36" s="10">
-        <v>243.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>140232</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C37" s="10">
         <v>2555</v>
@@ -1370,16 +1265,13 @@
       <c r="D37" s="10">
         <v>319.375</v>
       </c>
-      <c r="E37" s="10">
-        <v>3193.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>150360</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C38" s="10">
         <v>1707</v>
@@ -1387,16 +1279,13 @@
       <c r="D38" s="10">
         <v>213.375</v>
       </c>
-      <c r="E38" s="10">
-        <v>2133.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>150361</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C39" s="10">
         <v>3440</v>
@@ -1404,16 +1293,13 @@
       <c r="D39" s="10">
         <v>430</v>
       </c>
-      <c r="E39" s="10">
-        <v>4300</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>150362</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C40" s="10">
         <v>1847</v>
@@ -1421,16 +1307,13 @@
       <c r="D40" s="10">
         <v>230.875</v>
       </c>
-      <c r="E40" s="10">
-        <v>2308.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>150363</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C41" s="10">
         <v>2289</v>
@@ -1438,16 +1321,13 @@
       <c r="D41" s="10">
         <v>286.125</v>
       </c>
-      <c r="E41" s="10">
-        <v>2861.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>151500</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C42" s="10">
         <v>537</v>
@@ -1455,16 +1335,13 @@
       <c r="D42" s="10">
         <v>67.125</v>
       </c>
-      <c r="E42" s="10">
-        <v>671.25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>151501</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C43" s="10">
         <v>445</v>
@@ -1472,16 +1349,13 @@
       <c r="D43" s="10">
         <v>55.625</v>
       </c>
-      <c r="E43" s="10">
-        <v>556.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>151502</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C44" s="10">
         <v>382</v>
@@ -1489,16 +1363,13 @@
       <c r="D44" s="10">
         <v>47.75</v>
       </c>
-      <c r="E44" s="10">
-        <v>477.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>151503</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C45" s="10">
         <v>222</v>
@@ -1506,14 +1377,11 @@
       <c r="D45" s="10">
         <v>27.75</v>
       </c>
-      <c r="E45" s="10">
-        <v>277.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C46" s="10">
         <v>4</v>
@@ -1521,14 +1389,11 @@
       <c r="D46" s="10">
         <v>0.5</v>
       </c>
-      <c r="E46" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
       <c r="B47" s="9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C47" s="10">
         <v>25</v>
@@ -1536,18 +1401,15 @@
       <c r="D47" s="10">
         <v>3.125</v>
       </c>
-      <c r="E47" s="10">
-        <v>31.25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C48" s="16">
         <v>169430</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1562,37 +1424,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
@@ -1620,22 +1482,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="D4" s="11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DBB6D9-3925-4C00-BD57-7BD385F0DAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53E807D-FAF8-40AD-891A-36009874D983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53E807D-FAF8-40AD-891A-36009874D983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7BE71D-912C-4A08-AFF7-5D60760B662B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -35,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
-  <si>
-    <t>SALES BY SKU</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>DASHBOARD</t>
   </si>
@@ -230,7 +227,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,14 +245,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -357,21 +346,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -394,36 +374,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -433,12 +412,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,663 +729,644 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="50.7109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" style="14" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-    </row>
-    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-    </row>
-    <row r="3" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>110150</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>61</v>
+      <c r="C2" s="17">
+        <v>8524</v>
+      </c>
+      <c r="D2" s="18">
+        <v>1065.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>110151</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="17">
+        <v>614</v>
+      </c>
+      <c r="D3" s="18">
+        <v>76.75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <v>110150</v>
+        <v>110230</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="10">
-        <v>8524</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1065.5</v>
+        <v>9</v>
+      </c>
+      <c r="C4" s="17">
+        <v>3756</v>
+      </c>
+      <c r="D4" s="18">
+        <v>469.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
-        <v>110151</v>
+        <v>110400</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="10">
-        <v>614</v>
-      </c>
-      <c r="D5" s="10">
-        <v>76.75</v>
+        <v>10</v>
+      </c>
+      <c r="C5" s="17">
+        <v>730</v>
+      </c>
+      <c r="D5" s="18">
+        <v>91.25</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
-        <v>110230</v>
+        <v>111000</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10">
-        <v>3756</v>
-      </c>
-      <c r="D6" s="10">
-        <v>469.5</v>
+        <v>11</v>
+      </c>
+      <c r="C6" s="17">
+        <v>126</v>
+      </c>
+      <c r="D6" s="18">
+        <v>15.75</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
-        <v>110400</v>
+        <v>120130</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="10">
-        <v>730</v>
-      </c>
-      <c r="D7" s="10">
-        <v>91.25</v>
+        <v>12</v>
+      </c>
+      <c r="C7" s="17">
+        <v>8995</v>
+      </c>
+      <c r="D7" s="18">
+        <v>1124.375</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
-        <v>111000</v>
+        <v>120131</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="10">
-        <v>126</v>
-      </c>
-      <c r="D8" s="10">
-        <v>15.75</v>
+        <v>13</v>
+      </c>
+      <c r="C8" s="17">
+        <v>842</v>
+      </c>
+      <c r="D8" s="18">
+        <v>105.25</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
-        <v>120130</v>
+        <v>120132</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="10">
-        <v>8995</v>
-      </c>
-      <c r="D9" s="10">
-        <v>1124.375</v>
+        <v>14</v>
+      </c>
+      <c r="C9" s="17">
+        <v>2040</v>
+      </c>
+      <c r="D9" s="18">
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
-        <v>120131</v>
+        <v>130150</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="10">
-        <v>842</v>
-      </c>
-      <c r="D10" s="10">
-        <v>105.25</v>
+        <v>15</v>
+      </c>
+      <c r="C10" s="17">
+        <v>4552</v>
+      </c>
+      <c r="D10" s="18">
+        <v>569</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
-        <v>120132</v>
+        <v>130151</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="10">
-        <v>2040</v>
-      </c>
-      <c r="D11" s="10">
-        <v>255</v>
+        <v>16</v>
+      </c>
+      <c r="C11" s="17">
+        <v>2674</v>
+      </c>
+      <c r="D11" s="18">
+        <v>334.25</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
-        <v>130150</v>
+        <v>130152</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4552</v>
-      </c>
-      <c r="D12" s="10">
-        <v>569</v>
+        <v>17</v>
+      </c>
+      <c r="C12" s="17">
+        <v>22079</v>
+      </c>
+      <c r="D12" s="18">
+        <v>2759.875</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
-        <v>130151</v>
+        <v>130153</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="10">
-        <v>2674</v>
-      </c>
-      <c r="D13" s="10">
-        <v>334.25</v>
+        <v>18</v>
+      </c>
+      <c r="C13" s="17">
+        <v>15067</v>
+      </c>
+      <c r="D13" s="18">
+        <v>1883.375</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
-        <v>130152</v>
+        <v>130154</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="10">
-        <v>22079</v>
-      </c>
-      <c r="D14" s="10">
-        <v>2759.875</v>
+        <v>19</v>
+      </c>
+      <c r="C14" s="17">
+        <v>14849</v>
+      </c>
+      <c r="D14" s="18">
+        <v>1856.125</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
-        <v>130153</v>
+        <v>130155</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="10">
-        <v>15067</v>
-      </c>
-      <c r="D15" s="10">
-        <v>1883.375</v>
+        <v>20</v>
+      </c>
+      <c r="C15" s="17">
+        <v>16205</v>
+      </c>
+      <c r="D15" s="18">
+        <v>2025.625</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
-        <v>130154</v>
+        <v>130156</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="10">
-        <v>14849</v>
-      </c>
-      <c r="D16" s="10">
-        <v>1856.125</v>
+        <v>21</v>
+      </c>
+      <c r="C16" s="17">
+        <v>904</v>
+      </c>
+      <c r="D16" s="18">
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
-        <v>130155</v>
+        <v>130700</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="10">
-        <v>16205</v>
-      </c>
-      <c r="D17" s="10">
-        <v>2025.625</v>
+        <v>22</v>
+      </c>
+      <c r="C17" s="17">
+        <v>1356</v>
+      </c>
+      <c r="D17" s="18">
+        <v>169.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
-        <v>130156</v>
+        <v>130701</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="10">
-        <v>904</v>
-      </c>
-      <c r="D18" s="10">
-        <v>113</v>
+        <v>23</v>
+      </c>
+      <c r="C18" s="17">
+        <v>1315</v>
+      </c>
+      <c r="D18" s="18">
+        <v>164.375</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <v>130700</v>
+        <v>130702</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="10">
-        <v>1356</v>
-      </c>
-      <c r="D19" s="10">
-        <v>169.5</v>
+        <v>24</v>
+      </c>
+      <c r="C19" s="17">
+        <v>3298</v>
+      </c>
+      <c r="D19" s="18">
+        <v>412.25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
-        <v>130701</v>
+        <v>130703</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="10">
-        <v>1315</v>
-      </c>
-      <c r="D20" s="10">
-        <v>164.375</v>
+        <v>25</v>
+      </c>
+      <c r="C20" s="17">
+        <v>5480</v>
+      </c>
+      <c r="D20" s="18">
+        <v>685</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
-        <v>130702</v>
+        <v>130704</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="10">
-        <v>3298</v>
-      </c>
-      <c r="D21" s="10">
-        <v>412.25</v>
+        <v>26</v>
+      </c>
+      <c r="C21" s="17">
+        <v>101</v>
+      </c>
+      <c r="D21" s="18">
+        <v>12.625</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
-        <v>130703</v>
+        <v>130707</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="10">
-        <v>5480</v>
-      </c>
-      <c r="D22" s="10">
-        <v>685</v>
+        <v>27</v>
+      </c>
+      <c r="C22" s="17">
+        <v>250</v>
+      </c>
+      <c r="D22" s="18">
+        <v>31.25</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
-        <v>130704</v>
+        <v>131150</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="10">
-        <v>101</v>
-      </c>
-      <c r="D23" s="10">
-        <v>12.625</v>
+        <v>28</v>
+      </c>
+      <c r="C23" s="17">
+        <v>4456</v>
+      </c>
+      <c r="D23" s="18">
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
-        <v>130707</v>
+        <v>131151</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="10">
-        <v>250</v>
-      </c>
-      <c r="D24" s="10">
-        <v>31.25</v>
+        <v>29</v>
+      </c>
+      <c r="C24" s="17">
+        <v>7473</v>
+      </c>
+      <c r="D24" s="18">
+        <v>934.125</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
-        <v>131150</v>
+        <v>131152</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="10">
-        <v>4456</v>
-      </c>
-      <c r="D25" s="10">
-        <v>557</v>
+        <v>30</v>
+      </c>
+      <c r="C25" s="17">
+        <v>3212</v>
+      </c>
+      <c r="D25" s="18">
+        <v>401.5</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
-        <v>131151</v>
+        <v>131153</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="10">
-        <v>7473</v>
-      </c>
-      <c r="D26" s="10">
-        <v>934.125</v>
+        <v>31</v>
+      </c>
+      <c r="C26" s="17">
+        <v>2446</v>
+      </c>
+      <c r="D26" s="18">
+        <v>305.75</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
-        <v>131152</v>
+        <v>131700</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="10">
-        <v>3212</v>
-      </c>
-      <c r="D27" s="10">
-        <v>401.5</v>
+        <v>32</v>
+      </c>
+      <c r="C27" s="17">
+        <v>833</v>
+      </c>
+      <c r="D27" s="18">
+        <v>104.125</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
-        <v>131153</v>
+        <v>131701</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="10">
-        <v>2446</v>
-      </c>
-      <c r="D28" s="10">
-        <v>305.75</v>
+        <v>33</v>
+      </c>
+      <c r="C28" s="17">
+        <v>935</v>
+      </c>
+      <c r="D28" s="18">
+        <v>116.875</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
-        <v>131700</v>
+        <v>132150</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="10">
-        <v>833</v>
-      </c>
-      <c r="D29" s="10">
-        <v>104.125</v>
+        <v>34</v>
+      </c>
+      <c r="C29" s="17">
+        <v>5820</v>
+      </c>
+      <c r="D29" s="18">
+        <v>727.5</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
-        <v>131701</v>
+        <v>132151</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="10">
-        <v>935</v>
-      </c>
-      <c r="D30" s="10">
-        <v>116.875</v>
+        <v>35</v>
+      </c>
+      <c r="C30" s="17">
+        <v>4858</v>
+      </c>
+      <c r="D30" s="18">
+        <v>607.25</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
-        <v>132150</v>
+        <v>132152</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="10">
-        <v>5820</v>
-      </c>
-      <c r="D31" s="10">
-        <v>727.5</v>
+        <v>36</v>
+      </c>
+      <c r="C31" s="17">
+        <v>6305</v>
+      </c>
+      <c r="D31" s="18">
+        <v>788.125</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
-        <v>132151</v>
+        <v>132153</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="10">
-        <v>4858</v>
-      </c>
-      <c r="D32" s="10">
-        <v>607.25</v>
+        <v>37</v>
+      </c>
+      <c r="C32" s="17">
+        <v>4172</v>
+      </c>
+      <c r="D32" s="18">
+        <v>521.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
-        <v>132152</v>
+        <v>140230</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="10">
-        <v>6305</v>
-      </c>
-      <c r="D33" s="10">
-        <v>788.125</v>
+        <v>38</v>
+      </c>
+      <c r="C33" s="17">
+        <v>1515</v>
+      </c>
+      <c r="D33" s="18">
+        <v>189.375</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
-        <v>132153</v>
+        <v>140231</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="10">
-        <v>4172</v>
-      </c>
-      <c r="D34" s="10">
-        <v>521.5</v>
+        <v>39</v>
+      </c>
+      <c r="C34" s="17">
+        <v>195</v>
+      </c>
+      <c r="D34" s="18">
+        <v>24.375</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
-        <v>140230</v>
+        <v>140232</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="10">
-        <v>1515</v>
-      </c>
-      <c r="D35" s="10">
-        <v>189.375</v>
+        <v>40</v>
+      </c>
+      <c r="C35" s="17">
+        <v>2555</v>
+      </c>
+      <c r="D35" s="18">
+        <v>319.375</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
-        <v>140231</v>
+        <v>150360</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="10">
-        <v>195</v>
-      </c>
-      <c r="D36" s="10">
-        <v>24.375</v>
+        <v>41</v>
+      </c>
+      <c r="C36" s="17">
+        <v>1707</v>
+      </c>
+      <c r="D36" s="18">
+        <v>213.375</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
-        <v>140232</v>
+        <v>150361</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="10">
-        <v>2555</v>
-      </c>
-      <c r="D37" s="10">
-        <v>319.375</v>
+        <v>42</v>
+      </c>
+      <c r="C37" s="17">
+        <v>3440</v>
+      </c>
+      <c r="D37" s="18">
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
-        <v>150360</v>
+        <v>150362</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="10">
-        <v>1707</v>
-      </c>
-      <c r="D38" s="10">
-        <v>213.375</v>
+        <v>43</v>
+      </c>
+      <c r="C38" s="17">
+        <v>1847</v>
+      </c>
+      <c r="D38" s="18">
+        <v>230.875</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
-        <v>150361</v>
+        <v>150363</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="10">
-        <v>3440</v>
-      </c>
-      <c r="D39" s="10">
-        <v>430</v>
+        <v>44</v>
+      </c>
+      <c r="C39" s="17">
+        <v>2289</v>
+      </c>
+      <c r="D39" s="18">
+        <v>286.125</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
-        <v>150362</v>
+        <v>151500</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="10">
-        <v>1847</v>
-      </c>
-      <c r="D40" s="10">
-        <v>230.875</v>
+        <v>45</v>
+      </c>
+      <c r="C40" s="17">
+        <v>537</v>
+      </c>
+      <c r="D40" s="18">
+        <v>67.125</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
-        <v>150363</v>
+        <v>151501</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="10">
-        <v>2289</v>
-      </c>
-      <c r="D41" s="10">
-        <v>286.125</v>
+        <v>46</v>
+      </c>
+      <c r="C41" s="17">
+        <v>445</v>
+      </c>
+      <c r="D41" s="18">
+        <v>55.625</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
-        <v>151500</v>
+        <v>151502</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="10">
-        <v>537</v>
-      </c>
-      <c r="D42" s="10">
-        <v>67.125</v>
+        <v>47</v>
+      </c>
+      <c r="C42" s="17">
+        <v>382</v>
+      </c>
+      <c r="D42" s="18">
+        <v>47.75</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
-        <v>151501</v>
+        <v>151503</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="10">
-        <v>445</v>
-      </c>
-      <c r="D43" s="10">
-        <v>55.625</v>
+        <v>48</v>
+      </c>
+      <c r="C43" s="17">
+        <v>222</v>
+      </c>
+      <c r="D43" s="18">
+        <v>27.75</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="8">
-        <v>151502</v>
-      </c>
+      <c r="A44" s="8"/>
       <c r="B44" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="10">
-        <v>382</v>
-      </c>
-      <c r="D44" s="10">
-        <v>47.75</v>
+        <v>49</v>
+      </c>
+      <c r="C44" s="17">
+        <v>4</v>
+      </c>
+      <c r="D44" s="18">
+        <v>0.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
-        <v>151503</v>
-      </c>
+      <c r="A45" s="8"/>
       <c r="B45" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="10">
-        <v>222</v>
-      </c>
-      <c r="D45" s="10">
-        <v>27.75</v>
+        <v>50</v>
+      </c>
+      <c r="C45" s="17">
+        <v>25</v>
+      </c>
+      <c r="D45" s="18">
+        <v>3.125</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="10">
-        <v>4</v>
-      </c>
-      <c r="D46" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="10">
-        <v>25</v>
-      </c>
-      <c r="D47" s="10">
-        <v>3.125</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="16">
-        <v>169430</v>
-      </c>
+      <c r="C46" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1424,37 +1380,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
@@ -1481,42 +1437,42 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="F4" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>2145</v>
+      </c>
+      <c r="B5" s="12">
+        <v>46204</v>
+      </c>
+      <c r="C5" s="12">
+        <v>46216</v>
+      </c>
+      <c r="D5" s="12">
+        <v>46234</v>
+      </c>
+      <c r="E5" s="13">
         <v>8</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
-        <v>2145</v>
-      </c>
-      <c r="B5" s="13">
-        <v>46204</v>
-      </c>
-      <c r="C5" s="13">
-        <v>46216</v>
-      </c>
-      <c r="D5" s="13">
-        <v>46234</v>
-      </c>
-      <c r="E5" s="14">
-        <v>8</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>15</v>
       </c>
     </row>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7BE71D-912C-4A08-AFF7-5D60760B662B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FFF455-C575-4CE4-86A0-ECCA32E6E15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
     <sheet name="DASHBOARD" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -402,18 +405,18 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,6 +433,438 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="INVENTARIO NACIONAL 03-07-26"/>
+      <sheetName val="VINCULO VTS BY SKU JUNIO"/>
+      <sheetName val="VINCULO VTS BY SKU OPEN"/>
+      <sheetName val="DESV. VTS BY SKU"/>
+      <sheetName val="INVENTARIO NACIONAL 03-07-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 06-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 07-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 08-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 09-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 10-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 13-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-07-26"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="3">
+          <cell r="G3">
+            <v>190238</v>
+          </cell>
+          <cell r="H3">
+            <v>188030</v>
+          </cell>
+          <cell r="I3">
+            <v>21137.555555555555</v>
+          </cell>
+          <cell r="J3">
+            <v>486163.77777777775</v>
+          </cell>
+          <cell r="K3">
+            <v>696207</v>
+          </cell>
+          <cell r="L3">
+            <v>0.27324919169155149</v>
+          </cell>
+          <cell r="M3">
+            <v>-505969</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4">
+            <v>9430</v>
+          </cell>
+          <cell r="D4">
+            <v>1047.7777777777778</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>675</v>
+          </cell>
+          <cell r="D5">
+            <v>75</v>
+          </cell>
+          <cell r="G5">
+            <v>2208</v>
+          </cell>
+          <cell r="H5">
+            <v>46204</v>
+          </cell>
+          <cell r="I5">
+            <v>46216</v>
+          </cell>
+          <cell r="J5">
+            <v>46234</v>
+          </cell>
+          <cell r="K5">
+            <v>9</v>
+          </cell>
+          <cell r="L5">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>4261</v>
+          </cell>
+          <cell r="D6">
+            <v>473.44444444444446</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>797</v>
+          </cell>
+          <cell r="D7">
+            <v>88.555555555555557</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>139</v>
+          </cell>
+          <cell r="D8">
+            <v>15.444444444444445</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>10278</v>
+          </cell>
+          <cell r="D9">
+            <v>1142</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>913</v>
+          </cell>
+          <cell r="D10">
+            <v>101.44444444444444</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>2314</v>
+          </cell>
+          <cell r="D11">
+            <v>257.11111111111109</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>5040</v>
+          </cell>
+          <cell r="D12">
+            <v>560</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>2933</v>
+          </cell>
+          <cell r="D13">
+            <v>325.88888888888891</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>24613</v>
+          </cell>
+          <cell r="D14">
+            <v>2734.7777777777778</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>16778</v>
+          </cell>
+          <cell r="D15">
+            <v>1864.2222222222222</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>16429</v>
+          </cell>
+          <cell r="D16">
+            <v>1825.4444444444443</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>18000</v>
+          </cell>
+          <cell r="D17">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>962</v>
+          </cell>
+          <cell r="D18">
+            <v>106.88888888888889</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>1486</v>
+          </cell>
+          <cell r="D19">
+            <v>165.11111111111111</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>1388</v>
+          </cell>
+          <cell r="D20">
+            <v>154.22222222222223</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>3570</v>
+          </cell>
+          <cell r="D21">
+            <v>396.66666666666669</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>5794</v>
+          </cell>
+          <cell r="D22">
+            <v>643.77777777777783</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>101</v>
+          </cell>
+          <cell r="D23">
+            <v>11.222222222222221</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>250</v>
+          </cell>
+          <cell r="D24">
+            <v>27.777777777777779</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>5002</v>
+          </cell>
+          <cell r="D25">
+            <v>555.77777777777783</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>8496</v>
+          </cell>
+          <cell r="D26">
+            <v>944</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>3522</v>
+          </cell>
+          <cell r="D27">
+            <v>391.33333333333331</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>2796</v>
+          </cell>
+          <cell r="D28">
+            <v>310.66666666666669</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>896</v>
+          </cell>
+          <cell r="D29">
+            <v>99.555555555555557</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>1016</v>
+          </cell>
+          <cell r="D30">
+            <v>112.88888888888889</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>6357</v>
+          </cell>
+          <cell r="D31">
+            <v>706.33333333333337</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>5281</v>
+          </cell>
+          <cell r="D32">
+            <v>586.77777777777783</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>6877</v>
+          </cell>
+          <cell r="D33">
+            <v>764.11111111111109</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="C34">
+            <v>4558</v>
+          </cell>
+          <cell r="D34">
+            <v>506.44444444444446</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="C35">
+            <v>1695</v>
+          </cell>
+          <cell r="D35">
+            <v>188.33333333333334</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36">
+            <v>423</v>
+          </cell>
+          <cell r="D36">
+            <v>47</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="C37">
+            <v>2888</v>
+          </cell>
+          <cell r="D37">
+            <v>320.88888888888891</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="C38">
+            <v>2023</v>
+          </cell>
+          <cell r="D38">
+            <v>224.77777777777777</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="C39">
+            <v>3800</v>
+          </cell>
+          <cell r="D39">
+            <v>422.22222222222223</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="C40">
+            <v>2062</v>
+          </cell>
+          <cell r="D40">
+            <v>229.11111111111111</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="C41">
+            <v>2484</v>
+          </cell>
+          <cell r="D41">
+            <v>276</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42">
+            <v>543</v>
+          </cell>
+          <cell r="D42">
+            <v>60.333333333333336</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>475</v>
+          </cell>
+          <cell r="D43">
+            <v>52.777777777777779</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>394</v>
+          </cell>
+          <cell r="D44">
+            <v>43.777777777777779</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>260</v>
+          </cell>
+          <cell r="D45">
+            <v>28.888888888888889</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>4</v>
+          </cell>
+          <cell r="D46">
+            <v>0.44444444444444442</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="C47">
+            <v>27</v>
+          </cell>
+          <cell r="D47">
+            <v>3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -732,7 +1167,7 @@
   <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="50.7109375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" style="13" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
   </cols>
@@ -759,10 +1194,12 @@
         <v>5</v>
       </c>
       <c r="C2" s="17">
-        <v>8524</v>
-      </c>
-      <c r="D2" s="18">
-        <v>1065.5</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
+        <v>9430</v>
+      </c>
+      <c r="D2" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
+        <v>1047.7777777777778</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -773,10 +1210,12 @@
         <v>8</v>
       </c>
       <c r="C3" s="17">
-        <v>614</v>
-      </c>
-      <c r="D3" s="18">
-        <v>76.75</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
+        <v>675</v>
+      </c>
+      <c r="D3" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -787,10 +1226,12 @@
         <v>9</v>
       </c>
       <c r="C4" s="17">
-        <v>3756</v>
-      </c>
-      <c r="D4" s="18">
-        <v>469.5</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
+        <v>4261</v>
+      </c>
+      <c r="D4" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
+        <v>473.44444444444446</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -801,10 +1242,12 @@
         <v>10</v>
       </c>
       <c r="C5" s="17">
-        <v>730</v>
-      </c>
-      <c r="D5" s="18">
-        <v>91.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
+        <v>797</v>
+      </c>
+      <c r="D5" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
+        <v>88.555555555555557</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -815,10 +1258,12 @@
         <v>11</v>
       </c>
       <c r="C6" s="17">
-        <v>126</v>
-      </c>
-      <c r="D6" s="18">
-        <v>15.75</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
+        <v>139</v>
+      </c>
+      <c r="D6" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
+        <v>15.444444444444445</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -829,10 +1274,12 @@
         <v>12</v>
       </c>
       <c r="C7" s="17">
-        <v>8995</v>
-      </c>
-      <c r="D7" s="18">
-        <v>1124.375</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
+        <v>10278</v>
+      </c>
+      <c r="D7" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
+        <v>1142</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -843,10 +1290,12 @@
         <v>13</v>
       </c>
       <c r="C8" s="17">
-        <v>842</v>
-      </c>
-      <c r="D8" s="18">
-        <v>105.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
+        <v>913</v>
+      </c>
+      <c r="D8" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
+        <v>101.44444444444444</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -857,10 +1306,12 @@
         <v>14</v>
       </c>
       <c r="C9" s="17">
-        <v>2040</v>
-      </c>
-      <c r="D9" s="18">
-        <v>255</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
+        <v>2314</v>
+      </c>
+      <c r="D9" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
+        <v>257.11111111111109</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -871,10 +1322,12 @@
         <v>15</v>
       </c>
       <c r="C10" s="17">
-        <v>4552</v>
-      </c>
-      <c r="D10" s="18">
-        <v>569</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
+        <v>5040</v>
+      </c>
+      <c r="D10" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,10 +1338,12 @@
         <v>16</v>
       </c>
       <c r="C11" s="17">
-        <v>2674</v>
-      </c>
-      <c r="D11" s="18">
-        <v>334.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
+        <v>2933</v>
+      </c>
+      <c r="D11" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
+        <v>325.88888888888891</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -899,10 +1354,12 @@
         <v>17</v>
       </c>
       <c r="C12" s="17">
-        <v>22079</v>
-      </c>
-      <c r="D12" s="18">
-        <v>2759.875</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
+        <v>24613</v>
+      </c>
+      <c r="D12" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
+        <v>2734.7777777777778</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -913,10 +1370,12 @@
         <v>18</v>
       </c>
       <c r="C13" s="17">
-        <v>15067</v>
-      </c>
-      <c r="D13" s="18">
-        <v>1883.375</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
+        <v>16778</v>
+      </c>
+      <c r="D13" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
+        <v>1864.2222222222222</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -927,10 +1386,12 @@
         <v>19</v>
       </c>
       <c r="C14" s="17">
-        <v>14849</v>
-      </c>
-      <c r="D14" s="18">
-        <v>1856.125</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
+        <v>16429</v>
+      </c>
+      <c r="D14" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
+        <v>1825.4444444444443</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -941,10 +1402,12 @@
         <v>20</v>
       </c>
       <c r="C15" s="17">
-        <v>16205</v>
-      </c>
-      <c r="D15" s="18">
-        <v>2025.625</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
+        <v>18000</v>
+      </c>
+      <c r="D15" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -955,10 +1418,12 @@
         <v>21</v>
       </c>
       <c r="C16" s="17">
-        <v>904</v>
-      </c>
-      <c r="D16" s="18">
-        <v>113</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
+        <v>962</v>
+      </c>
+      <c r="D16" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
+        <v>106.88888888888889</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -969,10 +1434,12 @@
         <v>22</v>
       </c>
       <c r="C17" s="17">
-        <v>1356</v>
-      </c>
-      <c r="D17" s="18">
-        <v>169.5</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
+        <v>1486</v>
+      </c>
+      <c r="D17" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
+        <v>165.11111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -983,10 +1450,12 @@
         <v>23</v>
       </c>
       <c r="C18" s="17">
-        <v>1315</v>
-      </c>
-      <c r="D18" s="18">
-        <v>164.375</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
+        <v>1388</v>
+      </c>
+      <c r="D18" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
+        <v>154.22222222222223</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -997,10 +1466,12 @@
         <v>24</v>
       </c>
       <c r="C19" s="17">
-        <v>3298</v>
-      </c>
-      <c r="D19" s="18">
-        <v>412.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
+        <v>3570</v>
+      </c>
+      <c r="D19" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
+        <v>396.66666666666669</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1011,10 +1482,12 @@
         <v>25</v>
       </c>
       <c r="C20" s="17">
-        <v>5480</v>
-      </c>
-      <c r="D20" s="18">
-        <v>685</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
+        <v>5794</v>
+      </c>
+      <c r="D20" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
+        <v>643.77777777777783</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1025,10 +1498,12 @@
         <v>26</v>
       </c>
       <c r="C21" s="17">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
         <v>101</v>
       </c>
-      <c r="D21" s="18">
-        <v>12.625</v>
+      <c r="D21" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
+        <v>11.222222222222221</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1039,10 +1514,12 @@
         <v>27</v>
       </c>
       <c r="C22" s="17">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
         <v>250</v>
       </c>
-      <c r="D22" s="18">
-        <v>31.25</v>
+      <c r="D22" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
+        <v>27.777777777777779</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1053,10 +1530,12 @@
         <v>28</v>
       </c>
       <c r="C23" s="17">
-        <v>4456</v>
-      </c>
-      <c r="D23" s="18">
-        <v>557</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
+        <v>5002</v>
+      </c>
+      <c r="D23" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
+        <v>555.77777777777783</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1067,10 +1546,12 @@
         <v>29</v>
       </c>
       <c r="C24" s="17">
-        <v>7473</v>
-      </c>
-      <c r="D24" s="18">
-        <v>934.125</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
+        <v>8496</v>
+      </c>
+      <c r="D24" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
+        <v>944</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1081,10 +1562,12 @@
         <v>30</v>
       </c>
       <c r="C25" s="17">
-        <v>3212</v>
-      </c>
-      <c r="D25" s="18">
-        <v>401.5</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
+        <v>3522</v>
+      </c>
+      <c r="D25" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
+        <v>391.33333333333331</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1095,10 +1578,12 @@
         <v>31</v>
       </c>
       <c r="C26" s="17">
-        <v>2446</v>
-      </c>
-      <c r="D26" s="18">
-        <v>305.75</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
+        <v>2796</v>
+      </c>
+      <c r="D26" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
+        <v>310.66666666666669</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1109,10 +1594,12 @@
         <v>32</v>
       </c>
       <c r="C27" s="17">
-        <v>833</v>
-      </c>
-      <c r="D27" s="18">
-        <v>104.125</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
+        <v>896</v>
+      </c>
+      <c r="D27" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
+        <v>99.555555555555557</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1123,10 +1610,12 @@
         <v>33</v>
       </c>
       <c r="C28" s="17">
-        <v>935</v>
-      </c>
-      <c r="D28" s="18">
-        <v>116.875</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
+        <v>1016</v>
+      </c>
+      <c r="D28" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
+        <v>112.88888888888889</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1137,10 +1626,12 @@
         <v>34</v>
       </c>
       <c r="C29" s="17">
-        <v>5820</v>
-      </c>
-      <c r="D29" s="18">
-        <v>727.5</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
+        <v>6357</v>
+      </c>
+      <c r="D29" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
+        <v>706.33333333333337</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1151,10 +1642,12 @@
         <v>35</v>
       </c>
       <c r="C30" s="17">
-        <v>4858</v>
-      </c>
-      <c r="D30" s="18">
-        <v>607.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
+        <v>5281</v>
+      </c>
+      <c r="D30" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
+        <v>586.77777777777783</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1165,10 +1658,12 @@
         <v>36</v>
       </c>
       <c r="C31" s="17">
-        <v>6305</v>
-      </c>
-      <c r="D31" s="18">
-        <v>788.125</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
+        <v>6877</v>
+      </c>
+      <c r="D31" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
+        <v>764.11111111111109</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1179,10 +1674,12 @@
         <v>37</v>
       </c>
       <c r="C32" s="17">
-        <v>4172</v>
-      </c>
-      <c r="D32" s="18">
-        <v>521.5</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
+        <v>4558</v>
+      </c>
+      <c r="D32" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
+        <v>506.44444444444446</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1193,10 +1690,12 @@
         <v>38</v>
       </c>
       <c r="C33" s="17">
-        <v>1515</v>
-      </c>
-      <c r="D33" s="18">
-        <v>189.375</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
+        <v>1695</v>
+      </c>
+      <c r="D33" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
+        <v>188.33333333333334</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1207,10 +1706,12 @@
         <v>39</v>
       </c>
       <c r="C34" s="17">
-        <v>195</v>
-      </c>
-      <c r="D34" s="18">
-        <v>24.375</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
+        <v>423</v>
+      </c>
+      <c r="D34" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1221,10 +1722,12 @@
         <v>40</v>
       </c>
       <c r="C35" s="17">
-        <v>2555</v>
-      </c>
-      <c r="D35" s="18">
-        <v>319.375</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
+        <v>2888</v>
+      </c>
+      <c r="D35" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
+        <v>320.88888888888891</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1235,10 +1738,12 @@
         <v>41</v>
       </c>
       <c r="C36" s="17">
-        <v>1707</v>
-      </c>
-      <c r="D36" s="18">
-        <v>213.375</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
+        <v>2023</v>
+      </c>
+      <c r="D36" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
+        <v>224.77777777777777</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1249,10 +1754,12 @@
         <v>42</v>
       </c>
       <c r="C37" s="17">
-        <v>3440</v>
-      </c>
-      <c r="D37" s="18">
-        <v>430</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
+        <v>3800</v>
+      </c>
+      <c r="D37" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
+        <v>422.22222222222223</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,10 +1770,12 @@
         <v>43</v>
       </c>
       <c r="C38" s="17">
-        <v>1847</v>
-      </c>
-      <c r="D38" s="18">
-        <v>230.875</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
+        <v>2062</v>
+      </c>
+      <c r="D38" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
+        <v>229.11111111111111</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1277,10 +1786,12 @@
         <v>44</v>
       </c>
       <c r="C39" s="17">
-        <v>2289</v>
-      </c>
-      <c r="D39" s="18">
-        <v>286.125</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
+        <v>2484</v>
+      </c>
+      <c r="D39" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1291,10 +1802,12 @@
         <v>45</v>
       </c>
       <c r="C40" s="17">
-        <v>537</v>
-      </c>
-      <c r="D40" s="18">
-        <v>67.125</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
+        <v>543</v>
+      </c>
+      <c r="D40" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
+        <v>60.333333333333336</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1305,10 +1818,12 @@
         <v>46</v>
       </c>
       <c r="C41" s="17">
-        <v>445</v>
-      </c>
-      <c r="D41" s="18">
-        <v>55.625</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
+        <v>475</v>
+      </c>
+      <c r="D41" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
+        <v>52.777777777777779</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1319,10 +1834,12 @@
         <v>47</v>
       </c>
       <c r="C42" s="17">
-        <v>382</v>
-      </c>
-      <c r="D42" s="18">
-        <v>47.75</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
+        <v>394</v>
+      </c>
+      <c r="D42" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
+        <v>43.777777777777779</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1333,10 +1850,12 @@
         <v>48</v>
       </c>
       <c r="C43" s="17">
-        <v>222</v>
-      </c>
-      <c r="D43" s="18">
-        <v>27.75</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
+        <v>260</v>
+      </c>
+      <c r="D43" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
+        <v>28.888888888888889</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1345,10 +1864,12 @@
         <v>49</v>
       </c>
       <c r="C44" s="17">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
         <v>4</v>
       </c>
-      <c r="D44" s="18">
-        <v>0.5</v>
+      <c r="D44" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
+        <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1357,14 +1878,16 @@
         <v>50</v>
       </c>
       <c r="C45" s="17">
-        <v>25</v>
-      </c>
-      <c r="D45" s="18">
-        <v>3.125</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
+        <v>27</v>
+      </c>
+      <c r="D45" s="15">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="15"/>
+      <c r="C46" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1415,25 +1938,32 @@
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
-        <v>171575</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
+        <v>190238</v>
       </c>
       <c r="B3" s="3">
-        <v>169430</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
+        <v>188030</v>
       </c>
       <c r="C3" s="4">
-        <v>21446.875</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
+        <v>21137.555555555555</v>
       </c>
       <c r="D3" s="5">
-        <v>493278.125</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
+        <v>486163.77777777775</v>
       </c>
       <c r="E3" s="4">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
         <v>696207</v>
       </c>
       <c r="F3" s="6">
-        <v>0.24644250919625915</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
+        <v>0.27324919169155149</v>
       </c>
       <c r="G3" s="7">
-        <v>-524632</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
+        <v>-505969</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1458,21 +1988,27 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>2145</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
+        <v>2208</v>
       </c>
       <c r="B5" s="12">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
         <v>46204</v>
       </c>
       <c r="C5" s="12">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
         <v>46216</v>
       </c>
       <c r="D5" s="12">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
         <v>46234</v>
       </c>
-      <c r="E5" s="13">
-        <v>8</v>
-      </c>
-      <c r="F5" s="13">
+      <c r="E5" s="18">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
+        <v>9</v>
+      </c>
+      <c r="F5" s="18">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
         <v>15</v>
       </c>
     </row>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FFF455-C575-4CE4-86A0-ECCA32E6E15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC750C4C-79D7-4E6B-BBF7-4C0B88AF00E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -377,7 +377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -392,7 +392,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -410,12 +409,18 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1167,13 +1172,14 @@
   <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="50.7109375" style="13" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="12"/>
+    <col min="2" max="2" width="50.7109375" style="12" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1187,707 +1193,707 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="A2" s="19">
         <v>110150</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
         <v>9430</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
         <v>1047.7777777777778</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="A3" s="19">
         <v>110151</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
         <v>675</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
         <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="A4" s="19">
         <v>110230</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
         <v>4261</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
         <v>473.44444444444446</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="19">
         <v>110400</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
         <v>797</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
         <v>88.555555555555557</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="A6" s="19">
         <v>111000</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
         <v>139</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
         <v>15.444444444444445</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="A7" s="19">
         <v>120130</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
         <v>10278</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
         <v>1142</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="A8" s="19">
         <v>120131</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
         <v>913</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
         <v>101.44444444444444</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="19">
         <v>120132</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
         <v>2314</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
         <v>257.11111111111109</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="A10" s="19">
         <v>130150</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
         <v>5040</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
         <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="19">
         <v>130151</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
         <v>2933</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
         <v>325.88888888888891</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="A12" s="19">
         <v>130152</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
         <v>24613</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
         <v>2734.7777777777778</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="A13" s="19">
         <v>130153</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
         <v>16778</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
         <v>1864.2222222222222</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="A14" s="19">
         <v>130154</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
         <v>16429</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
         <v>1825.4444444444443</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="A15" s="19">
         <v>130155</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
         <v>18000</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
         <v>2000</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="A16" s="19">
         <v>130156</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
         <v>962</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
         <v>106.88888888888889</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="A17" s="19">
         <v>130700</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
         <v>1486</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
         <v>165.11111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="A18" s="19">
         <v>130701</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
         <v>1388</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
         <v>154.22222222222223</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+      <c r="A19" s="19">
         <v>130702</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
         <v>3570</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
         <v>396.66666666666669</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="A20" s="19">
         <v>130703</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
         <v>5794</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
         <v>643.77777777777783</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="A21" s="19">
         <v>130704</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
         <v>101</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
         <v>11.222222222222221</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="A22" s="19">
         <v>130707</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
         <v>250</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
         <v>27.777777777777779</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="A23" s="19">
         <v>131150</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
         <v>5002</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
         <v>555.77777777777783</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+      <c r="A24" s="19">
         <v>131151</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
         <v>8496</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
         <v>944</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+      <c r="A25" s="19">
         <v>131152</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
         <v>3522</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
         <v>391.33333333333331</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+      <c r="A26" s="19">
         <v>131153</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
         <v>2796</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
         <v>310.66666666666669</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
+      <c r="A27" s="19">
         <v>131700</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
         <v>896</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
         <v>99.555555555555557</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
+      <c r="A28" s="19">
         <v>131701</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
         <v>1016</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
         <v>112.88888888888889</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
+      <c r="A29" s="19">
         <v>132150</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
         <v>6357</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
         <v>706.33333333333337</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
+      <c r="A30" s="19">
         <v>132151</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
         <v>5281</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
         <v>586.77777777777783</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
+      <c r="A31" s="19">
         <v>132152</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
         <v>6877</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
         <v>764.11111111111109</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
+      <c r="A32" s="19">
         <v>132153</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
         <v>4558</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
         <v>506.44444444444446</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
+      <c r="A33" s="19">
         <v>140230</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
         <v>1695</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
         <v>188.33333333333334</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
+      <c r="A34" s="19">
         <v>140231</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
         <v>423</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
         <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
+      <c r="A35" s="19">
         <v>140232</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
         <v>2888</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
         <v>320.88888888888891</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
+      <c r="A36" s="19">
         <v>150360</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
         <v>2023</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
         <v>224.77777777777777</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
+      <c r="A37" s="19">
         <v>150361</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
         <v>3800</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
         <v>422.22222222222223</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
+      <c r="A38" s="19">
         <v>150362</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="17">
+      <c r="C38" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
         <v>2062</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
         <v>229.11111111111111</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
+      <c r="A39" s="19">
         <v>150363</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
         <v>2484</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
         <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
+      <c r="A40" s="19">
         <v>151500</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
         <v>543</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
         <v>60.333333333333336</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
+      <c r="A41" s="19">
         <v>151501</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
         <v>475</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
         <v>52.777777777777779</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
+      <c r="A42" s="19">
         <v>151502</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
         <v>394</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
         <v>43.777777777777779</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="8">
+      <c r="A43" s="19">
         <v>151503</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
         <v>260</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
         <v>28.888888888888889</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9" t="s">
+      <c r="A44" s="19"/>
+      <c r="B44" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
         <v>4</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
         <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9" t="s">
+      <c r="A45" s="19"/>
+      <c r="B45" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
         <v>27</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
         <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="14"/>
+      <c r="C46" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1903,15 +1909,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1967,47 +1973,47 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
         <v>2208</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
         <v>46204</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
         <v>46216</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
         <v>46234</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
         <v>9</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
         <v>15</v>
       </c>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC750C4C-79D7-4E6B-BBF7-4C0B88AF00E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A069EE-34A6-45D0-8C24-E4B02C703931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -413,14 +413,14 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -459,6 +459,7 @@
       <sheetName val="INVENTARIO NACIONAL 10-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 13-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 15-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -466,224 +467,224 @@
       <sheetData sheetId="2">
         <row r="3">
           <cell r="G3">
-            <v>190238</v>
+            <v>219422</v>
           </cell>
           <cell r="H3">
-            <v>188030</v>
+            <v>216761</v>
           </cell>
           <cell r="I3">
-            <v>21137.555555555555</v>
+            <v>21942.2</v>
           </cell>
           <cell r="J3">
-            <v>486163.77777777775</v>
+            <v>504670.60000000003</v>
           </cell>
           <cell r="K3">
             <v>696207</v>
           </cell>
           <cell r="L3">
-            <v>0.27324919169155149</v>
+            <v>0.31516775901420124</v>
           </cell>
           <cell r="M3">
-            <v>-505969</v>
+            <v>-476785</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>9430</v>
+            <v>10562</v>
           </cell>
           <cell r="D4">
-            <v>1047.7777777777778</v>
+            <v>1056.2</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>675</v>
+            <v>757</v>
           </cell>
           <cell r="D5">
-            <v>75</v>
+            <v>75.7</v>
           </cell>
           <cell r="G5">
-            <v>2208</v>
+            <v>2661</v>
           </cell>
           <cell r="H5">
             <v>46204</v>
           </cell>
           <cell r="I5">
-            <v>46216</v>
+            <v>46217</v>
           </cell>
           <cell r="J5">
             <v>46234</v>
           </cell>
           <cell r="K5">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="L5">
-            <v>15</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>4261</v>
+            <v>4701</v>
           </cell>
           <cell r="D6">
-            <v>473.44444444444446</v>
+            <v>470.1</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>797</v>
+            <v>947</v>
           </cell>
           <cell r="D7">
-            <v>88.555555555555557</v>
+            <v>94.7</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>139</v>
+            <v>164</v>
           </cell>
           <cell r="D8">
-            <v>15.444444444444445</v>
+            <v>16.399999999999999</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>10278</v>
+            <v>11437</v>
           </cell>
           <cell r="D9">
-            <v>1142</v>
+            <v>1143.7</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>913</v>
+            <v>1092</v>
           </cell>
           <cell r="D10">
-            <v>101.44444444444444</v>
+            <v>109.2</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>2314</v>
+            <v>2763</v>
           </cell>
           <cell r="D11">
-            <v>257.11111111111109</v>
+            <v>276.3</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>5040</v>
+            <v>5823</v>
           </cell>
           <cell r="D12">
-            <v>560</v>
+            <v>582.29999999999995</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>2933</v>
+            <v>3468</v>
           </cell>
           <cell r="D13">
-            <v>325.88888888888891</v>
+            <v>346.8</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>24613</v>
+            <v>28256</v>
           </cell>
           <cell r="D14">
-            <v>2734.7777777777778</v>
+            <v>2825.6</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>16778</v>
+            <v>19502</v>
           </cell>
           <cell r="D15">
-            <v>1864.2222222222222</v>
+            <v>1950.2</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>16429</v>
+            <v>18917</v>
           </cell>
           <cell r="D16">
-            <v>1825.4444444444443</v>
+            <v>1891.7</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>18000</v>
+            <v>21031</v>
           </cell>
           <cell r="D17">
-            <v>2000</v>
+            <v>2103.1</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>962</v>
+            <v>1132</v>
           </cell>
           <cell r="D18">
-            <v>106.88888888888889</v>
+            <v>113.2</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>1486</v>
+            <v>1803</v>
           </cell>
           <cell r="D19">
-            <v>165.11111111111111</v>
+            <v>180.3</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>1388</v>
+            <v>1536</v>
           </cell>
           <cell r="D20">
-            <v>154.22222222222223</v>
+            <v>153.6</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>3570</v>
+            <v>4366</v>
           </cell>
           <cell r="D21">
-            <v>396.66666666666669</v>
+            <v>436.6</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>5794</v>
+            <v>6641</v>
           </cell>
           <cell r="D22">
-            <v>643.77777777777783</v>
+            <v>664.1</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>101</v>
+            <v>103</v>
           </cell>
           <cell r="D23">
-            <v>11.222222222222221</v>
+            <v>10.3</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>250</v>
+            <v>600</v>
           </cell>
           <cell r="D24">
-            <v>27.777777777777779</v>
+            <v>60</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>5002</v>
+            <v>5651</v>
           </cell>
           <cell r="D25">
-            <v>555.77777777777783</v>
+            <v>565.1</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>8496</v>
+            <v>9440</v>
           </cell>
           <cell r="D26">
             <v>944</v>
@@ -691,154 +692,154 @@
         </row>
         <row r="27">
           <cell r="C27">
-            <v>3522</v>
+            <v>4184</v>
           </cell>
           <cell r="D27">
-            <v>391.33333333333331</v>
+            <v>418.4</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>2796</v>
+            <v>3276</v>
           </cell>
           <cell r="D28">
-            <v>310.66666666666669</v>
+            <v>327.60000000000002</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>896</v>
+            <v>1047</v>
           </cell>
           <cell r="D29">
-            <v>99.555555555555557</v>
+            <v>104.7</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>1016</v>
+            <v>1173</v>
           </cell>
           <cell r="D30">
-            <v>112.88888888888889</v>
+            <v>117.3</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>6357</v>
+            <v>7310</v>
           </cell>
           <cell r="D31">
-            <v>706.33333333333337</v>
+            <v>731</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>5281</v>
+            <v>6140</v>
           </cell>
           <cell r="D32">
-            <v>586.77777777777783</v>
+            <v>614</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>6877</v>
+            <v>7704</v>
           </cell>
           <cell r="D33">
-            <v>764.11111111111109</v>
+            <v>770.4</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>4558</v>
+            <v>5129</v>
           </cell>
           <cell r="D34">
-            <v>506.44444444444446</v>
+            <v>512.9</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>1695</v>
+            <v>1937</v>
           </cell>
           <cell r="D35">
-            <v>188.33333333333334</v>
+            <v>193.7</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>423</v>
+            <v>647</v>
           </cell>
           <cell r="D36">
-            <v>47</v>
+            <v>64.7</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>2888</v>
+            <v>3649</v>
           </cell>
           <cell r="D37">
-            <v>320.88888888888891</v>
+            <v>364.9</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>2023</v>
+            <v>2418</v>
           </cell>
           <cell r="D38">
-            <v>224.77777777777777</v>
+            <v>241.8</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>3800</v>
+            <v>4284</v>
           </cell>
           <cell r="D39">
-            <v>422.22222222222223</v>
+            <v>428.4</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>2062</v>
+            <v>2382</v>
           </cell>
           <cell r="D40">
-            <v>229.11111111111111</v>
+            <v>238.2</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>2484</v>
+            <v>2772</v>
           </cell>
           <cell r="D41">
-            <v>276</v>
+            <v>277.2</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>543</v>
+            <v>626</v>
           </cell>
           <cell r="D42">
-            <v>60.333333333333336</v>
+            <v>62.6</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>475</v>
+            <v>571</v>
           </cell>
           <cell r="D43">
-            <v>52.777777777777779</v>
+            <v>57.1</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>394</v>
+            <v>466</v>
           </cell>
           <cell r="D44">
-            <v>43.777777777777779</v>
+            <v>46.6</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>260</v>
+            <v>323</v>
           </cell>
           <cell r="D45">
-            <v>28.888888888888889</v>
+            <v>32.299999999999997</v>
           </cell>
         </row>
         <row r="46">
@@ -846,7 +847,7 @@
             <v>4</v>
           </cell>
           <cell r="D46">
-            <v>0.44444444444444442</v>
+            <v>0.4</v>
           </cell>
         </row>
         <row r="47">
@@ -854,7 +855,7 @@
             <v>27</v>
           </cell>
           <cell r="D47">
-            <v>3</v>
+            <v>2.7</v>
           </cell>
         </row>
       </sheetData>
@@ -867,6 +868,7 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1179,7 +1181,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1193,7 +1195,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
+      <c r="A2" s="18">
         <v>110150</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -1201,15 +1203,15 @@
       </c>
       <c r="C2" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>9430</v>
+        <v>10562</v>
       </c>
       <c r="D2" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1047.7777777777778</v>
+        <v>1056.2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
+      <c r="A3" s="18">
         <v>110151</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1217,15 +1219,15 @@
       </c>
       <c r="C3" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>675</v>
+        <v>757</v>
       </c>
       <c r="D3" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>75</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
+      <c r="A4" s="18">
         <v>110230</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -1233,15 +1235,15 @@
       </c>
       <c r="C4" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>4261</v>
+        <v>4701</v>
       </c>
       <c r="D4" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>473.44444444444446</v>
+        <v>470.1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
+      <c r="A5" s="18">
         <v>110400</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1249,15 +1251,15 @@
       </c>
       <c r="C5" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>797</v>
+        <v>947</v>
       </c>
       <c r="D5" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>88.555555555555557</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>111000</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1265,15 +1267,15 @@
       </c>
       <c r="C6" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="D6" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>15.444444444444445</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
+      <c r="A7" s="18">
         <v>120130</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -1281,15 +1283,15 @@
       </c>
       <c r="C7" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>10278</v>
+        <v>11437</v>
       </c>
       <c r="D7" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1142</v>
+        <v>1143.7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>120131</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -1297,15 +1299,15 @@
       </c>
       <c r="C8" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>913</v>
+        <v>1092</v>
       </c>
       <c r="D8" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>101.44444444444444</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>120132</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -1313,15 +1315,15 @@
       </c>
       <c r="C9" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>2314</v>
+        <v>2763</v>
       </c>
       <c r="D9" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>257.11111111111109</v>
+        <v>276.3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <v>130150</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -1329,15 +1331,15 @@
       </c>
       <c r="C10" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>5040</v>
+        <v>5823</v>
       </c>
       <c r="D10" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>560</v>
+        <v>582.29999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
+      <c r="A11" s="18">
         <v>130151</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -1345,15 +1347,15 @@
       </c>
       <c r="C11" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>2933</v>
+        <v>3468</v>
       </c>
       <c r="D11" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>325.88888888888891</v>
+        <v>346.8</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <v>130152</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -1361,15 +1363,15 @@
       </c>
       <c r="C12" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>24613</v>
+        <v>28256</v>
       </c>
       <c r="D12" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2734.7777777777778</v>
+        <v>2825.6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+      <c r="A13" s="18">
         <v>130153</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -1377,15 +1379,15 @@
       </c>
       <c r="C13" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>16778</v>
+        <v>19502</v>
       </c>
       <c r="D13" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1864.2222222222222</v>
+        <v>1950.2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <v>130154</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -1393,15 +1395,15 @@
       </c>
       <c r="C14" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>16429</v>
+        <v>18917</v>
       </c>
       <c r="D14" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1825.4444444444443</v>
+        <v>1891.7</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+      <c r="A15" s="18">
         <v>130155</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -1409,15 +1411,15 @@
       </c>
       <c r="C15" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>18000</v>
+        <v>21031</v>
       </c>
       <c r="D15" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2000</v>
+        <v>2103.1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+      <c r="A16" s="18">
         <v>130156</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -1425,15 +1427,15 @@
       </c>
       <c r="C16" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>962</v>
+        <v>1132</v>
       </c>
       <c r="D16" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>106.88888888888889</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
+      <c r="A17" s="18">
         <v>130700</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -1441,15 +1443,15 @@
       </c>
       <c r="C17" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>1486</v>
+        <v>1803</v>
       </c>
       <c r="D17" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>165.11111111111111</v>
+        <v>180.3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
+      <c r="A18" s="18">
         <v>130701</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -1457,15 +1459,15 @@
       </c>
       <c r="C18" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>1388</v>
+        <v>1536</v>
       </c>
       <c r="D18" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>154.22222222222223</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
+      <c r="A19" s="18">
         <v>130702</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -1473,15 +1475,15 @@
       </c>
       <c r="C19" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>3570</v>
+        <v>4366</v>
       </c>
       <c r="D19" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>396.66666666666669</v>
+        <v>436.6</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+      <c r="A20" s="18">
         <v>130703</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -1489,15 +1491,15 @@
       </c>
       <c r="C20" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>5794</v>
+        <v>6641</v>
       </c>
       <c r="D20" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>643.77777777777783</v>
+        <v>664.1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
+      <c r="A21" s="18">
         <v>130704</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -1505,15 +1507,15 @@
       </c>
       <c r="C21" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D21" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>11.222222222222221</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
+      <c r="A22" s="18">
         <v>130707</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -1521,15 +1523,15 @@
       </c>
       <c r="C22" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="D22" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>27.777777777777779</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
+      <c r="A23" s="18">
         <v>131150</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -1537,15 +1539,15 @@
       </c>
       <c r="C23" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>5002</v>
+        <v>5651</v>
       </c>
       <c r="D23" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>555.77777777777783</v>
+        <v>565.1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
+      <c r="A24" s="18">
         <v>131151</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -1553,7 +1555,7 @@
       </c>
       <c r="C24" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>8496</v>
+        <v>9440</v>
       </c>
       <c r="D24" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
@@ -1561,7 +1563,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
+      <c r="A25" s="18">
         <v>131152</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -1569,15 +1571,15 @@
       </c>
       <c r="C25" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>3522</v>
+        <v>4184</v>
       </c>
       <c r="D25" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>391.33333333333331</v>
+        <v>418.4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="19">
+      <c r="A26" s="18">
         <v>131153</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -1585,15 +1587,15 @@
       </c>
       <c r="C26" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>2796</v>
+        <v>3276</v>
       </c>
       <c r="D26" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>310.66666666666669</v>
+        <v>327.60000000000002</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="19">
+      <c r="A27" s="18">
         <v>131700</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -1601,15 +1603,15 @@
       </c>
       <c r="C27" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>896</v>
+        <v>1047</v>
       </c>
       <c r="D27" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>99.555555555555557</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="19">
+      <c r="A28" s="18">
         <v>131701</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -1617,15 +1619,15 @@
       </c>
       <c r="C28" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1016</v>
+        <v>1173</v>
       </c>
       <c r="D28" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>112.88888888888889</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="19">
+      <c r="A29" s="18">
         <v>132150</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -1633,15 +1635,15 @@
       </c>
       <c r="C29" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>6357</v>
+        <v>7310</v>
       </c>
       <c r="D29" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>706.33333333333337</v>
+        <v>731</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="19">
+      <c r="A30" s="18">
         <v>132151</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -1649,15 +1651,15 @@
       </c>
       <c r="C30" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>5281</v>
+        <v>6140</v>
       </c>
       <c r="D30" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>586.77777777777783</v>
+        <v>614</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="19">
+      <c r="A31" s="18">
         <v>132152</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -1665,15 +1667,15 @@
       </c>
       <c r="C31" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>6877</v>
+        <v>7704</v>
       </c>
       <c r="D31" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>764.11111111111109</v>
+        <v>770.4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="19">
+      <c r="A32" s="18">
         <v>132153</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -1681,15 +1683,15 @@
       </c>
       <c r="C32" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>4558</v>
+        <v>5129</v>
       </c>
       <c r="D32" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>506.44444444444446</v>
+        <v>512.9</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="19">
+      <c r="A33" s="18">
         <v>140230</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -1697,15 +1699,15 @@
       </c>
       <c r="C33" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>1695</v>
+        <v>1937</v>
       </c>
       <c r="D33" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>188.33333333333334</v>
+        <v>193.7</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="19">
+      <c r="A34" s="18">
         <v>140231</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -1713,15 +1715,15 @@
       </c>
       <c r="C34" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>423</v>
+        <v>647</v>
       </c>
       <c r="D34" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>47</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="19">
+      <c r="A35" s="18">
         <v>140232</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -1729,15 +1731,15 @@
       </c>
       <c r="C35" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>2888</v>
+        <v>3649</v>
       </c>
       <c r="D35" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>320.88888888888891</v>
+        <v>364.9</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
+      <c r="A36" s="18">
         <v>150360</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -1745,15 +1747,15 @@
       </c>
       <c r="C36" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>2023</v>
+        <v>2418</v>
       </c>
       <c r="D36" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>224.77777777777777</v>
+        <v>241.8</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="19">
+      <c r="A37" s="18">
         <v>150361</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -1761,15 +1763,15 @@
       </c>
       <c r="C37" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>3800</v>
+        <v>4284</v>
       </c>
       <c r="D37" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>422.22222222222223</v>
+        <v>428.4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="19">
+      <c r="A38" s="18">
         <v>150362</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -1777,15 +1779,15 @@
       </c>
       <c r="C38" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2062</v>
+        <v>2382</v>
       </c>
       <c r="D38" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>229.11111111111111</v>
+        <v>238.2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="19">
+      <c r="A39" s="18">
         <v>150363</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -1793,15 +1795,15 @@
       </c>
       <c r="C39" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2484</v>
+        <v>2772</v>
       </c>
       <c r="D39" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>276</v>
+        <v>277.2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="19">
+      <c r="A40" s="18">
         <v>151500</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -1809,15 +1811,15 @@
       </c>
       <c r="C40" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>543</v>
+        <v>626</v>
       </c>
       <c r="D40" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>60.333333333333336</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="19">
+      <c r="A41" s="18">
         <v>151501</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -1825,15 +1827,15 @@
       </c>
       <c r="C41" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>475</v>
+        <v>571</v>
       </c>
       <c r="D41" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>52.777777777777779</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="19">
+      <c r="A42" s="18">
         <v>151502</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -1841,15 +1843,15 @@
       </c>
       <c r="C42" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="D42" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>43.777777777777779</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="19">
+      <c r="A43" s="18">
         <v>151503</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -1857,15 +1859,15 @@
       </c>
       <c r="C43" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>260</v>
+        <v>323</v>
       </c>
       <c r="D43" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>28.888888888888889</v>
+        <v>32.299999999999997</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="19"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="8" t="s">
         <v>49</v>
       </c>
@@ -1875,11 +1877,11 @@
       </c>
       <c r="D44" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.44444444444444442</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="19"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="8" t="s">
         <v>50</v>
       </c>
@@ -1889,7 +1891,7 @@
       </c>
       <c r="D45" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1909,15 +1911,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1945,19 +1947,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>190238</v>
+        <v>219422</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>188030</v>
+        <v>216761</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>21137.555555555555</v>
+        <v>21942.2</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>486163.77777777775</v>
+        <v>504670.60000000003</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1965,11 +1967,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.27324919169155149</v>
+        <v>0.31516775901420124</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-505969</v>
+        <v>-476785</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1995,7 +1997,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2208</v>
+        <v>2661</v>
       </c>
       <c r="B5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2003,7 +2005,7 @@
       </c>
       <c r="C5" s="11">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="D5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2011,11 +2013,11 @@
       </c>
       <c r="E5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A069EE-34A6-45D0-8C24-E4B02C703931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3322B4-F09F-4FB2-9B36-B42AD5C332A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -460,6 +460,8 @@
       <sheetName val="INVENTARIO NACIONAL 13-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 15-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 16-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -467,203 +469,203 @@
       <sheetData sheetId="2">
         <row r="3">
           <cell r="G3">
-            <v>219422</v>
+            <v>267355</v>
           </cell>
           <cell r="H3">
-            <v>216761</v>
+            <v>265198</v>
           </cell>
           <cell r="I3">
-            <v>21942.2</v>
+            <v>22279.583333333332</v>
           </cell>
           <cell r="J3">
-            <v>504670.60000000003</v>
+            <v>512430.41666666663</v>
           </cell>
           <cell r="K3">
             <v>696207</v>
           </cell>
           <cell r="L3">
-            <v>0.31516775901420124</v>
+            <v>0.38401653531205515</v>
           </cell>
           <cell r="M3">
-            <v>-476785</v>
+            <v>-428852</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>10562</v>
+            <v>12546</v>
           </cell>
           <cell r="D4">
-            <v>1056.2</v>
+            <v>1045.5</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>757</v>
+            <v>870</v>
           </cell>
           <cell r="D5">
-            <v>75.7</v>
+            <v>72.5</v>
           </cell>
           <cell r="G5">
-            <v>2661</v>
+            <v>2157</v>
           </cell>
           <cell r="H5">
             <v>46204</v>
           </cell>
           <cell r="I5">
-            <v>46217</v>
+            <v>46219</v>
           </cell>
           <cell r="J5">
             <v>46234</v>
           </cell>
           <cell r="K5">
-            <v>10</v>
+            <v>12</v>
           </cell>
           <cell r="L5">
-            <v>14</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>4701</v>
+            <v>5725</v>
           </cell>
           <cell r="D6">
-            <v>470.1</v>
+            <v>477.08333333333331</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>947</v>
+            <v>1199</v>
           </cell>
           <cell r="D7">
-            <v>94.7</v>
+            <v>99.916666666666671</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>164</v>
+            <v>214</v>
           </cell>
           <cell r="D8">
-            <v>16.399999999999999</v>
+            <v>17.833333333333332</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>11437</v>
+            <v>13921</v>
           </cell>
           <cell r="D9">
-            <v>1143.7</v>
+            <v>1160.0833333333333</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>1092</v>
+            <v>1463</v>
           </cell>
           <cell r="D10">
-            <v>109.2</v>
+            <v>121.91666666666667</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>2763</v>
+            <v>3489</v>
           </cell>
           <cell r="D11">
-            <v>276.3</v>
+            <v>290.75</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>5823</v>
+            <v>7303</v>
           </cell>
           <cell r="D12">
-            <v>582.29999999999995</v>
+            <v>608.58333333333337</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>3468</v>
+            <v>4201</v>
           </cell>
           <cell r="D13">
-            <v>346.8</v>
+            <v>350.08333333333331</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>28256</v>
+            <v>34496</v>
           </cell>
           <cell r="D14">
-            <v>2825.6</v>
+            <v>2874.6666666666665</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>19502</v>
+            <v>23702</v>
           </cell>
           <cell r="D15">
-            <v>1950.2</v>
+            <v>1975.1666666666667</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>18917</v>
+            <v>22940</v>
           </cell>
           <cell r="D16">
-            <v>1891.7</v>
+            <v>1911.6666666666667</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>21031</v>
+            <v>25630</v>
           </cell>
           <cell r="D17">
-            <v>2103.1</v>
+            <v>2135.8333333333335</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>1132</v>
+            <v>1454</v>
           </cell>
           <cell r="D18">
-            <v>113.2</v>
+            <v>121.16666666666667</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>1803</v>
+            <v>2312</v>
           </cell>
           <cell r="D19">
-            <v>180.3</v>
+            <v>192.66666666666666</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>1536</v>
+            <v>1842</v>
           </cell>
           <cell r="D20">
-            <v>153.6</v>
+            <v>153.5</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>4366</v>
+            <v>5427</v>
           </cell>
           <cell r="D21">
-            <v>436.6</v>
+            <v>452.25</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>6641</v>
+            <v>9200</v>
           </cell>
           <cell r="D22">
-            <v>664.1</v>
+            <v>766.66666666666663</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>103</v>
+            <v>108</v>
           </cell>
           <cell r="D23">
-            <v>10.3</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="24">
@@ -671,191 +673,191 @@
             <v>600</v>
           </cell>
           <cell r="D24">
-            <v>60</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>5651</v>
+            <v>6876</v>
           </cell>
           <cell r="D25">
-            <v>565.1</v>
+            <v>573</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>9440</v>
+            <v>11388</v>
           </cell>
           <cell r="D26">
-            <v>944</v>
+            <v>949</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>4184</v>
+            <v>5168</v>
           </cell>
           <cell r="D27">
-            <v>418.4</v>
+            <v>430.66666666666669</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>3276</v>
+            <v>4121</v>
           </cell>
           <cell r="D28">
-            <v>327.60000000000002</v>
+            <v>343.41666666666669</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>1047</v>
+            <v>1289</v>
           </cell>
           <cell r="D29">
-            <v>104.7</v>
+            <v>107.41666666666667</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>1173</v>
+            <v>1342</v>
           </cell>
           <cell r="D30">
-            <v>117.3</v>
+            <v>111.83333333333333</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>7310</v>
+            <v>8973</v>
           </cell>
           <cell r="D31">
-            <v>731</v>
+            <v>747.75</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>6140</v>
+            <v>7541</v>
           </cell>
           <cell r="D32">
-            <v>614</v>
+            <v>628.41666666666663</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>7704</v>
+            <v>9578</v>
           </cell>
           <cell r="D33">
-            <v>770.4</v>
+            <v>798.16666666666663</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>5129</v>
+            <v>6303</v>
           </cell>
           <cell r="D34">
-            <v>512.9</v>
+            <v>525.25</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>1937</v>
+            <v>2462</v>
           </cell>
           <cell r="D35">
-            <v>193.7</v>
+            <v>205.16666666666666</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>647</v>
+            <v>702</v>
           </cell>
           <cell r="D36">
-            <v>64.7</v>
+            <v>58.5</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>3649</v>
+            <v>4291</v>
           </cell>
           <cell r="D37">
-            <v>364.9</v>
+            <v>357.58333333333331</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>2418</v>
+            <v>2994</v>
           </cell>
           <cell r="D38">
-            <v>241.8</v>
+            <v>249.5</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>4284</v>
+            <v>4975</v>
           </cell>
           <cell r="D39">
-            <v>428.4</v>
+            <v>414.58333333333331</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>2382</v>
+            <v>2819</v>
           </cell>
           <cell r="D40">
-            <v>238.2</v>
+            <v>234.91666666666666</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>2772</v>
+            <v>3303</v>
           </cell>
           <cell r="D41">
-            <v>277.2</v>
+            <v>275.25</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>626</v>
+            <v>705</v>
           </cell>
           <cell r="D42">
-            <v>62.6</v>
+            <v>58.75</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>571</v>
+            <v>769</v>
           </cell>
           <cell r="D43">
-            <v>57.1</v>
+            <v>64.083333333333329</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>466</v>
+            <v>523</v>
           </cell>
           <cell r="D44">
-            <v>46.6</v>
+            <v>43.583333333333336</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>323</v>
+            <v>389</v>
           </cell>
           <cell r="D45">
-            <v>32.299999999999997</v>
+            <v>32.416666666666664</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>4</v>
+            <v>9</v>
           </cell>
           <cell r="D46">
-            <v>0.4</v>
+            <v>0.75</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>27</v>
+            <v>36</v>
           </cell>
           <cell r="D47">
-            <v>2.7</v>
+            <v>3</v>
           </cell>
         </row>
       </sheetData>
@@ -869,6 +871,8 @@
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1203,11 +1207,11 @@
       </c>
       <c r="C2" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>10562</v>
+        <v>12546</v>
       </c>
       <c r="D2" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1056.2</v>
+        <v>1045.5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1219,11 +1223,11 @@
       </c>
       <c r="C3" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>757</v>
+        <v>870</v>
       </c>
       <c r="D3" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>75.7</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1235,11 +1239,11 @@
       </c>
       <c r="C4" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>4701</v>
+        <v>5725</v>
       </c>
       <c r="D4" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>470.1</v>
+        <v>477.08333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1251,11 +1255,11 @@
       </c>
       <c r="C5" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>947</v>
+        <v>1199</v>
       </c>
       <c r="D5" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>94.7</v>
+        <v>99.916666666666671</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1267,11 +1271,11 @@
       </c>
       <c r="C6" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="D6" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>16.399999999999999</v>
+        <v>17.833333333333332</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,11 +1287,11 @@
       </c>
       <c r="C7" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>11437</v>
+        <v>13921</v>
       </c>
       <c r="D7" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1143.7</v>
+        <v>1160.0833333333333</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1299,11 +1303,11 @@
       </c>
       <c r="C8" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1092</v>
+        <v>1463</v>
       </c>
       <c r="D8" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>109.2</v>
+        <v>121.91666666666667</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1315,11 +1319,11 @@
       </c>
       <c r="C9" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>2763</v>
+        <v>3489</v>
       </c>
       <c r="D9" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>276.3</v>
+        <v>290.75</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,11 +1335,11 @@
       </c>
       <c r="C10" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>5823</v>
+        <v>7303</v>
       </c>
       <c r="D10" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>582.29999999999995</v>
+        <v>608.58333333333337</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1347,11 +1351,11 @@
       </c>
       <c r="C11" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>3468</v>
+        <v>4201</v>
       </c>
       <c r="D11" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>346.8</v>
+        <v>350.08333333333331</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1363,11 +1367,11 @@
       </c>
       <c r="C12" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>28256</v>
+        <v>34496</v>
       </c>
       <c r="D12" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2825.6</v>
+        <v>2874.6666666666665</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,11 +1383,11 @@
       </c>
       <c r="C13" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>19502</v>
+        <v>23702</v>
       </c>
       <c r="D13" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1950.2</v>
+        <v>1975.1666666666667</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1395,11 +1399,11 @@
       </c>
       <c r="C14" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>18917</v>
+        <v>22940</v>
       </c>
       <c r="D14" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1891.7</v>
+        <v>1911.6666666666667</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1411,11 +1415,11 @@
       </c>
       <c r="C15" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>21031</v>
+        <v>25630</v>
       </c>
       <c r="D15" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2103.1</v>
+        <v>2135.8333333333335</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1427,11 +1431,11 @@
       </c>
       <c r="C16" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>1132</v>
+        <v>1454</v>
       </c>
       <c r="D16" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>113.2</v>
+        <v>121.16666666666667</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1443,11 +1447,11 @@
       </c>
       <c r="C17" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>1803</v>
+        <v>2312</v>
       </c>
       <c r="D17" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>180.3</v>
+        <v>192.66666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1459,11 +1463,11 @@
       </c>
       <c r="C18" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>1536</v>
+        <v>1842</v>
       </c>
       <c r="D18" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>153.6</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1475,11 +1479,11 @@
       </c>
       <c r="C19" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>4366</v>
+        <v>5427</v>
       </c>
       <c r="D19" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>436.6</v>
+        <v>452.25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,11 +1495,11 @@
       </c>
       <c r="C20" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>6641</v>
+        <v>9200</v>
       </c>
       <c r="D20" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>664.1</v>
+        <v>766.66666666666663</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1507,11 +1511,11 @@
       </c>
       <c r="C21" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D21" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>10.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="D22" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1539,11 +1543,11 @@
       </c>
       <c r="C23" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>5651</v>
+        <v>6876</v>
       </c>
       <c r="D23" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>565.1</v>
+        <v>573</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,11 +1559,11 @@
       </c>
       <c r="C24" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>9440</v>
+        <v>11388</v>
       </c>
       <c r="D24" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1571,11 +1575,11 @@
       </c>
       <c r="C25" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>4184</v>
+        <v>5168</v>
       </c>
       <c r="D25" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>418.4</v>
+        <v>430.66666666666669</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1587,11 +1591,11 @@
       </c>
       <c r="C26" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>3276</v>
+        <v>4121</v>
       </c>
       <c r="D26" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>327.60000000000002</v>
+        <v>343.41666666666669</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1603,11 +1607,11 @@
       </c>
       <c r="C27" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1047</v>
+        <v>1289</v>
       </c>
       <c r="D27" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>104.7</v>
+        <v>107.41666666666667</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1619,11 +1623,11 @@
       </c>
       <c r="C28" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1173</v>
+        <v>1342</v>
       </c>
       <c r="D28" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>117.3</v>
+        <v>111.83333333333333</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1635,11 +1639,11 @@
       </c>
       <c r="C29" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>7310</v>
+        <v>8973</v>
       </c>
       <c r="D29" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>731</v>
+        <v>747.75</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,11 +1655,11 @@
       </c>
       <c r="C30" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>6140</v>
+        <v>7541</v>
       </c>
       <c r="D30" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>614</v>
+        <v>628.41666666666663</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1667,11 +1671,11 @@
       </c>
       <c r="C31" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>7704</v>
+        <v>9578</v>
       </c>
       <c r="D31" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>770.4</v>
+        <v>798.16666666666663</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1683,11 +1687,11 @@
       </c>
       <c r="C32" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>5129</v>
+        <v>6303</v>
       </c>
       <c r="D32" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>512.9</v>
+        <v>525.25</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1699,11 +1703,11 @@
       </c>
       <c r="C33" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>1937</v>
+        <v>2462</v>
       </c>
       <c r="D33" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>193.7</v>
+        <v>205.16666666666666</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1715,11 +1719,11 @@
       </c>
       <c r="C34" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>647</v>
+        <v>702</v>
       </c>
       <c r="D34" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>64.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1731,11 +1735,11 @@
       </c>
       <c r="C35" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>3649</v>
+        <v>4291</v>
       </c>
       <c r="D35" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>364.9</v>
+        <v>357.58333333333331</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1747,11 +1751,11 @@
       </c>
       <c r="C36" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>2418</v>
+        <v>2994</v>
       </c>
       <c r="D36" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>241.8</v>
+        <v>249.5</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1763,11 +1767,11 @@
       </c>
       <c r="C37" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>4284</v>
+        <v>4975</v>
       </c>
       <c r="D37" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>428.4</v>
+        <v>414.58333333333331</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1779,11 +1783,11 @@
       </c>
       <c r="C38" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2382</v>
+        <v>2819</v>
       </c>
       <c r="D38" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>238.2</v>
+        <v>234.91666666666666</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1795,11 +1799,11 @@
       </c>
       <c r="C39" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2772</v>
+        <v>3303</v>
       </c>
       <c r="D39" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>277.2</v>
+        <v>275.25</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1811,11 +1815,11 @@
       </c>
       <c r="C40" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>626</v>
+        <v>705</v>
       </c>
       <c r="D40" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>62.6</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1827,11 +1831,11 @@
       </c>
       <c r="C41" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>571</v>
+        <v>769</v>
       </c>
       <c r="D41" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>57.1</v>
+        <v>64.083333333333329</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1843,11 +1847,11 @@
       </c>
       <c r="C42" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>466</v>
+        <v>523</v>
       </c>
       <c r="D42" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>46.6</v>
+        <v>43.583333333333336</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1859,11 +1863,11 @@
       </c>
       <c r="C43" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>323</v>
+        <v>389</v>
       </c>
       <c r="D43" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>32.299999999999997</v>
+        <v>32.416666666666664</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1873,11 +1877,11 @@
       </c>
       <c r="C44" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D44" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1887,11 +1891,11 @@
       </c>
       <c r="C45" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D45" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,19 +1951,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>219422</v>
+        <v>267355</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>216761</v>
+        <v>265198</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>21942.2</v>
+        <v>22279.583333333332</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>504670.60000000003</v>
+        <v>512430.41666666663</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1967,11 +1971,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.31516775901420124</v>
+        <v>0.38401653531205515</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-476785</v>
+        <v>-428852</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1997,7 +2001,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2661</v>
+        <v>2157</v>
       </c>
       <c r="B5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2005,7 +2009,7 @@
       </c>
       <c r="C5" s="11">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="D5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2013,11 +2017,11 @@
       </c>
       <c r="E5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3322B4-F09F-4FB2-9B36-B42AD5C332A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4DE850-9512-4C2A-BB20-782C69E68D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -462,6 +462,9 @@
       <sheetName val="INVENTARIO NACIONAL 15-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 16-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 21-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 22-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -469,379 +472,379 @@
       <sheetData sheetId="2">
         <row r="3">
           <cell r="G3">
-            <v>267355</v>
+            <v>340311</v>
           </cell>
           <cell r="H3">
-            <v>265198</v>
+            <v>337483</v>
           </cell>
           <cell r="I3">
-            <v>22279.583333333332</v>
+            <v>22687.4</v>
           </cell>
           <cell r="J3">
-            <v>512430.41666666663</v>
+            <v>499122.80000000005</v>
           </cell>
           <cell r="K3">
             <v>696207</v>
           </cell>
           <cell r="L3">
-            <v>0.38401653531205515</v>
+            <v>0.4888072082010092</v>
           </cell>
           <cell r="M3">
-            <v>-428852</v>
+            <v>-355896</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>12546</v>
+            <v>15803</v>
           </cell>
           <cell r="D4">
-            <v>1045.5</v>
+            <v>1053.5333333333333</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>870</v>
+            <v>1084</v>
           </cell>
           <cell r="D5">
-            <v>72.5</v>
+            <v>72.266666666666666</v>
           </cell>
           <cell r="G5">
-            <v>2157</v>
+            <v>2828</v>
           </cell>
           <cell r="H5">
             <v>46204</v>
           </cell>
           <cell r="I5">
-            <v>46219</v>
+            <v>46224</v>
           </cell>
           <cell r="J5">
             <v>46234</v>
           </cell>
           <cell r="K5">
-            <v>12</v>
+            <v>15</v>
           </cell>
           <cell r="L5">
-            <v>11</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>5725</v>
+            <v>7353</v>
           </cell>
           <cell r="D6">
-            <v>477.08333333333331</v>
+            <v>490.2</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1199</v>
+            <v>1437</v>
           </cell>
           <cell r="D7">
-            <v>99.916666666666671</v>
+            <v>95.8</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>214</v>
+            <v>247</v>
           </cell>
           <cell r="D8">
-            <v>17.833333333333332</v>
+            <v>16.466666666666665</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>13921</v>
+            <v>17995</v>
           </cell>
           <cell r="D9">
-            <v>1160.0833333333333</v>
+            <v>1199.6666666666667</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>1463</v>
+            <v>1690</v>
           </cell>
           <cell r="D10">
-            <v>121.91666666666667</v>
+            <v>112.66666666666667</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>3489</v>
+            <v>4065</v>
           </cell>
           <cell r="D11">
-            <v>290.75</v>
+            <v>271</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>7303</v>
+            <v>9170</v>
           </cell>
           <cell r="D12">
-            <v>608.58333333333337</v>
+            <v>611.33333333333337</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>4201</v>
+            <v>5243</v>
           </cell>
           <cell r="D13">
-            <v>350.08333333333331</v>
+            <v>349.53333333333336</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>34496</v>
+            <v>44494</v>
           </cell>
           <cell r="D14">
-            <v>2874.6666666666665</v>
+            <v>2966.2666666666669</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>23702</v>
+            <v>30091</v>
           </cell>
           <cell r="D15">
-            <v>1975.1666666666667</v>
+            <v>2006.0666666666666</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>22940</v>
+            <v>29646</v>
           </cell>
           <cell r="D16">
-            <v>1911.6666666666667</v>
+            <v>1976.4</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>25630</v>
+            <v>33033</v>
           </cell>
           <cell r="D17">
-            <v>2135.8333333333335</v>
+            <v>2202.1999999999998</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>1454</v>
+            <v>1975</v>
           </cell>
           <cell r="D18">
-            <v>121.16666666666667</v>
+            <v>131.66666666666666</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>2312</v>
+            <v>2885</v>
           </cell>
           <cell r="D19">
-            <v>192.66666666666666</v>
+            <v>192.33333333333334</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>1842</v>
+            <v>2203</v>
           </cell>
           <cell r="D20">
-            <v>153.5</v>
+            <v>146.86666666666667</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>5427</v>
+            <v>6788</v>
           </cell>
           <cell r="D21">
-            <v>452.25</v>
+            <v>452.53333333333336</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>9200</v>
+            <v>11461</v>
           </cell>
           <cell r="D22">
-            <v>766.66666666666663</v>
+            <v>764.06666666666672</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>108</v>
+            <v>110</v>
           </cell>
           <cell r="D23">
-            <v>9</v>
+            <v>7.333333333333333</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>600</v>
+            <v>870</v>
           </cell>
           <cell r="D24">
-            <v>50</v>
+            <v>58</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>6876</v>
+            <v>9196</v>
           </cell>
           <cell r="D25">
-            <v>573</v>
+            <v>613.06666666666672</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>11388</v>
+            <v>14865</v>
           </cell>
           <cell r="D26">
-            <v>949</v>
+            <v>991</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>5168</v>
+            <v>6594</v>
           </cell>
           <cell r="D27">
-            <v>430.66666666666669</v>
+            <v>439.6</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>4121</v>
+            <v>5181</v>
           </cell>
           <cell r="D28">
-            <v>343.41666666666669</v>
+            <v>345.4</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>1289</v>
+            <v>1571</v>
           </cell>
           <cell r="D29">
-            <v>107.41666666666667</v>
+            <v>104.73333333333333</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>1342</v>
+            <v>1668</v>
           </cell>
           <cell r="D30">
-            <v>111.83333333333333</v>
+            <v>111.2</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>8973</v>
+            <v>10991</v>
           </cell>
           <cell r="D31">
-            <v>747.75</v>
+            <v>732.73333333333335</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>7541</v>
+            <v>9248</v>
           </cell>
           <cell r="D32">
-            <v>628.41666666666663</v>
+            <v>616.5333333333333</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>9578</v>
+            <v>11635</v>
           </cell>
           <cell r="D33">
-            <v>798.16666666666663</v>
+            <v>775.66666666666663</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>6303</v>
+            <v>7791</v>
           </cell>
           <cell r="D34">
-            <v>525.25</v>
+            <v>519.4</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>2462</v>
+            <v>2991</v>
           </cell>
           <cell r="D35">
-            <v>205.16666666666666</v>
+            <v>199.4</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>702</v>
+            <v>2162</v>
           </cell>
           <cell r="D36">
-            <v>58.5</v>
+            <v>144.13333333333333</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>4291</v>
+            <v>5325</v>
           </cell>
           <cell r="D37">
-            <v>357.58333333333331</v>
+            <v>355</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>2994</v>
+            <v>4118</v>
           </cell>
           <cell r="D38">
-            <v>249.5</v>
+            <v>274.53333333333336</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>4975</v>
+            <v>5820</v>
           </cell>
           <cell r="D39">
-            <v>414.58333333333331</v>
+            <v>388</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>2819</v>
+            <v>3581</v>
           </cell>
           <cell r="D40">
-            <v>234.91666666666666</v>
+            <v>238.73333333333332</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>3303</v>
+            <v>3818</v>
           </cell>
           <cell r="D41">
-            <v>275.25</v>
+            <v>254.53333333333333</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>705</v>
+            <v>753</v>
           </cell>
           <cell r="D42">
-            <v>58.75</v>
+            <v>50.2</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>769</v>
+            <v>1267</v>
           </cell>
           <cell r="D43">
-            <v>64.083333333333329</v>
+            <v>84.466666666666669</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>523</v>
+            <v>547</v>
           </cell>
           <cell r="D44">
-            <v>43.583333333333336</v>
+            <v>36.466666666666669</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>389</v>
+            <v>661</v>
           </cell>
           <cell r="D45">
-            <v>32.416666666666664</v>
+            <v>44.06666666666667</v>
           </cell>
         </row>
         <row r="46">
@@ -849,15 +852,15 @@
             <v>9</v>
           </cell>
           <cell r="D46">
-            <v>0.75</v>
+            <v>0.6</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>36</v>
+            <v>48</v>
           </cell>
           <cell r="D47">
-            <v>3</v>
+            <v>3.2</v>
           </cell>
         </row>
       </sheetData>
@@ -873,6 +876,9 @@
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1207,11 +1213,11 @@
       </c>
       <c r="C2" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>12546</v>
+        <v>15803</v>
       </c>
       <c r="D2" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1045.5</v>
+        <v>1053.5333333333333</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1223,11 +1229,11 @@
       </c>
       <c r="C3" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>870</v>
+        <v>1084</v>
       </c>
       <c r="D3" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>72.5</v>
+        <v>72.266666666666666</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1239,11 +1245,11 @@
       </c>
       <c r="C4" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>5725</v>
+        <v>7353</v>
       </c>
       <c r="D4" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>477.08333333333331</v>
+        <v>490.2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1255,11 +1261,11 @@
       </c>
       <c r="C5" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1199</v>
+        <v>1437</v>
       </c>
       <c r="D5" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>99.916666666666671</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1271,11 +1277,11 @@
       </c>
       <c r="C6" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="D6" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>17.833333333333332</v>
+        <v>16.466666666666665</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1287,11 +1293,11 @@
       </c>
       <c r="C7" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>13921</v>
+        <v>17995</v>
       </c>
       <c r="D7" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1160.0833333333333</v>
+        <v>1199.6666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1303,11 +1309,11 @@
       </c>
       <c r="C8" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1463</v>
+        <v>1690</v>
       </c>
       <c r="D8" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>121.91666666666667</v>
+        <v>112.66666666666667</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1319,11 +1325,11 @@
       </c>
       <c r="C9" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>3489</v>
+        <v>4065</v>
       </c>
       <c r="D9" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>290.75</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1335,11 +1341,11 @@
       </c>
       <c r="C10" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>7303</v>
+        <v>9170</v>
       </c>
       <c r="D10" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>608.58333333333337</v>
+        <v>611.33333333333337</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1351,11 +1357,11 @@
       </c>
       <c r="C11" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>4201</v>
+        <v>5243</v>
       </c>
       <c r="D11" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>350.08333333333331</v>
+        <v>349.53333333333336</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1367,11 +1373,11 @@
       </c>
       <c r="C12" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>34496</v>
+        <v>44494</v>
       </c>
       <c r="D12" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2874.6666666666665</v>
+        <v>2966.2666666666669</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1383,11 +1389,11 @@
       </c>
       <c r="C13" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>23702</v>
+        <v>30091</v>
       </c>
       <c r="D13" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1975.1666666666667</v>
+        <v>2006.0666666666666</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1399,11 +1405,11 @@
       </c>
       <c r="C14" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>22940</v>
+        <v>29646</v>
       </c>
       <c r="D14" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1911.6666666666667</v>
+        <v>1976.4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,11 +1421,11 @@
       </c>
       <c r="C15" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>25630</v>
+        <v>33033</v>
       </c>
       <c r="D15" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2135.8333333333335</v>
+        <v>2202.1999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1431,11 +1437,11 @@
       </c>
       <c r="C16" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>1454</v>
+        <v>1975</v>
       </c>
       <c r="D16" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>121.16666666666667</v>
+        <v>131.66666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1447,11 +1453,11 @@
       </c>
       <c r="C17" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>2312</v>
+        <v>2885</v>
       </c>
       <c r="D17" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>192.66666666666666</v>
+        <v>192.33333333333334</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,11 +1469,11 @@
       </c>
       <c r="C18" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>1842</v>
+        <v>2203</v>
       </c>
       <c r="D18" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>153.5</v>
+        <v>146.86666666666667</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1479,11 +1485,11 @@
       </c>
       <c r="C19" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>5427</v>
+        <v>6788</v>
       </c>
       <c r="D19" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>452.25</v>
+        <v>452.53333333333336</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1495,11 +1501,11 @@
       </c>
       <c r="C20" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>9200</v>
+        <v>11461</v>
       </c>
       <c r="D20" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>766.66666666666663</v>
+        <v>764.06666666666672</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1511,11 +1517,11 @@
       </c>
       <c r="C21" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D21" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>9</v>
+        <v>7.333333333333333</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,11 +1533,11 @@
       </c>
       <c r="C22" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>600</v>
+        <v>870</v>
       </c>
       <c r="D22" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1543,11 +1549,11 @@
       </c>
       <c r="C23" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>6876</v>
+        <v>9196</v>
       </c>
       <c r="D23" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>573</v>
+        <v>613.06666666666672</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1559,11 +1565,11 @@
       </c>
       <c r="C24" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>11388</v>
+        <v>14865</v>
       </c>
       <c r="D24" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>949</v>
+        <v>991</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1575,11 +1581,11 @@
       </c>
       <c r="C25" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>5168</v>
+        <v>6594</v>
       </c>
       <c r="D25" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>430.66666666666669</v>
+        <v>439.6</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1591,11 +1597,11 @@
       </c>
       <c r="C26" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>4121</v>
+        <v>5181</v>
       </c>
       <c r="D26" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>343.41666666666669</v>
+        <v>345.4</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1607,11 +1613,11 @@
       </c>
       <c r="C27" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1289</v>
+        <v>1571</v>
       </c>
       <c r="D27" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>107.41666666666667</v>
+        <v>104.73333333333333</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1623,11 +1629,11 @@
       </c>
       <c r="C28" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1342</v>
+        <v>1668</v>
       </c>
       <c r="D28" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>111.83333333333333</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1639,11 +1645,11 @@
       </c>
       <c r="C29" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>8973</v>
+        <v>10991</v>
       </c>
       <c r="D29" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>747.75</v>
+        <v>732.73333333333335</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1655,11 +1661,11 @@
       </c>
       <c r="C30" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>7541</v>
+        <v>9248</v>
       </c>
       <c r="D30" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>628.41666666666663</v>
+        <v>616.5333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1671,11 +1677,11 @@
       </c>
       <c r="C31" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>9578</v>
+        <v>11635</v>
       </c>
       <c r="D31" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>798.16666666666663</v>
+        <v>775.66666666666663</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1687,11 +1693,11 @@
       </c>
       <c r="C32" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>6303</v>
+        <v>7791</v>
       </c>
       <c r="D32" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>525.25</v>
+        <v>519.4</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1703,11 +1709,11 @@
       </c>
       <c r="C33" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>2462</v>
+        <v>2991</v>
       </c>
       <c r="D33" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>205.16666666666666</v>
+        <v>199.4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1719,11 +1725,11 @@
       </c>
       <c r="C34" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>702</v>
+        <v>2162</v>
       </c>
       <c r="D34" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>58.5</v>
+        <v>144.13333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1735,11 +1741,11 @@
       </c>
       <c r="C35" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>4291</v>
+        <v>5325</v>
       </c>
       <c r="D35" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>357.58333333333331</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1751,11 +1757,11 @@
       </c>
       <c r="C36" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>2994</v>
+        <v>4118</v>
       </c>
       <c r="D36" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>249.5</v>
+        <v>274.53333333333336</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1767,11 +1773,11 @@
       </c>
       <c r="C37" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>4975</v>
+        <v>5820</v>
       </c>
       <c r="D37" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>414.58333333333331</v>
+        <v>388</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1783,11 +1789,11 @@
       </c>
       <c r="C38" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>2819</v>
+        <v>3581</v>
       </c>
       <c r="D38" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>234.91666666666666</v>
+        <v>238.73333333333332</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1799,11 +1805,11 @@
       </c>
       <c r="C39" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>3303</v>
+        <v>3818</v>
       </c>
       <c r="D39" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>275.25</v>
+        <v>254.53333333333333</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1815,11 +1821,11 @@
       </c>
       <c r="C40" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>705</v>
+        <v>753</v>
       </c>
       <c r="D40" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>58.75</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1831,11 +1837,11 @@
       </c>
       <c r="C41" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>769</v>
+        <v>1267</v>
       </c>
       <c r="D41" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>64.083333333333329</v>
+        <v>84.466666666666669</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1847,11 +1853,11 @@
       </c>
       <c r="C42" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="D42" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>43.583333333333336</v>
+        <v>36.466666666666669</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1863,11 +1869,11 @@
       </c>
       <c r="C43" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>389</v>
+        <v>661</v>
       </c>
       <c r="D43" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>32.416666666666664</v>
+        <v>44.06666666666667</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1881,7 +1887,7 @@
       </c>
       <c r="D44" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1891,11 +1897,11 @@
       </c>
       <c r="C45" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D45" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1951,19 +1957,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>267355</v>
+        <v>340311</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>265198</v>
+        <v>337483</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>22279.583333333332</v>
+        <v>22687.4</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>512430.41666666663</v>
+        <v>499122.80000000005</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1971,11 +1977,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.38401653531205515</v>
+        <v>0.4888072082010092</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-428852</v>
+        <v>-355896</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2001,7 +2007,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2157</v>
+        <v>2828</v>
       </c>
       <c r="B5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2009,7 +2015,7 @@
       </c>
       <c r="C5" s="11">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="D5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2017,11 +2023,11 @@
       </c>
       <c r="E5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4DE850-9512-4C2A-BB20-782C69E68D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2BE1FA-F36A-4353-B525-B48F9416D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2BE1FA-F36A-4353-B525-B48F9416D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00126FDE-2BF8-40D2-B20B-4425A532FD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -465,6 +465,8 @@
       <sheetName val="INVENTARIO NACIONAL 20-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 21-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 22-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 23-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -472,195 +474,195 @@
       <sheetData sheetId="2">
         <row r="3">
           <cell r="G3">
-            <v>340311</v>
+            <v>415844</v>
           </cell>
           <cell r="H3">
-            <v>337483</v>
+            <v>410956</v>
           </cell>
           <cell r="I3">
-            <v>22687.4</v>
+            <v>24461.411764705881</v>
           </cell>
           <cell r="J3">
-            <v>499122.80000000005</v>
+            <v>538151.0588235294</v>
           </cell>
           <cell r="K3">
             <v>696207</v>
           </cell>
           <cell r="L3">
-            <v>0.4888072082010092</v>
+            <v>0.59729936642406645</v>
           </cell>
           <cell r="M3">
-            <v>-355896</v>
+            <v>-280363</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>15803</v>
+            <v>19244</v>
           </cell>
           <cell r="D4">
-            <v>1053.5333333333333</v>
+            <v>1132</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1084</v>
+            <v>1282</v>
           </cell>
           <cell r="D5">
-            <v>72.266666666666666</v>
+            <v>75.411764705882348</v>
           </cell>
           <cell r="G5">
-            <v>2828</v>
+            <v>4888</v>
           </cell>
           <cell r="H5">
             <v>46204</v>
           </cell>
           <cell r="I5">
-            <v>46224</v>
+            <v>46229</v>
           </cell>
           <cell r="J5">
             <v>46234</v>
           </cell>
           <cell r="K5">
-            <v>15</v>
+            <v>17</v>
           </cell>
           <cell r="L5">
-            <v>7</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>7353</v>
+            <v>9264</v>
           </cell>
           <cell r="D6">
-            <v>490.2</v>
+            <v>544.94117647058829</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1437</v>
+            <v>1661</v>
           </cell>
           <cell r="D7">
-            <v>95.8</v>
+            <v>97.705882352941174</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>247</v>
+            <v>289</v>
           </cell>
           <cell r="D8">
-            <v>16.466666666666665</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>17995</v>
+            <v>21428</v>
           </cell>
           <cell r="D9">
-            <v>1199.6666666666667</v>
+            <v>1260.4705882352941</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>1690</v>
+            <v>2017</v>
           </cell>
           <cell r="D10">
-            <v>112.66666666666667</v>
+            <v>118.64705882352941</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>4065</v>
+            <v>4806</v>
           </cell>
           <cell r="D11">
-            <v>271</v>
+            <v>282.70588235294116</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>9170</v>
+            <v>10925</v>
           </cell>
           <cell r="D12">
-            <v>611.33333333333337</v>
+            <v>642.64705882352939</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>5243</v>
+            <v>6325</v>
           </cell>
           <cell r="D13">
-            <v>349.53333333333336</v>
+            <v>372.05882352941177</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>44494</v>
+            <v>54660</v>
           </cell>
           <cell r="D14">
-            <v>2966.2666666666669</v>
+            <v>3215.294117647059</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>30091</v>
+            <v>36825</v>
           </cell>
           <cell r="D15">
-            <v>2006.0666666666666</v>
+            <v>2166.1764705882351</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>29646</v>
+            <v>36606</v>
           </cell>
           <cell r="D16">
-            <v>1976.4</v>
+            <v>2153.294117647059</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>33033</v>
+            <v>40543</v>
           </cell>
           <cell r="D17">
-            <v>2202.1999999999998</v>
+            <v>2384.8823529411766</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>1975</v>
+            <v>2281</v>
           </cell>
           <cell r="D18">
-            <v>131.66666666666666</v>
+            <v>134.1764705882353</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>2885</v>
+            <v>3613</v>
           </cell>
           <cell r="D19">
-            <v>192.33333333333334</v>
+            <v>212.52941176470588</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>2203</v>
+            <v>2646</v>
           </cell>
           <cell r="D20">
-            <v>146.86666666666667</v>
+            <v>155.64705882352942</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>6788</v>
+            <v>8211</v>
           </cell>
           <cell r="D21">
-            <v>452.53333333333336</v>
+            <v>483</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>11461</v>
+            <v>13716</v>
           </cell>
           <cell r="D22">
-            <v>764.06666666666672</v>
+            <v>806.82352941176475</v>
           </cell>
         </row>
         <row r="23">
@@ -668,199 +670,199 @@
             <v>110</v>
           </cell>
           <cell r="D23">
-            <v>7.333333333333333</v>
+            <v>6.4705882352941178</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>870</v>
+            <v>890</v>
           </cell>
           <cell r="D24">
-            <v>58</v>
+            <v>52.352941176470587</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>9196</v>
+            <v>11866</v>
           </cell>
           <cell r="D25">
-            <v>613.06666666666672</v>
+            <v>698</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>14865</v>
+            <v>18440</v>
           </cell>
           <cell r="D26">
-            <v>991</v>
+            <v>1084.7058823529412</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>6594</v>
+            <v>8047</v>
           </cell>
           <cell r="D27">
-            <v>439.6</v>
+            <v>473.35294117647061</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>5181</v>
+            <v>6254</v>
           </cell>
           <cell r="D28">
-            <v>345.4</v>
+            <v>367.88235294117646</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>1571</v>
+            <v>1841</v>
           </cell>
           <cell r="D29">
-            <v>104.73333333333333</v>
+            <v>108.29411764705883</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>1668</v>
+            <v>2009</v>
           </cell>
           <cell r="D30">
-            <v>111.2</v>
+            <v>118.17647058823529</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>10991</v>
+            <v>13571</v>
           </cell>
           <cell r="D31">
-            <v>732.73333333333335</v>
+            <v>798.29411764705878</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>9248</v>
+            <v>11386</v>
           </cell>
           <cell r="D32">
-            <v>616.5333333333333</v>
+            <v>669.76470588235293</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>11635</v>
+            <v>14188</v>
           </cell>
           <cell r="D33">
-            <v>775.66666666666663</v>
+            <v>834.58823529411768</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>7791</v>
+            <v>9633</v>
           </cell>
           <cell r="D34">
-            <v>519.4</v>
+            <v>566.64705882352939</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>2991</v>
+            <v>3669</v>
           </cell>
           <cell r="D35">
-            <v>199.4</v>
+            <v>215.8235294117647</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>2162</v>
+            <v>3171</v>
           </cell>
           <cell r="D36">
-            <v>144.13333333333333</v>
+            <v>186.52941176470588</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>5325</v>
+            <v>5952</v>
           </cell>
           <cell r="D37">
-            <v>355</v>
+            <v>350.11764705882354</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>4118</v>
+            <v>4621</v>
           </cell>
           <cell r="D38">
-            <v>274.53333333333336</v>
+            <v>271.8235294117647</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>5820</v>
+            <v>6813</v>
           </cell>
           <cell r="D39">
-            <v>388</v>
+            <v>400.76470588235293</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>3581</v>
+            <v>4214</v>
           </cell>
           <cell r="D40">
-            <v>238.73333333333332</v>
+            <v>247.88235294117646</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>3818</v>
+            <v>4341</v>
           </cell>
           <cell r="D41">
-            <v>254.53333333333333</v>
+            <v>255.35294117647058</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>753</v>
+            <v>842</v>
           </cell>
           <cell r="D42">
-            <v>50.2</v>
+            <v>49.529411764705884</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1267</v>
+            <v>1370</v>
           </cell>
           <cell r="D43">
-            <v>84.466666666666669</v>
+            <v>80.588235294117652</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>547</v>
+            <v>602</v>
           </cell>
           <cell r="D44">
-            <v>36.466666666666669</v>
+            <v>35.411764705882355</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>661</v>
+            <v>720</v>
           </cell>
           <cell r="D45">
-            <v>44.06666666666667</v>
+            <v>42.352941176470587</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="D46">
-            <v>0.6</v>
+            <v>0.58823529411764708</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>48</v>
+            <v>54</v>
           </cell>
           <cell r="D47">
-            <v>3.2</v>
+            <v>3.1764705882352939</v>
           </cell>
         </row>
       </sheetData>
@@ -879,6 +881,8 @@
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1213,11 +1217,11 @@
       </c>
       <c r="C2" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>15803</v>
+        <v>19244</v>
       </c>
       <c r="D2" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1053.5333333333333</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1229,11 +1233,11 @@
       </c>
       <c r="C3" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1084</v>
+        <v>1282</v>
       </c>
       <c r="D3" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>72.266666666666666</v>
+        <v>75.411764705882348</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1245,11 +1249,11 @@
       </c>
       <c r="C4" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>7353</v>
+        <v>9264</v>
       </c>
       <c r="D4" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>490.2</v>
+        <v>544.94117647058829</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1261,11 +1265,11 @@
       </c>
       <c r="C5" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1437</v>
+        <v>1661</v>
       </c>
       <c r="D5" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>95.8</v>
+        <v>97.705882352941174</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1277,11 +1281,11 @@
       </c>
       <c r="C6" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="D6" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>16.466666666666665</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1293,11 +1297,11 @@
       </c>
       <c r="C7" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>17995</v>
+        <v>21428</v>
       </c>
       <c r="D7" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1199.6666666666667</v>
+        <v>1260.4705882352941</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1309,11 +1313,11 @@
       </c>
       <c r="C8" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1690</v>
+        <v>2017</v>
       </c>
       <c r="D8" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>112.66666666666667</v>
+        <v>118.64705882352941</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,11 +1329,11 @@
       </c>
       <c r="C9" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>4065</v>
+        <v>4806</v>
       </c>
       <c r="D9" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>271</v>
+        <v>282.70588235294116</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1341,11 +1345,11 @@
       </c>
       <c r="C10" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>9170</v>
+        <v>10925</v>
       </c>
       <c r="D10" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>611.33333333333337</v>
+        <v>642.64705882352939</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1357,11 +1361,11 @@
       </c>
       <c r="C11" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>5243</v>
+        <v>6325</v>
       </c>
       <c r="D11" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>349.53333333333336</v>
+        <v>372.05882352941177</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,11 +1377,11 @@
       </c>
       <c r="C12" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>44494</v>
+        <v>54660</v>
       </c>
       <c r="D12" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2966.2666666666669</v>
+        <v>3215.294117647059</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1389,11 +1393,11 @@
       </c>
       <c r="C13" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>30091</v>
+        <v>36825</v>
       </c>
       <c r="D13" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2006.0666666666666</v>
+        <v>2166.1764705882351</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,11 +1409,11 @@
       </c>
       <c r="C14" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>29646</v>
+        <v>36606</v>
       </c>
       <c r="D14" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1976.4</v>
+        <v>2153.294117647059</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1421,11 +1425,11 @@
       </c>
       <c r="C15" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>33033</v>
+        <v>40543</v>
       </c>
       <c r="D15" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2202.1999999999998</v>
+        <v>2384.8823529411766</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1437,11 +1441,11 @@
       </c>
       <c r="C16" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>1975</v>
+        <v>2281</v>
       </c>
       <c r="D16" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>131.66666666666666</v>
+        <v>134.1764705882353</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1453,11 +1457,11 @@
       </c>
       <c r="C17" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>2885</v>
+        <v>3613</v>
       </c>
       <c r="D17" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>192.33333333333334</v>
+        <v>212.52941176470588</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,11 +1473,11 @@
       </c>
       <c r="C18" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>2203</v>
+        <v>2646</v>
       </c>
       <c r="D18" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>146.86666666666667</v>
+        <v>155.64705882352942</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,11 +1489,11 @@
       </c>
       <c r="C19" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>6788</v>
+        <v>8211</v>
       </c>
       <c r="D19" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>452.53333333333336</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1501,11 +1505,11 @@
       </c>
       <c r="C20" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>11461</v>
+        <v>13716</v>
       </c>
       <c r="D20" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>764.06666666666672</v>
+        <v>806.82352941176475</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1521,7 +1525,7 @@
       </c>
       <c r="D21" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>7.333333333333333</v>
+        <v>6.4705882352941178</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,11 +1537,11 @@
       </c>
       <c r="C22" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="D22" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>58</v>
+        <v>52.352941176470587</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1549,11 +1553,11 @@
       </c>
       <c r="C23" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>9196</v>
+        <v>11866</v>
       </c>
       <c r="D23" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>613.06666666666672</v>
+        <v>698</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1565,11 +1569,11 @@
       </c>
       <c r="C24" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>14865</v>
+        <v>18440</v>
       </c>
       <c r="D24" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>991</v>
+        <v>1084.7058823529412</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1581,11 +1585,11 @@
       </c>
       <c r="C25" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>6594</v>
+        <v>8047</v>
       </c>
       <c r="D25" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>439.6</v>
+        <v>473.35294117647061</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1597,11 +1601,11 @@
       </c>
       <c r="C26" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>5181</v>
+        <v>6254</v>
       </c>
       <c r="D26" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>345.4</v>
+        <v>367.88235294117646</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,11 +1617,11 @@
       </c>
       <c r="C27" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1571</v>
+        <v>1841</v>
       </c>
       <c r="D27" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>104.73333333333333</v>
+        <v>108.29411764705883</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1629,11 +1633,11 @@
       </c>
       <c r="C28" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1668</v>
+        <v>2009</v>
       </c>
       <c r="D28" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>111.2</v>
+        <v>118.17647058823529</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,11 +1649,11 @@
       </c>
       <c r="C29" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>10991</v>
+        <v>13571</v>
       </c>
       <c r="D29" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>732.73333333333335</v>
+        <v>798.29411764705878</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1661,11 +1665,11 @@
       </c>
       <c r="C30" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>9248</v>
+        <v>11386</v>
       </c>
       <c r="D30" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>616.5333333333333</v>
+        <v>669.76470588235293</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1677,11 +1681,11 @@
       </c>
       <c r="C31" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>11635</v>
+        <v>14188</v>
       </c>
       <c r="D31" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>775.66666666666663</v>
+        <v>834.58823529411768</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1693,11 +1697,11 @@
       </c>
       <c r="C32" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>7791</v>
+        <v>9633</v>
       </c>
       <c r="D32" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>519.4</v>
+        <v>566.64705882352939</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,11 +1713,11 @@
       </c>
       <c r="C33" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>2991</v>
+        <v>3669</v>
       </c>
       <c r="D33" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>199.4</v>
+        <v>215.8235294117647</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1725,11 +1729,11 @@
       </c>
       <c r="C34" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>2162</v>
+        <v>3171</v>
       </c>
       <c r="D34" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>144.13333333333333</v>
+        <v>186.52941176470588</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1741,11 +1745,11 @@
       </c>
       <c r="C35" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>5325</v>
+        <v>5952</v>
       </c>
       <c r="D35" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>355</v>
+        <v>350.11764705882354</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1757,11 +1761,11 @@
       </c>
       <c r="C36" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>4118</v>
+        <v>4621</v>
       </c>
       <c r="D36" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>274.53333333333336</v>
+        <v>271.8235294117647</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1773,11 +1777,11 @@
       </c>
       <c r="C37" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>5820</v>
+        <v>6813</v>
       </c>
       <c r="D37" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>388</v>
+        <v>400.76470588235293</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1789,11 +1793,11 @@
       </c>
       <c r="C38" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>3581</v>
+        <v>4214</v>
       </c>
       <c r="D38" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>238.73333333333332</v>
+        <v>247.88235294117646</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1805,11 +1809,11 @@
       </c>
       <c r="C39" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>3818</v>
+        <v>4341</v>
       </c>
       <c r="D39" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>254.53333333333333</v>
+        <v>255.35294117647058</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1821,11 +1825,11 @@
       </c>
       <c r="C40" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>753</v>
+        <v>842</v>
       </c>
       <c r="D40" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>50.2</v>
+        <v>49.529411764705884</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1837,11 +1841,11 @@
       </c>
       <c r="C41" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1267</v>
+        <v>1370</v>
       </c>
       <c r="D41" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>84.466666666666669</v>
+        <v>80.588235294117652</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1853,11 +1857,11 @@
       </c>
       <c r="C42" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>547</v>
+        <v>602</v>
       </c>
       <c r="D42" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>36.466666666666669</v>
+        <v>35.411764705882355</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1869,11 +1873,11 @@
       </c>
       <c r="C43" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>661</v>
+        <v>720</v>
       </c>
       <c r="D43" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>44.06666666666667</v>
+        <v>42.352941176470587</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1883,11 +1887,11 @@
       </c>
       <c r="C44" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.6</v>
+        <v>0.58823529411764708</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1897,11 +1901,11 @@
       </c>
       <c r="C45" s="15">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D45" s="14">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>3.2</v>
+        <v>3.1764705882352939</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1957,19 +1961,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>340311</v>
+        <v>415844</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>337483</v>
+        <v>410956</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>22687.4</v>
+        <v>24461.411764705881</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>499122.80000000005</v>
+        <v>538151.0588235294</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1977,11 +1981,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.4888072082010092</v>
+        <v>0.59729936642406645</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-355896</v>
+        <v>-280363</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2007,7 +2011,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2828</v>
+        <v>4888</v>
       </c>
       <c r="B5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2015,7 +2019,7 @@
       </c>
       <c r="C5" s="11">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46224</v>
+        <v>46229</v>
       </c>
       <c r="D5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2023,11 +2027,11 @@
       </c>
       <c r="E5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00126FDE-2BF8-40D2-B20B-4425A532FD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CDBF21-3C3D-41AA-ABCC-1D1F1887F4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CDBF21-3C3D-41AA-ABCC-1D1F1887F4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559CEB68-C08F-44EC-B670-87EE97EA5E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -1185,16 +1185,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="12"/>
     <col min="2" max="2" width="50.7109375" style="12" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>3</v>
       </c>
@@ -1207,8 +1217,47 @@
       <c r="D1" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="18">
         <v>110150</v>
       </c>
@@ -1223,8 +1272,60 @@
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
         <v>1132</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="3">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
+        <v>415844</v>
+      </c>
+      <c r="F2" s="3">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
+        <v>410956</v>
+      </c>
+      <c r="G2" s="4">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
+        <v>24461.411764705881</v>
+      </c>
+      <c r="H2" s="5">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
+        <v>538151.0588235294</v>
+      </c>
+      <c r="I2" s="4">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
+        <v>696207</v>
+      </c>
+      <c r="J2" s="6">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
+        <v>0.59729936642406645</v>
+      </c>
+      <c r="K2" s="7">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
+        <v>-280363</v>
+      </c>
+      <c r="L2" s="10">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
+        <v>4888</v>
+      </c>
+      <c r="M2" s="11">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
+        <v>46204</v>
+      </c>
+      <c r="N2" s="11">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
+        <v>46229</v>
+      </c>
+      <c r="O2" s="11">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
+        <v>46234</v>
+      </c>
+      <c r="P2" s="16">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
+        <v>17</v>
+      </c>
+      <c r="Q2" s="16">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>110151</v>
       </c>
@@ -1240,7 +1341,7 @@
         <v>75.411764705882348</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>110230</v>
       </c>
@@ -1256,7 +1357,7 @@
         <v>544.94117647058829</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>110400</v>
       </c>
@@ -1272,7 +1373,7 @@
         <v>97.705882352941174</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>111000</v>
       </c>
@@ -1288,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>120130</v>
       </c>
@@ -1304,7 +1405,7 @@
         <v>1260.4705882352941</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>120131</v>
       </c>
@@ -1320,7 +1421,7 @@
         <v>118.64705882352941</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>120132</v>
       </c>
@@ -1336,7 +1437,7 @@
         <v>282.70588235294116</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>130150</v>
       </c>
@@ -1352,7 +1453,7 @@
         <v>642.64705882352939</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>130151</v>
       </c>
@@ -1368,7 +1469,7 @@
         <v>372.05882352941177</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>130152</v>
       </c>
@@ -1384,7 +1485,7 @@
         <v>3215.294117647059</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>130153</v>
       </c>
@@ -1400,7 +1501,7 @@
         <v>2166.1764705882351</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>130154</v>
       </c>
@@ -1416,7 +1517,7 @@
         <v>2153.294117647059</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>130155</v>
       </c>
@@ -1432,7 +1533,7 @@
         <v>2384.8823529411766</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>130156</v>
       </c>
@@ -1918,7 +2019,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC79391-350C-4657-A510-D4378E4F4331}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="13.28515625" customWidth="1"/>
@@ -1935,105 +2036,6 @@
       <c r="F1" s="19"/>
       <c r="G1" s="19"/>
     </row>
-    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>415844</v>
-      </c>
-      <c r="B3" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>410956</v>
-      </c>
-      <c r="C3" s="4">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>24461.411764705881</v>
-      </c>
-      <c r="D3" s="5">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>538151.0588235294</v>
-      </c>
-      <c r="E3" s="4">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
-        <v>696207</v>
-      </c>
-      <c r="F3" s="6">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.59729936642406645</v>
-      </c>
-      <c r="G3" s="7">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-280363</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>4888</v>
-      </c>
-      <c r="B5" s="11">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
-        <v>46204</v>
-      </c>
-      <c r="C5" s="11">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46229</v>
-      </c>
-      <c r="D5" s="11">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
-        <v>46234</v>
-      </c>
-      <c r="E5" s="16">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>17</v>
-      </c>
-      <c r="F5" s="16">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559CEB68-C08F-44EC-B670-87EE97EA5E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BC96CD-1347-42E3-AF7D-D661726920D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -1185,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="12"/>
@@ -1204,7 +1204,7 @@
     <col min="15" max="15" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>3</v>
       </c>
@@ -1217,47 +1217,8 @@
       <c r="D1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="18">
         <v>110150</v>
       </c>
@@ -1272,60 +1233,8 @@
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
         <v>1132</v>
       </c>
-      <c r="E2" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>415844</v>
-      </c>
-      <c r="F2" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>410956</v>
-      </c>
-      <c r="G2" s="4">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>24461.411764705881</v>
-      </c>
-      <c r="H2" s="5">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>538151.0588235294</v>
-      </c>
-      <c r="I2" s="4">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
-        <v>696207</v>
-      </c>
-      <c r="J2" s="6">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.59729936642406645</v>
-      </c>
-      <c r="K2" s="7">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-280363</v>
-      </c>
-      <c r="L2" s="10">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>4888</v>
-      </c>
-      <c r="M2" s="11">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
-        <v>46204</v>
-      </c>
-      <c r="N2" s="11">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46229</v>
-      </c>
-      <c r="O2" s="11">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
-        <v>46234</v>
-      </c>
-      <c r="P2" s="16">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>17</v>
-      </c>
-      <c r="Q2" s="16">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>110151</v>
       </c>
@@ -1341,7 +1250,7 @@
         <v>75.411764705882348</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>110230</v>
       </c>
@@ -1357,7 +1266,7 @@
         <v>544.94117647058829</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>110400</v>
       </c>
@@ -1373,7 +1282,7 @@
         <v>97.705882352941174</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>111000</v>
       </c>
@@ -1389,7 +1298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>120130</v>
       </c>
@@ -1405,7 +1314,7 @@
         <v>1260.4705882352941</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>120131</v>
       </c>
@@ -1421,7 +1330,7 @@
         <v>118.64705882352941</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>120132</v>
       </c>
@@ -1437,7 +1346,7 @@
         <v>282.70588235294116</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>130150</v>
       </c>
@@ -1453,7 +1362,7 @@
         <v>642.64705882352939</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>130151</v>
       </c>
@@ -1469,7 +1378,7 @@
         <v>372.05882352941177</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>130152</v>
       </c>
@@ -1485,7 +1394,7 @@
         <v>3215.294117647059</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>130153</v>
       </c>
@@ -1501,7 +1410,7 @@
         <v>2166.1764705882351</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>130154</v>
       </c>
@@ -1517,7 +1426,7 @@
         <v>2153.294117647059</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>130155</v>
       </c>
@@ -1533,7 +1442,7 @@
         <v>2384.8823529411766</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>130156</v>
       </c>
@@ -2019,7 +1928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC79391-350C-4657-A510-D4378E4F4331}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="13.28515625" customWidth="1"/>
@@ -2036,6 +1945,105 @@
       <c r="F1" s="19"/>
       <c r="G1" s="19"/>
     </row>
+    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
+        <v>415844</v>
+      </c>
+      <c r="B3" s="3">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
+        <v>410956</v>
+      </c>
+      <c r="C3" s="4">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
+        <v>24461.411764705881</v>
+      </c>
+      <c r="D3" s="5">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
+        <v>538151.0588235294</v>
+      </c>
+      <c r="E3" s="4">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
+        <v>696207</v>
+      </c>
+      <c r="F3" s="6">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
+        <v>0.59729936642406645</v>
+      </c>
+      <c r="G3" s="7">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
+        <v>-280363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
+        <v>4888</v>
+      </c>
+      <c r="B5" s="11">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
+        <v>46204</v>
+      </c>
+      <c r="C5" s="11">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
+        <v>46229</v>
+      </c>
+      <c r="D5" s="11">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
+        <v>46234</v>
+      </c>
+      <c r="E5" s="16">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
+        <v>17</v>
+      </c>
+      <c r="F5" s="16">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BC96CD-1347-42E3-AF7D-D661726920D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6DD430-2549-4EF3-A5A7-3540E093B277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -38,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>DASHBOARD</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>FORECAST</t>
   </si>
@@ -58,12 +55,6 @@
     <t>Cremosillo Tradicional 150g</t>
   </si>
   <si>
-    <t>INICIO DE VENTA</t>
-  </si>
-  <si>
-    <t>FINAL DE VENTA</t>
-  </si>
-  <si>
     <t>Cremosillo Coco 150g</t>
   </si>
   <si>
@@ -193,9 +184,6 @@
     <t>Cremigurt Griego Natural 4 Kg</t>
   </si>
   <si>
-    <t>TOTAL UNIDADES VENTA BRUTA</t>
-  </si>
-  <si>
     <t>TOTAL UNIDADES VENTA NETA</t>
   </si>
   <si>
@@ -208,29 +196,20 @@
     <t>DIFERENCIA ALCANCE FORCAST</t>
   </si>
   <si>
-    <t>UNIDADES DEVOLUCION</t>
-  </si>
-  <si>
-    <t>DIAS VENTAS EFECTIVOS</t>
-  </si>
-  <si>
-    <t>DIAS VENTA RESTANTES</t>
-  </si>
-  <si>
-    <t>TRANSCURSO DE VENTA</t>
-  </si>
-  <si>
     <t>PROMEDIO DE VENTA DIARIA</t>
   </si>
   <si>
     <t>VENTA BRUTA</t>
+  </si>
+  <si>
+    <t>UNITS RETURN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,14 +218,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -299,14 +270,6 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
@@ -314,27 +277,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -377,32 +326,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -410,17 +353,11 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -473,9 +410,6 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="3">
-          <cell r="G3">
-            <v>415844</v>
-          </cell>
           <cell r="H3">
             <v>410956</v>
           </cell>
@@ -512,21 +446,6 @@
           </cell>
           <cell r="G5">
             <v>4888</v>
-          </cell>
-          <cell r="H5">
-            <v>46204</v>
-          </cell>
-          <cell r="I5">
-            <v>46229</v>
-          </cell>
-          <cell r="J5">
-            <v>46234</v>
-          </cell>
-          <cell r="K5">
-            <v>17</v>
-          </cell>
-          <cell r="L5">
-            <v>5</v>
           </cell>
         </row>
         <row r="6">
@@ -1188,8 +1107,8 @@
   <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="12"/>
-    <col min="2" max="2" width="50.7109375" style="12" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="10"/>
+    <col min="2" max="2" width="50.7109375" style="10" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
@@ -1205,721 +1124,721 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>110150</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="18">
-        <v>110150</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="15">
+      <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
         <v>19244</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
         <v>1132</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="15">
         <v>110151</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="15">
+        <v>5</v>
+      </c>
+      <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
         <v>1282</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
         <v>75.411764705882348</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
+      <c r="A4" s="15">
         <v>110230</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="15">
+        <v>6</v>
+      </c>
+      <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
         <v>9264</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
         <v>544.94117647058829</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
+      <c r="A5" s="15">
         <v>110400</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="15">
+        <v>7</v>
+      </c>
+      <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
         <v>1661</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
         <v>97.705882352941174</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="A6" s="15">
         <v>111000</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="15">
+        <v>8</v>
+      </c>
+      <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
         <v>289</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="18">
+      <c r="A7" s="15">
         <v>120130</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="15">
+        <v>9</v>
+      </c>
+      <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
         <v>21428</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
         <v>1260.4705882352941</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
+      <c r="A8" s="15">
         <v>120131</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="15">
+        <v>10</v>
+      </c>
+      <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
         <v>2017</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
         <v>118.64705882352941</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="15">
         <v>120132</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="15">
+        <v>11</v>
+      </c>
+      <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
         <v>4806</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
         <v>282.70588235294116</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+      <c r="A10" s="15">
         <v>130150</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="15">
+        <v>12</v>
+      </c>
+      <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
         <v>10925</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
         <v>642.64705882352939</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
+      <c r="A11" s="15">
         <v>130151</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="15">
+        <v>13</v>
+      </c>
+      <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
         <v>6325</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
         <v>372.05882352941177</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
+      <c r="A12" s="15">
         <v>130152</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="15">
+        <v>14</v>
+      </c>
+      <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
         <v>54660</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
         <v>3215.294117647059</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
+      <c r="A13" s="15">
         <v>130153</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="15">
+        <v>15</v>
+      </c>
+      <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
         <v>36825</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
         <v>2166.1764705882351</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
+      <c r="A14" s="15">
         <v>130154</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="15">
+        <v>16</v>
+      </c>
+      <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
         <v>36606</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
         <v>2153.294117647059</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
+      <c r="A15" s="15">
         <v>130155</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="15">
+        <v>17</v>
+      </c>
+      <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
         <v>40543</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
         <v>2384.8823529411766</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
+      <c r="A16" s="15">
         <v>130156</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="15">
+        <v>18</v>
+      </c>
+      <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
         <v>2281</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
         <v>134.1764705882353</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="18">
+      <c r="A17" s="15">
         <v>130700</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="15">
+        <v>19</v>
+      </c>
+      <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
         <v>3613</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
         <v>212.52941176470588</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
+      <c r="A18" s="15">
         <v>130701</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="15">
+        <v>20</v>
+      </c>
+      <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
         <v>2646</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
         <v>155.64705882352942</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="18">
+      <c r="A19" s="15">
         <v>130702</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="15">
+        <v>21</v>
+      </c>
+      <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
         <v>8211</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
         <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="18">
+      <c r="A20" s="15">
         <v>130703</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="15">
+        <v>22</v>
+      </c>
+      <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
         <v>13716</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
         <v>806.82352941176475</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="18">
+      <c r="A21" s="15">
         <v>130704</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="15">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
         <v>110</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
         <v>6.4705882352941178</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="18">
+      <c r="A22" s="15">
         <v>130707</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="15">
+        <v>24</v>
+      </c>
+      <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
         <v>890</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
         <v>52.352941176470587</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="18">
+      <c r="A23" s="15">
         <v>131150</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="15">
+        <v>25</v>
+      </c>
+      <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
         <v>11866</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
         <v>698</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="18">
+      <c r="A24" s="15">
         <v>131151</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="15">
+        <v>26</v>
+      </c>
+      <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
         <v>18440</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
         <v>1084.7058823529412</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="18">
+      <c r="A25" s="15">
         <v>131152</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="15">
+        <v>27</v>
+      </c>
+      <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
         <v>8047</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
         <v>473.35294117647061</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="18">
+      <c r="A26" s="15">
         <v>131153</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="15">
+        <v>28</v>
+      </c>
+      <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
         <v>6254</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
         <v>367.88235294117646</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
+      <c r="A27" s="15">
         <v>131700</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="15">
+        <v>29</v>
+      </c>
+      <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
         <v>1841</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
         <v>108.29411764705883</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="18">
+      <c r="A28" s="15">
         <v>131701</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="15">
+        <v>30</v>
+      </c>
+      <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
         <v>2009</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
         <v>118.17647058823529</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="18">
+      <c r="A29" s="15">
         <v>132150</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="15">
+        <v>31</v>
+      </c>
+      <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
         <v>13571</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
         <v>798.29411764705878</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="18">
+      <c r="A30" s="15">
         <v>132151</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="15">
+        <v>32</v>
+      </c>
+      <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
         <v>11386</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
         <v>669.76470588235293</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="18">
+      <c r="A31" s="15">
         <v>132152</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="15">
+        <v>33</v>
+      </c>
+      <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
         <v>14188</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
         <v>834.58823529411768</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="18">
+      <c r="A32" s="15">
         <v>132153</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="15">
+        <v>34</v>
+      </c>
+      <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
         <v>9633</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
         <v>566.64705882352939</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="18">
+      <c r="A33" s="15">
         <v>140230</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="15">
+        <v>35</v>
+      </c>
+      <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
         <v>3669</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
         <v>215.8235294117647</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="18">
+      <c r="A34" s="15">
         <v>140231</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="15">
+        <v>36</v>
+      </c>
+      <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
         <v>3171</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
         <v>186.52941176470588</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="18">
+      <c r="A35" s="15">
         <v>140232</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="15">
+        <v>37</v>
+      </c>
+      <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
         <v>5952</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
         <v>350.11764705882354</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="18">
+      <c r="A36" s="15">
         <v>150360</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="15">
+        <v>38</v>
+      </c>
+      <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
         <v>4621</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
         <v>271.8235294117647</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="18">
+      <c r="A37" s="15">
         <v>150361</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" s="15">
+        <v>39</v>
+      </c>
+      <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
         <v>6813</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
         <v>400.76470588235293</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="18">
+      <c r="A38" s="15">
         <v>150362</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="15">
+        <v>40</v>
+      </c>
+      <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
         <v>4214</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
         <v>247.88235294117646</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="18">
+      <c r="A39" s="15">
         <v>150363</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="15">
+        <v>41</v>
+      </c>
+      <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
         <v>4341</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
         <v>255.35294117647058</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="18">
+      <c r="A40" s="15">
         <v>151500</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="15">
+        <v>42</v>
+      </c>
+      <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
         <v>842</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
         <v>49.529411764705884</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="18">
+      <c r="A41" s="15">
         <v>151501</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="15">
+        <v>43</v>
+      </c>
+      <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
         <v>1370</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
         <v>80.588235294117652</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="18">
+      <c r="A42" s="15">
         <v>151502</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="15">
+        <v>44</v>
+      </c>
+      <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
         <v>602</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
         <v>35.411764705882355</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="18">
+      <c r="A43" s="15">
         <v>151503</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="15">
+        <v>45</v>
+      </c>
+      <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
         <v>720</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
         <v>42.352941176470587</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="18"/>
+      <c r="A44" s="15"/>
       <c r="B44" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="15">
+        <v>46</v>
+      </c>
+      <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
         <v>10</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
         <v>0.58823529411764708</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="18"/>
+      <c r="A45" s="15"/>
       <c r="B45" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="15">
+        <v>47</v>
+      </c>
+      <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
         <v>54</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
         <v>3.1764705882352939</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="13"/>
+      <c r="C46" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1928,51 +1847,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC79391-350C-4657-A510-D4378E4F4331}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A2:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-    </row>
-    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>415844</v>
-      </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
         <v>410956</v>
@@ -1999,55 +1901,17 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>58</v>
+      <c r="A4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
         <v>4888</v>
       </c>
-      <c r="B5" s="11">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
-        <v>46204</v>
-      </c>
-      <c r="C5" s="11">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46229</v>
-      </c>
-      <c r="D5" s="11">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
-        <v>46234</v>
-      </c>
-      <c r="E5" s="16">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>17</v>
-      </c>
-      <c r="F5" s="16">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6DD430-2549-4EF3-A5A7-3540E093B277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EA908B-8D97-4461-8E49-4A44825EBA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EA908B-8D97-4461-8E49-4A44825EBA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BEF28A-B576-44BD-80EA-7C508B9A49E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -18,6 +18,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>FORECAST</t>
   </si>
@@ -184,18 +185,6 @@
     <t>Cremigurt Griego Natural 4 Kg</t>
   </si>
   <si>
-    <t>TOTAL UNIDADES VENTA NETA</t>
-  </si>
-  <si>
-    <t>PROMEDIO VENTA DIARIA</t>
-  </si>
-  <si>
-    <t>PRONOSTICO VENTA MENSUAL</t>
-  </si>
-  <si>
-    <t>DIFERENCIA ALCANCE FORCAST</t>
-  </si>
-  <si>
     <t>PROMEDIO DE VENTA DIARIA</t>
   </si>
   <si>
@@ -203,13 +192,46 @@
   </si>
   <si>
     <t>UNITS RETURN</t>
+  </si>
+  <si>
+    <t>DASHBOARD</t>
+  </si>
+  <si>
+    <t>TOTAL UNITS SALES GROSS</t>
+  </si>
+  <si>
+    <t>TOTAL UNITS SALES NET</t>
+  </si>
+  <si>
+    <t>PROMD VTA DIA</t>
+  </si>
+  <si>
+    <t>PROMD VTA MES</t>
+  </si>
+  <si>
+    <t>DIF UNITS</t>
+  </si>
+  <si>
+    <t>INICIO DE VENTA</t>
+  </si>
+  <si>
+    <t>TRANSC. VENTA</t>
+  </si>
+  <si>
+    <t>FINAL DE VENTA</t>
+  </si>
+  <si>
+    <t>DIAS VENTA EFECT.</t>
+  </si>
+  <si>
+    <t>DIAS VENTA RESTA.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,8 +299,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -294,6 +340,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -358,6 +410,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -409,26 +476,6 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2">
-        <row r="3">
-          <cell r="H3">
-            <v>410956</v>
-          </cell>
-          <cell r="I3">
-            <v>24461.411764705881</v>
-          </cell>
-          <cell r="J3">
-            <v>538151.0588235294</v>
-          </cell>
-          <cell r="K3">
-            <v>696207</v>
-          </cell>
-          <cell r="L3">
-            <v>0.59729936642406645</v>
-          </cell>
-          <cell r="M3">
-            <v>-280363</v>
-          </cell>
-        </row>
         <row r="4">
           <cell r="C4">
             <v>19244</v>
@@ -444,9 +491,6 @@
           <cell r="D5">
             <v>75.411764705882348</v>
           </cell>
-          <cell r="G5">
-            <v>4888</v>
-          </cell>
         </row>
         <row r="6">
           <cell r="C6">
@@ -785,7 +829,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="3">
+        <row r="3">
+          <cell r="K3">
+            <v>410956</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
@@ -802,6 +852,42 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="VENTAS JULIO"/>
+      <sheetName val="VENTAS DIARIA POR SKU"/>
+      <sheetName val="DESPACHO"/>
+      <sheetName val="RELACION DE VIAJES"/>
+      <sheetName val="RELACION DE VIAJES SITES "/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="117">
+          <cell r="G117">
+            <v>415844</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="O2">
+            <v>1510</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1131,10 +1217,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1847,22 +1933,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC79391-350C-4657-A510-D4378E4F4331}">
-  <dimension ref="A2:G5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="13.28515625" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
@@ -1871,47 +1971,86 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <f>'[2]VENTAS JULIO'!$G$117</f>
+        <v>415844</v>
+      </c>
       <c r="B3" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
+        <f>'[1]DESV. VTS BY SKU'!$K$3</f>
         <v>410956</v>
       </c>
       <c r="C3" s="4">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>24461.411764705881</v>
+        <f ca="1">A3/E5</f>
+        <v>23102.444444444445</v>
       </c>
       <c r="D3" s="5">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>538151.0588235294</v>
+        <f ca="1">C3*22</f>
+        <v>508253.77777777781</v>
       </c>
       <c r="E3" s="4">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
         <v>696207</v>
       </c>
       <c r="F3" s="6">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
+        <f>A3/E3</f>
         <v>0.59729936642406645</v>
       </c>
       <c r="G3" s="7">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
+        <f>A3-E3</f>
         <v>-280363</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>54</v>
+      <c r="A4" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
+        <f>A3-B3</f>
         <v>4888</v>
       </c>
+      <c r="B5" s="18">
+        <v>46204</v>
+      </c>
+      <c r="C5" s="18">
+        <f ca="1">TODAY()-1</f>
+        <v>46229</v>
+      </c>
+      <c r="D5" s="18">
+        <v>46234</v>
+      </c>
+      <c r="E5" s="19">
+        <f ca="1">NETWORKDAYS(B5,C5)</f>
+        <v>18</v>
+      </c>
+      <c r="F5" s="20">
+        <f ca="1">NETWORKDAYS(C5,D5)-2</f>
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BEF28A-B576-44BD-80EA-7C508B9A49E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3C9A0F-FB1D-4029-8778-2B1DBDB828F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -411,9 +411,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -424,6 +421,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,6 +445,42 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="VENTAS JULIO"/>
+      <sheetName val="VENTAS DIARIA POR SKU"/>
+      <sheetName val="DESPACHO"/>
+      <sheetName val="RELACION DE VIAJES"/>
+      <sheetName val="RELACION DE VIAJES SITES "/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="117">
+          <cell r="G117">
+            <v>415844</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="O2">
+            <v>1510</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -852,42 +888,6 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="VENTAS JULIO"/>
-      <sheetName val="VENTAS DIARIA POR SKU"/>
-      <sheetName val="DESPACHO"/>
-      <sheetName val="RELACION DE VIAJES"/>
-      <sheetName val="RELACION DE VIAJES SITES "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="117">
-          <cell r="G117">
-            <v>415844</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="O2">
-            <v>1510</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1231,11 +1231,11 @@
         <v>4</v>
       </c>
       <c r="C2" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
         <v>19244</v>
       </c>
       <c r="D2" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
         <v>1132</v>
       </c>
     </row>
@@ -1247,11 +1247,11 @@
         <v>5</v>
       </c>
       <c r="C3" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
         <v>1282</v>
       </c>
       <c r="D3" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
         <v>75.411764705882348</v>
       </c>
     </row>
@@ -1263,11 +1263,11 @@
         <v>6</v>
       </c>
       <c r="C4" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
         <v>9264</v>
       </c>
       <c r="D4" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
         <v>544.94117647058829</v>
       </c>
     </row>
@@ -1279,11 +1279,11 @@
         <v>7</v>
       </c>
       <c r="C5" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
         <v>1661</v>
       </c>
       <c r="D5" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
         <v>97.705882352941174</v>
       </c>
     </row>
@@ -1295,11 +1295,11 @@
         <v>8</v>
       </c>
       <c r="C6" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
         <v>289</v>
       </c>
       <c r="D6" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
         <v>17</v>
       </c>
     </row>
@@ -1311,11 +1311,11 @@
         <v>9</v>
       </c>
       <c r="C7" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
         <v>21428</v>
       </c>
       <c r="D7" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
         <v>1260.4705882352941</v>
       </c>
     </row>
@@ -1327,11 +1327,11 @@
         <v>10</v>
       </c>
       <c r="C8" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
         <v>2017</v>
       </c>
       <c r="D8" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
         <v>118.64705882352941</v>
       </c>
     </row>
@@ -1343,11 +1343,11 @@
         <v>11</v>
       </c>
       <c r="C9" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
         <v>4806</v>
       </c>
       <c r="D9" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
         <v>282.70588235294116</v>
       </c>
     </row>
@@ -1359,11 +1359,11 @@
         <v>12</v>
       </c>
       <c r="C10" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
         <v>10925</v>
       </c>
       <c r="D10" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
         <v>642.64705882352939</v>
       </c>
     </row>
@@ -1375,11 +1375,11 @@
         <v>13</v>
       </c>
       <c r="C11" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
         <v>6325</v>
       </c>
       <c r="D11" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
         <v>372.05882352941177</v>
       </c>
     </row>
@@ -1391,11 +1391,11 @@
         <v>14</v>
       </c>
       <c r="C12" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
         <v>54660</v>
       </c>
       <c r="D12" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
         <v>3215.294117647059</v>
       </c>
     </row>
@@ -1407,11 +1407,11 @@
         <v>15</v>
       </c>
       <c r="C13" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
         <v>36825</v>
       </c>
       <c r="D13" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
         <v>2166.1764705882351</v>
       </c>
     </row>
@@ -1423,11 +1423,11 @@
         <v>16</v>
       </c>
       <c r="C14" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
         <v>36606</v>
       </c>
       <c r="D14" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
         <v>2153.294117647059</v>
       </c>
     </row>
@@ -1439,11 +1439,11 @@
         <v>17</v>
       </c>
       <c r="C15" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
         <v>40543</v>
       </c>
       <c r="D15" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
         <v>2384.8823529411766</v>
       </c>
     </row>
@@ -1455,11 +1455,11 @@
         <v>18</v>
       </c>
       <c r="C16" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
         <v>2281</v>
       </c>
       <c r="D16" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
         <v>134.1764705882353</v>
       </c>
     </row>
@@ -1471,11 +1471,11 @@
         <v>19</v>
       </c>
       <c r="C17" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
         <v>3613</v>
       </c>
       <c r="D17" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
         <v>212.52941176470588</v>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         <v>20</v>
       </c>
       <c r="C18" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
         <v>2646</v>
       </c>
       <c r="D18" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
         <v>155.64705882352942</v>
       </c>
     </row>
@@ -1503,11 +1503,11 @@
         <v>21</v>
       </c>
       <c r="C19" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
         <v>8211</v>
       </c>
       <c r="D19" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
         <v>483</v>
       </c>
     </row>
@@ -1519,11 +1519,11 @@
         <v>22</v>
       </c>
       <c r="C20" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
         <v>13716</v>
       </c>
       <c r="D20" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
         <v>806.82352941176475</v>
       </c>
     </row>
@@ -1535,11 +1535,11 @@
         <v>23</v>
       </c>
       <c r="C21" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C23</f>
         <v>110</v>
       </c>
       <c r="D21" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
         <v>6.4705882352941178</v>
       </c>
     </row>
@@ -1551,11 +1551,11 @@
         <v>24</v>
       </c>
       <c r="C22" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C24</f>
         <v>890</v>
       </c>
       <c r="D22" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
         <v>52.352941176470587</v>
       </c>
     </row>
@@ -1567,11 +1567,11 @@
         <v>25</v>
       </c>
       <c r="C23" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C25</f>
         <v>11866</v>
       </c>
       <c r="D23" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
         <v>698</v>
       </c>
     </row>
@@ -1583,11 +1583,11 @@
         <v>26</v>
       </c>
       <c r="C24" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
         <v>18440</v>
       </c>
       <c r="D24" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
         <v>1084.7058823529412</v>
       </c>
     </row>
@@ -1599,11 +1599,11 @@
         <v>27</v>
       </c>
       <c r="C25" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
         <v>8047</v>
       </c>
       <c r="D25" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
         <v>473.35294117647061</v>
       </c>
     </row>
@@ -1615,11 +1615,11 @@
         <v>28</v>
       </c>
       <c r="C26" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
         <v>6254</v>
       </c>
       <c r="D26" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
         <v>367.88235294117646</v>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         <v>29</v>
       </c>
       <c r="C27" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
         <v>1841</v>
       </c>
       <c r="D27" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
         <v>108.29411764705883</v>
       </c>
     </row>
@@ -1647,11 +1647,11 @@
         <v>30</v>
       </c>
       <c r="C28" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
         <v>2009</v>
       </c>
       <c r="D28" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
         <v>118.17647058823529</v>
       </c>
     </row>
@@ -1663,11 +1663,11 @@
         <v>31</v>
       </c>
       <c r="C29" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
         <v>13571</v>
       </c>
       <c r="D29" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
         <v>798.29411764705878</v>
       </c>
     </row>
@@ -1679,11 +1679,11 @@
         <v>32</v>
       </c>
       <c r="C30" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
         <v>11386</v>
       </c>
       <c r="D30" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
         <v>669.76470588235293</v>
       </c>
     </row>
@@ -1695,11 +1695,11 @@
         <v>33</v>
       </c>
       <c r="C31" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
         <v>14188</v>
       </c>
       <c r="D31" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
         <v>834.58823529411768</v>
       </c>
     </row>
@@ -1711,11 +1711,11 @@
         <v>34</v>
       </c>
       <c r="C32" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
         <v>9633</v>
       </c>
       <c r="D32" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
         <v>566.64705882352939</v>
       </c>
     </row>
@@ -1727,11 +1727,11 @@
         <v>35</v>
       </c>
       <c r="C33" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
         <v>3669</v>
       </c>
       <c r="D33" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
         <v>215.8235294117647</v>
       </c>
     </row>
@@ -1743,11 +1743,11 @@
         <v>36</v>
       </c>
       <c r="C34" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
         <v>3171</v>
       </c>
       <c r="D34" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
         <v>186.52941176470588</v>
       </c>
     </row>
@@ -1759,11 +1759,11 @@
         <v>37</v>
       </c>
       <c r="C35" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
         <v>5952</v>
       </c>
       <c r="D35" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
         <v>350.11764705882354</v>
       </c>
     </row>
@@ -1775,11 +1775,11 @@
         <v>38</v>
       </c>
       <c r="C36" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
         <v>4621</v>
       </c>
       <c r="D36" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
         <v>271.8235294117647</v>
       </c>
     </row>
@@ -1791,11 +1791,11 @@
         <v>39</v>
       </c>
       <c r="C37" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C39</f>
         <v>6813</v>
       </c>
       <c r="D37" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D39</f>
         <v>400.76470588235293</v>
       </c>
     </row>
@@ -1807,11 +1807,11 @@
         <v>40</v>
       </c>
       <c r="C38" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
         <v>4214</v>
       </c>
       <c r="D38" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
         <v>247.88235294117646</v>
       </c>
     </row>
@@ -1823,11 +1823,11 @@
         <v>41</v>
       </c>
       <c r="C39" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
         <v>4341</v>
       </c>
       <c r="D39" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
         <v>255.35294117647058</v>
       </c>
     </row>
@@ -1839,11 +1839,11 @@
         <v>42</v>
       </c>
       <c r="C40" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
         <v>842</v>
       </c>
       <c r="D40" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
         <v>49.529411764705884</v>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         <v>43</v>
       </c>
       <c r="C41" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
         <v>1370</v>
       </c>
       <c r="D41" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
         <v>80.588235294117652</v>
       </c>
     </row>
@@ -1871,11 +1871,11 @@
         <v>44</v>
       </c>
       <c r="C42" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
         <v>602</v>
       </c>
       <c r="D42" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
         <v>35.411764705882355</v>
       </c>
     </row>
@@ -1887,11 +1887,11 @@
         <v>45</v>
       </c>
       <c r="C43" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
         <v>720</v>
       </c>
       <c r="D43" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
         <v>42.352941176470587</v>
       </c>
     </row>
@@ -1901,11 +1901,11 @@
         <v>46</v>
       </c>
       <c r="C44" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C46</f>
         <v>10</v>
       </c>
       <c r="D44" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
         <v>0.58823529411764708</v>
       </c>
     </row>
@@ -1915,11 +1915,11 @@
         <v>47</v>
       </c>
       <c r="C45" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
+        <f>'[2]VINCULO VTS BY SKU OPEN'!C47</f>
         <v>54</v>
       </c>
       <c r="D45" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
+        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
         <v>3.1764705882352939</v>
       </c>
     </row>
@@ -1941,15 +1941,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1976,11 +1976,11 @@
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
-        <f>'[2]VENTAS JULIO'!$G$117</f>
+        <f>'[1]VENTAS JULIO'!$G$117</f>
         <v>415844</v>
       </c>
       <c r="B3" s="3">
-        <f>'[1]DESV. VTS BY SKU'!$K$3</f>
+        <f>'[2]DESV. VTS BY SKU'!$K$3</f>
         <v>410956</v>
       </c>
       <c r="C3" s="4">
@@ -2004,22 +2004,22 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="16" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2028,21 +2028,21 @@
         <f>A3-B3</f>
         <v>4888</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>46204</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <f ca="1">TODAY()-1</f>
         <v>46229</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>46234</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <f ca="1">NETWORKDAYS(B5,C5)</f>
         <v>18</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="19">
         <f ca="1">NETWORKDAYS(C5,D5)-2</f>
         <v>3</v>
       </c>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3C9A0F-FB1D-4029-8778-2B1DBDB828F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FC855B-6E09-4509-94D8-33CD3D56A4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -417,13 +417,13 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1941,15 +1941,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1985,11 +1985,11 @@
       </c>
       <c r="C3" s="4">
         <f ca="1">A3/E5</f>
-        <v>23102.444444444445</v>
+        <v>24461.411764705881</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">C3*22</f>
-        <v>508253.77777777781</v>
+        <v>538151.0588235294</v>
       </c>
       <c r="E3" s="4">
         <v>696207</v>
@@ -2038,13 +2038,13 @@
       <c r="D5" s="17">
         <v>46234</v>
       </c>
-      <c r="E5" s="18">
-        <f ca="1">NETWORKDAYS(B5,C5)</f>
-        <v>18</v>
-      </c>
-      <c r="F5" s="19">
-        <f ca="1">NETWORKDAYS(C5,D5)-2</f>
-        <v>3</v>
+      <c r="E5" s="20">
+        <f ca="1">NETWORKDAYS(B5,C5)-1</f>
+        <v>17</v>
+      </c>
+      <c r="F5" s="18">
+        <f ca="1">NETWORKDAYS(C5,D5)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FC855B-6E09-4509-94D8-33CD3D56A4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE4776E-F7B4-4E55-A351-FE5F177985DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -420,10 +420,10 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -461,17 +461,11 @@
       <sheetData sheetId="0">
         <row r="117">
           <cell r="G117">
-            <v>415844</v>
+            <v>437550</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="O2">
-            <v>1510</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -507,6 +501,7 @@
       <sheetName val="INVENTARIO NACIONAL 22-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 23-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -514,154 +509,154 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="C4">
-            <v>19244</v>
+            <v>20321</v>
           </cell>
           <cell r="D4">
-            <v>1132</v>
+            <v>1128.9444444444443</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1282</v>
+            <v>1383</v>
           </cell>
           <cell r="D5">
-            <v>75.411764705882348</v>
+            <v>76.833333333333329</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>9264</v>
+            <v>9742</v>
           </cell>
           <cell r="D6">
-            <v>544.94117647058829</v>
+            <v>541.22222222222217</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1661</v>
+            <v>1708</v>
           </cell>
           <cell r="D7">
-            <v>97.705882352941174</v>
+            <v>94.888888888888886</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>289</v>
+            <v>308</v>
           </cell>
           <cell r="D8">
-            <v>17</v>
+            <v>17.111111111111111</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>21428</v>
+            <v>22713</v>
           </cell>
           <cell r="D9">
-            <v>1260.4705882352941</v>
+            <v>1261.8333333333333</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2017</v>
+            <v>2107</v>
           </cell>
           <cell r="D10">
-            <v>118.64705882352941</v>
+            <v>117.05555555555556</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>4806</v>
+            <v>5094</v>
           </cell>
           <cell r="D11">
-            <v>282.70588235294116</v>
+            <v>283</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>10925</v>
+            <v>11445</v>
           </cell>
           <cell r="D12">
-            <v>642.64705882352939</v>
+            <v>635.83333333333337</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>6325</v>
+            <v>6557</v>
           </cell>
           <cell r="D13">
-            <v>372.05882352941177</v>
+            <v>364.27777777777777</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>54660</v>
+            <v>58109</v>
           </cell>
           <cell r="D14">
-            <v>3215.294117647059</v>
+            <v>3228.2777777777778</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>36825</v>
+            <v>38934</v>
           </cell>
           <cell r="D15">
-            <v>2166.1764705882351</v>
+            <v>2163</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>36606</v>
+            <v>38638</v>
           </cell>
           <cell r="D16">
-            <v>2153.294117647059</v>
+            <v>2146.5555555555557</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>40543</v>
+            <v>42932</v>
           </cell>
           <cell r="D17">
-            <v>2384.8823529411766</v>
+            <v>2385.1111111111113</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>2281</v>
+            <v>2387</v>
           </cell>
           <cell r="D18">
-            <v>134.1764705882353</v>
+            <v>132.61111111111111</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>3613</v>
+            <v>3858</v>
           </cell>
           <cell r="D19">
-            <v>212.52941176470588</v>
+            <v>214.33333333333334</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>2646</v>
+            <v>2712</v>
           </cell>
           <cell r="D20">
-            <v>155.64705882352942</v>
+            <v>150.66666666666666</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>8211</v>
+            <v>8570</v>
           </cell>
           <cell r="D21">
-            <v>483</v>
+            <v>476.11111111111109</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>13716</v>
+            <v>14310</v>
           </cell>
           <cell r="D22">
-            <v>806.82352941176475</v>
+            <v>795</v>
           </cell>
         </row>
         <row r="23">
@@ -669,7 +664,7 @@
             <v>110</v>
           </cell>
           <cell r="D23">
-            <v>6.4705882352941178</v>
+            <v>6.1111111111111107</v>
           </cell>
         </row>
         <row r="24">
@@ -677,175 +672,175 @@
             <v>890</v>
           </cell>
           <cell r="D24">
-            <v>52.352941176470587</v>
+            <v>49.444444444444443</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>11866</v>
+            <v>12438</v>
           </cell>
           <cell r="D25">
-            <v>698</v>
+            <v>691</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>18440</v>
+            <v>19701</v>
           </cell>
           <cell r="D26">
-            <v>1084.7058823529412</v>
+            <v>1094.5</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>8047</v>
+            <v>8401</v>
           </cell>
           <cell r="D27">
-            <v>473.35294117647061</v>
+            <v>466.72222222222223</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>6254</v>
+            <v>6620</v>
           </cell>
           <cell r="D28">
-            <v>367.88235294117646</v>
+            <v>367.77777777777777</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>1841</v>
+            <v>1921</v>
           </cell>
           <cell r="D29">
-            <v>108.29411764705883</v>
+            <v>106.72222222222223</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>2009</v>
+            <v>2124</v>
           </cell>
           <cell r="D30">
-            <v>118.17647058823529</v>
+            <v>118</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>13571</v>
+            <v>14262</v>
           </cell>
           <cell r="D31">
-            <v>798.29411764705878</v>
+            <v>792.33333333333337</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>11386</v>
+            <v>11797</v>
           </cell>
           <cell r="D32">
-            <v>669.76470588235293</v>
+            <v>655.38888888888891</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>14188</v>
+            <v>14867</v>
           </cell>
           <cell r="D33">
-            <v>834.58823529411768</v>
+            <v>825.94444444444446</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>9633</v>
+            <v>10085</v>
           </cell>
           <cell r="D34">
-            <v>566.64705882352939</v>
+            <v>560.27777777777783</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>3669</v>
+            <v>3803</v>
           </cell>
           <cell r="D35">
-            <v>215.8235294117647</v>
+            <v>211.27777777777777</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>3171</v>
+            <v>3808</v>
           </cell>
           <cell r="D36">
-            <v>186.52941176470588</v>
+            <v>211.55555555555554</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>5952</v>
+            <v>6380</v>
           </cell>
           <cell r="D37">
-            <v>350.11764705882354</v>
+            <v>354.44444444444446</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>4621</v>
+            <v>4876</v>
           </cell>
           <cell r="D38">
-            <v>271.8235294117647</v>
+            <v>270.88888888888891</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>6813</v>
+            <v>7330</v>
           </cell>
           <cell r="D39">
-            <v>400.76470588235293</v>
+            <v>407.22222222222223</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>4214</v>
+            <v>4369</v>
           </cell>
           <cell r="D40">
-            <v>247.88235294117646</v>
+            <v>242.72222222222223</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>4341</v>
+            <v>4622</v>
           </cell>
           <cell r="D41">
-            <v>255.35294117647058</v>
+            <v>256.77777777777777</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>842</v>
+            <v>938</v>
           </cell>
           <cell r="D42">
-            <v>49.529411764705884</v>
+            <v>52.111111111111114</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1370</v>
+            <v>1534</v>
           </cell>
           <cell r="D43">
-            <v>80.588235294117652</v>
+            <v>85.222222222222229</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>602</v>
+            <v>638</v>
           </cell>
           <cell r="D44">
-            <v>35.411764705882355</v>
+            <v>35.444444444444443</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>720</v>
+            <v>750</v>
           </cell>
           <cell r="D45">
-            <v>42.352941176470587</v>
+            <v>41.666666666666664</v>
           </cell>
         </row>
         <row r="46">
@@ -853,22 +848,22 @@
             <v>10</v>
           </cell>
           <cell r="D46">
-            <v>0.58823529411764708</v>
+            <v>0.55555555555555558</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>54</v>
+            <v>55</v>
           </cell>
           <cell r="D47">
-            <v>3.1764705882352939</v>
+            <v>3.0555555555555554</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="3">
           <cell r="K3">
-            <v>410956</v>
+            <v>434157</v>
           </cell>
         </row>
       </sheetData>
@@ -888,6 +883,7 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1232,11 +1228,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>19244</v>
+        <v>20321</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1132</v>
+        <v>1128.9444444444443</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1248,11 +1244,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1282</v>
+        <v>1383</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>75.411764705882348</v>
+        <v>76.833333333333329</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1264,11 +1260,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>9264</v>
+        <v>9742</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>544.94117647058829</v>
+        <v>541.22222222222217</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1280,11 +1276,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1661</v>
+        <v>1708</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>97.705882352941174</v>
+        <v>94.888888888888886</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1296,11 +1292,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>17</v>
+        <v>17.111111111111111</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1312,11 +1308,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>21428</v>
+        <v>22713</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1260.4705882352941</v>
+        <v>1261.8333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1328,11 +1324,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2017</v>
+        <v>2107</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>118.64705882352941</v>
+        <v>117.05555555555556</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1344,11 +1340,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>4806</v>
+        <v>5094</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>282.70588235294116</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1360,11 +1356,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>10925</v>
+        <v>11445</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>642.64705882352939</v>
+        <v>635.83333333333337</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1376,11 +1372,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>6325</v>
+        <v>6557</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>372.05882352941177</v>
+        <v>364.27777777777777</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1392,11 +1388,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>54660</v>
+        <v>58109</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3215.294117647059</v>
+        <v>3228.2777777777778</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1408,11 +1404,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>36825</v>
+        <v>38934</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2166.1764705882351</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,11 +1420,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>36606</v>
+        <v>38638</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2153.294117647059</v>
+        <v>2146.5555555555557</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1440,11 +1436,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>40543</v>
+        <v>42932</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2384.8823529411766</v>
+        <v>2385.1111111111113</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1456,11 +1452,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>2281</v>
+        <v>2387</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>134.1764705882353</v>
+        <v>132.61111111111111</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1472,11 +1468,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>3613</v>
+        <v>3858</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>212.52941176470588</v>
+        <v>214.33333333333334</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1488,11 +1484,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>2646</v>
+        <v>2712</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>155.64705882352942</v>
+        <v>150.66666666666666</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1504,11 +1500,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>8211</v>
+        <v>8570</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>483</v>
+        <v>476.11111111111109</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,11 +1516,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>13716</v>
+        <v>14310</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>806.82352941176475</v>
+        <v>795</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1540,7 +1536,7 @@
       </c>
       <c r="D21" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>6.4705882352941178</v>
+        <v>6.1111111111111107</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1556,7 +1552,7 @@
       </c>
       <c r="D22" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>52.352941176470587</v>
+        <v>49.444444444444443</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1568,11 +1564,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>11866</v>
+        <v>12438</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>698</v>
+        <v>691</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1584,11 +1580,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>18440</v>
+        <v>19701</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>1084.7058823529412</v>
+        <v>1094.5</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,11 +1596,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>8047</v>
+        <v>8401</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>473.35294117647061</v>
+        <v>466.72222222222223</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1616,11 +1612,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>6254</v>
+        <v>6620</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>367.88235294117646</v>
+        <v>367.77777777777777</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,11 +1628,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1841</v>
+        <v>1921</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>108.29411764705883</v>
+        <v>106.72222222222223</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1648,11 +1644,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>2009</v>
+        <v>2124</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>118.17647058823529</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,11 +1660,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>13571</v>
+        <v>14262</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>798.29411764705878</v>
+        <v>792.33333333333337</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1680,11 +1676,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>11386</v>
+        <v>11797</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>669.76470588235293</v>
+        <v>655.38888888888891</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1696,11 +1692,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>14188</v>
+        <v>14867</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>834.58823529411768</v>
+        <v>825.94444444444446</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1712,11 +1708,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>9633</v>
+        <v>10085</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>566.64705882352939</v>
+        <v>560.27777777777783</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1728,11 +1724,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>3669</v>
+        <v>3803</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>215.8235294117647</v>
+        <v>211.27777777777777</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1744,11 +1740,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>3171</v>
+        <v>3808</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>186.52941176470588</v>
+        <v>211.55555555555554</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1760,11 +1756,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>5952</v>
+        <v>6380</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>350.11764705882354</v>
+        <v>354.44444444444446</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1776,11 +1772,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>4621</v>
+        <v>4876</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>271.8235294117647</v>
+        <v>270.88888888888891</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1792,11 +1788,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>6813</v>
+        <v>7330</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>400.76470588235293</v>
+        <v>407.22222222222223</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1808,11 +1804,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>4214</v>
+        <v>4369</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>247.88235294117646</v>
+        <v>242.72222222222223</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1824,11 +1820,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>4341</v>
+        <v>4622</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>255.35294117647058</v>
+        <v>256.77777777777777</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1840,11 +1836,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>842</v>
+        <v>938</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>49.529411764705884</v>
+        <v>52.111111111111114</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1856,11 +1852,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1370</v>
+        <v>1534</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>80.588235294117652</v>
+        <v>85.222222222222229</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1872,11 +1868,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>35.411764705882355</v>
+        <v>35.444444444444443</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1888,11 +1884,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>42.352941176470587</v>
+        <v>41.666666666666664</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1906,7 +1902,7 @@
       </c>
       <c r="D44" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.58823529411764708</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1916,11 +1912,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>3.1764705882352939</v>
+        <v>3.0555555555555554</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1941,15 +1937,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1977,30 +1973,30 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VENTAS JULIO'!$G$117</f>
-        <v>415844</v>
+        <v>437550</v>
       </c>
       <c r="B3" s="3">
         <f>'[2]DESV. VTS BY SKU'!$K$3</f>
-        <v>410956</v>
+        <v>434157</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">A3/E5</f>
-        <v>24461.411764705881</v>
+        <v>24308.333333333332</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">C3*22</f>
-        <v>538151.0588235294</v>
+        <v>534783.33333333326</v>
       </c>
       <c r="E3" s="4">
         <v>696207</v>
       </c>
       <c r="F3" s="6">
         <f>A3/E3</f>
-        <v>0.59729936642406645</v>
+        <v>0.62847687541205421</v>
       </c>
       <c r="G3" s="7">
         <f>A3-E3</f>
-        <v>-280363</v>
+        <v>-258657</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2026,21 +2022,21 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>A3-B3</f>
-        <v>4888</v>
+        <v>3393</v>
       </c>
       <c r="B5" s="17">
         <v>46204</v>
       </c>
       <c r="C5" s="17">
         <f ca="1">TODAY()-1</f>
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="D5" s="17">
         <v>46234</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="19">
         <f ca="1">NETWORKDAYS(B5,C5)-1</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="18">
         <f ca="1">NETWORKDAYS(C5,D5)</f>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE4776E-F7B4-4E55-A351-FE5F177985DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2383F2-0EBB-442E-9F76-C45315137C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -461,14 +461,20 @@
       <sheetData sheetId="0">
         <row r="117">
           <cell r="G117">
-            <v>437550</v>
+            <v>469155</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="S2">
+            <v>1217</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -502,6 +508,7 @@
       <sheetName val="INVENTARIO NACIONAL 23-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 29-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -509,154 +516,154 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="C4">
-            <v>20321</v>
+            <v>21538</v>
           </cell>
           <cell r="D4">
-            <v>1128.9444444444443</v>
+            <v>1133.578947368421</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1383</v>
+            <v>1466</v>
           </cell>
           <cell r="D5">
-            <v>76.833333333333329</v>
+            <v>77.15789473684211</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>9742</v>
+            <v>10333</v>
           </cell>
           <cell r="D6">
-            <v>541.22222222222217</v>
+            <v>543.84210526315792</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1708</v>
+            <v>1808</v>
           </cell>
           <cell r="D7">
-            <v>94.888888888888886</v>
+            <v>95.15789473684211</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>308</v>
+            <v>329</v>
           </cell>
           <cell r="D8">
-            <v>17.111111111111111</v>
+            <v>17.315789473684209</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>22713</v>
+            <v>23882</v>
           </cell>
           <cell r="D9">
-            <v>1261.8333333333333</v>
+            <v>1256.9473684210527</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2107</v>
+            <v>2304</v>
           </cell>
           <cell r="D10">
-            <v>117.05555555555556</v>
+            <v>121.26315789473684</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>5094</v>
+            <v>5468</v>
           </cell>
           <cell r="D11">
-            <v>283</v>
+            <v>287.78947368421052</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>11445</v>
+            <v>12751</v>
           </cell>
           <cell r="D12">
-            <v>635.83333333333337</v>
+            <v>671.10526315789468</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>6557</v>
+            <v>7473</v>
           </cell>
           <cell r="D13">
-            <v>364.27777777777777</v>
+            <v>393.31578947368422</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>58109</v>
+            <v>62089</v>
           </cell>
           <cell r="D14">
-            <v>3228.2777777777778</v>
+            <v>3267.8421052631579</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>38934</v>
+            <v>41509</v>
           </cell>
           <cell r="D15">
-            <v>2163</v>
+            <v>2184.6842105263158</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>38638</v>
+            <v>41342</v>
           </cell>
           <cell r="D16">
-            <v>2146.5555555555557</v>
+            <v>2175.8947368421054</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>42932</v>
+            <v>46139</v>
           </cell>
           <cell r="D17">
-            <v>2385.1111111111113</v>
+            <v>2428.3684210526317</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>2387</v>
+            <v>2586</v>
           </cell>
           <cell r="D18">
-            <v>132.61111111111111</v>
+            <v>136.10526315789474</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>3858</v>
+            <v>4256</v>
           </cell>
           <cell r="D19">
-            <v>214.33333333333334</v>
+            <v>224</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>2712</v>
+            <v>2917</v>
           </cell>
           <cell r="D20">
-            <v>150.66666666666666</v>
+            <v>153.52631578947367</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>8570</v>
+            <v>9375</v>
           </cell>
           <cell r="D21">
-            <v>476.11111111111109</v>
+            <v>493.42105263157896</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>14310</v>
+            <v>15649</v>
           </cell>
           <cell r="D22">
-            <v>795</v>
+            <v>823.63157894736844</v>
           </cell>
         </row>
         <row r="23">
@@ -664,183 +671,183 @@
             <v>110</v>
           </cell>
           <cell r="D23">
-            <v>6.1111111111111107</v>
+            <v>5.7894736842105265</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>890</v>
+            <v>1010</v>
           </cell>
           <cell r="D24">
-            <v>49.444444444444443</v>
+            <v>53.157894736842103</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>12438</v>
+            <v>13088</v>
           </cell>
           <cell r="D25">
-            <v>691</v>
+            <v>688.84210526315792</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>19701</v>
+            <v>20780</v>
           </cell>
           <cell r="D26">
-            <v>1094.5</v>
+            <v>1093.6842105263158</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>8401</v>
+            <v>9054</v>
           </cell>
           <cell r="D27">
-            <v>466.72222222222223</v>
+            <v>476.5263157894737</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>6620</v>
+            <v>7176</v>
           </cell>
           <cell r="D28">
-            <v>367.77777777777777</v>
+            <v>377.68421052631578</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>1921</v>
+            <v>2114</v>
           </cell>
           <cell r="D29">
-            <v>106.72222222222223</v>
+            <v>111.26315789473684</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>2124</v>
+            <v>2365</v>
           </cell>
           <cell r="D30">
-            <v>118</v>
+            <v>124.47368421052632</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>14262</v>
+            <v>15225</v>
           </cell>
           <cell r="D31">
-            <v>792.33333333333337</v>
+            <v>801.31578947368416</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>11797</v>
+            <v>12504</v>
           </cell>
           <cell r="D32">
-            <v>655.38888888888891</v>
+            <v>658.10526315789468</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>14867</v>
+            <v>15988</v>
           </cell>
           <cell r="D33">
-            <v>825.94444444444446</v>
+            <v>841.47368421052636</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>10085</v>
+            <v>10679</v>
           </cell>
           <cell r="D34">
-            <v>560.27777777777783</v>
+            <v>562.0526315789474</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>3803</v>
+            <v>4051</v>
           </cell>
           <cell r="D35">
-            <v>211.27777777777777</v>
+            <v>213.21052631578948</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>3808</v>
+            <v>4486</v>
           </cell>
           <cell r="D36">
-            <v>211.55555555555554</v>
+            <v>236.10526315789474</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>6380</v>
+            <v>6922</v>
           </cell>
           <cell r="D37">
-            <v>354.44444444444446</v>
+            <v>364.31578947368422</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>4876</v>
+            <v>5205</v>
           </cell>
           <cell r="D38">
-            <v>270.88888888888891</v>
+            <v>273.94736842105266</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>7330</v>
+            <v>7928</v>
           </cell>
           <cell r="D39">
-            <v>407.22222222222223</v>
+            <v>417.26315789473682</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>4369</v>
+            <v>4630</v>
           </cell>
           <cell r="D40">
-            <v>242.72222222222223</v>
+            <v>243.68421052631578</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>4622</v>
+            <v>5010</v>
           </cell>
           <cell r="D41">
-            <v>256.77777777777777</v>
+            <v>263.68421052631578</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>938</v>
+            <v>976</v>
           </cell>
           <cell r="D42">
-            <v>52.111111111111114</v>
+            <v>51.368421052631582</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1534</v>
+            <v>1621</v>
           </cell>
           <cell r="D43">
-            <v>85.222222222222229</v>
+            <v>85.315789473684205</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>638</v>
+            <v>654</v>
           </cell>
           <cell r="D44">
-            <v>35.444444444444443</v>
+            <v>34.421052631578945</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>750</v>
+            <v>787</v>
           </cell>
           <cell r="D45">
-            <v>41.666666666666664</v>
+            <v>41.421052631578945</v>
           </cell>
         </row>
         <row r="46">
@@ -848,7 +855,7 @@
             <v>10</v>
           </cell>
           <cell r="D46">
-            <v>0.55555555555555558</v>
+            <v>0.52631578947368418</v>
           </cell>
         </row>
         <row r="47">
@@ -856,14 +863,14 @@
             <v>55</v>
           </cell>
           <cell r="D47">
-            <v>3.0555555555555554</v>
+            <v>2.8947368421052633</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="3">
           <cell r="K3">
-            <v>434157</v>
+            <v>465642</v>
           </cell>
         </row>
       </sheetData>
@@ -884,6 +891,7 @@
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1228,11 +1236,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>20321</v>
+        <v>21538</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1128.9444444444443</v>
+        <v>1133.578947368421</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1244,11 +1252,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1383</v>
+        <v>1466</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>76.833333333333329</v>
+        <v>77.15789473684211</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1260,11 +1268,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>9742</v>
+        <v>10333</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>541.22222222222217</v>
+        <v>543.84210526315792</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1276,11 +1284,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1708</v>
+        <v>1808</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>94.888888888888886</v>
+        <v>95.15789473684211</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1292,11 +1300,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>17.111111111111111</v>
+        <v>17.315789473684209</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1308,11 +1316,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>22713</v>
+        <v>23882</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1261.8333333333333</v>
+        <v>1256.9473684210527</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1324,11 +1332,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2107</v>
+        <v>2304</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>117.05555555555556</v>
+        <v>121.26315789473684</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,11 +1348,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>5094</v>
+        <v>5468</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>283</v>
+        <v>287.78947368421052</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1356,11 +1364,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>11445</v>
+        <v>12751</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>635.83333333333337</v>
+        <v>671.10526315789468</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1372,11 +1380,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>6557</v>
+        <v>7473</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>364.27777777777777</v>
+        <v>393.31578947368422</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1388,11 +1396,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>58109</v>
+        <v>62089</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3228.2777777777778</v>
+        <v>3267.8421052631579</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1404,11 +1412,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>38934</v>
+        <v>41509</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2163</v>
+        <v>2184.6842105263158</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1420,11 +1428,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>38638</v>
+        <v>41342</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2146.5555555555557</v>
+        <v>2175.8947368421054</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,11 +1444,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>42932</v>
+        <v>46139</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2385.1111111111113</v>
+        <v>2428.3684210526317</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,11 +1460,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>2387</v>
+        <v>2586</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>132.61111111111111</v>
+        <v>136.10526315789474</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1468,11 +1476,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>3858</v>
+        <v>4256</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>214.33333333333334</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1484,11 +1492,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>2712</v>
+        <v>2917</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>150.66666666666666</v>
+        <v>153.52631578947367</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,11 +1508,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>8570</v>
+        <v>9375</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>476.11111111111109</v>
+        <v>493.42105263157896</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1516,11 +1524,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>14310</v>
+        <v>15649</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>795</v>
+        <v>823.63157894736844</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,7 +1544,7 @@
       </c>
       <c r="D21" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>6.1111111111111107</v>
+        <v>5.7894736842105265</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,11 +1556,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>890</v>
+        <v>1010</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>49.444444444444443</v>
+        <v>53.157894736842103</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1564,11 +1572,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>12438</v>
+        <v>13088</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>691</v>
+        <v>688.84210526315792</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1580,11 +1588,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>19701</v>
+        <v>20780</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>1094.5</v>
+        <v>1093.6842105263158</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1596,11 +1604,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>8401</v>
+        <v>9054</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>466.72222222222223</v>
+        <v>476.5263157894737</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1612,11 +1620,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>6620</v>
+        <v>7176</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>367.77777777777777</v>
+        <v>377.68421052631578</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1628,11 +1636,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1921</v>
+        <v>2114</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>106.72222222222223</v>
+        <v>111.26315789473684</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,11 +1652,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>2124</v>
+        <v>2365</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>118</v>
+        <v>124.47368421052632</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,11 +1668,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>14262</v>
+        <v>15225</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>792.33333333333337</v>
+        <v>801.31578947368416</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1676,11 +1684,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>11797</v>
+        <v>12504</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>655.38888888888891</v>
+        <v>658.10526315789468</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1692,11 +1700,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>14867</v>
+        <v>15988</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>825.94444444444446</v>
+        <v>841.47368421052636</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1708,11 +1716,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>10085</v>
+        <v>10679</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>560.27777777777783</v>
+        <v>562.0526315789474</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1724,11 +1732,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>3803</v>
+        <v>4051</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>211.27777777777777</v>
+        <v>213.21052631578948</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1740,11 +1748,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>3808</v>
+        <v>4486</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>211.55555555555554</v>
+        <v>236.10526315789474</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1756,11 +1764,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>6380</v>
+        <v>6922</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>354.44444444444446</v>
+        <v>364.31578947368422</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1772,11 +1780,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>4876</v>
+        <v>5205</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>270.88888888888891</v>
+        <v>273.94736842105266</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,11 +1796,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>7330</v>
+        <v>7928</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>407.22222222222223</v>
+        <v>417.26315789473682</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1804,11 +1812,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>4369</v>
+        <v>4630</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>242.72222222222223</v>
+        <v>243.68421052631578</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1820,11 +1828,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>4622</v>
+        <v>5010</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>256.77777777777777</v>
+        <v>263.68421052631578</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1836,11 +1844,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>938</v>
+        <v>976</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>52.111111111111114</v>
+        <v>51.368421052631582</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1852,11 +1860,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1534</v>
+        <v>1621</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>85.222222222222229</v>
+        <v>85.315789473684205</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1868,11 +1876,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>35.444444444444443</v>
+        <v>34.421052631578945</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,11 +1892,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>41.666666666666664</v>
+        <v>41.421052631578945</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1902,7 +1910,7 @@
       </c>
       <c r="D44" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.55555555555555558</v>
+        <v>0.52631578947368418</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1916,7 +1924,7 @@
       </c>
       <c r="D45" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>3.0555555555555554</v>
+        <v>2.8947368421052633</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1973,30 +1981,30 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VENTAS JULIO'!$G$117</f>
-        <v>437550</v>
+        <v>469155</v>
       </c>
       <c r="B3" s="3">
         <f>'[2]DESV. VTS BY SKU'!$K$3</f>
-        <v>434157</v>
+        <v>465642</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">A3/E5</f>
-        <v>24308.333333333332</v>
+        <v>24692.36842105263</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">C3*22</f>
-        <v>534783.33333333326</v>
+        <v>543232.10526315786</v>
       </c>
       <c r="E3" s="4">
         <v>696207</v>
       </c>
       <c r="F3" s="6">
         <f>A3/E3</f>
-        <v>0.62847687541205421</v>
+        <v>0.67387285677966469</v>
       </c>
       <c r="G3" s="7">
         <f>A3-E3</f>
-        <v>-258657</v>
+        <v>-227052</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2022,25 +2030,25 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>A3-B3</f>
-        <v>3393</v>
+        <v>3513</v>
       </c>
       <c r="B5" s="17">
         <v>46204</v>
       </c>
       <c r="C5" s="17">
         <f ca="1">TODAY()-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="D5" s="17">
         <v>46234</v>
       </c>
       <c r="E5" s="19">
         <f ca="1">NETWORKDAYS(B5,C5)-1</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="18">
         <f ca="1">NETWORKDAYS(C5,D5)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2383F2-0EBB-442E-9F76-C45315137C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AEABC1-5FED-40DD-8921-A04FB8E73A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -461,20 +461,14 @@
       <sheetData sheetId="0">
         <row r="117">
           <cell r="G117">
-            <v>469155</v>
+            <v>503437</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="S2">
-            <v>1217</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -509,6 +503,7 @@
       <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 29-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 30-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -516,154 +511,154 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="C4">
-            <v>21538</v>
+            <v>23127</v>
           </cell>
           <cell r="D4">
-            <v>1133.578947368421</v>
+            <v>1156.3499999999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1466</v>
+            <v>1569</v>
           </cell>
           <cell r="D5">
-            <v>77.15789473684211</v>
+            <v>78.45</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>10333</v>
+            <v>11440</v>
           </cell>
           <cell r="D6">
-            <v>543.84210526315792</v>
+            <v>572</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1808</v>
+            <v>1950</v>
           </cell>
           <cell r="D7">
-            <v>95.15789473684211</v>
+            <v>97.5</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>329</v>
+            <v>359</v>
           </cell>
           <cell r="D8">
-            <v>17.315789473684209</v>
+            <v>17.95</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>23882</v>
+            <v>26238</v>
           </cell>
           <cell r="D9">
-            <v>1256.9473684210527</v>
+            <v>1311.9</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2304</v>
+            <v>2433</v>
           </cell>
           <cell r="D10">
-            <v>121.26315789473684</v>
+            <v>121.65</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>5468</v>
+            <v>6009</v>
           </cell>
           <cell r="D11">
-            <v>287.78947368421052</v>
+            <v>300.45</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>12751</v>
+            <v>13501</v>
           </cell>
           <cell r="D12">
-            <v>671.10526315789468</v>
+            <v>675.05</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>7473</v>
+            <v>8241</v>
           </cell>
           <cell r="D13">
-            <v>393.31578947368422</v>
+            <v>412.05</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>62089</v>
+            <v>66529</v>
           </cell>
           <cell r="D14">
-            <v>3267.8421052631579</v>
+            <v>3326.45</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>41509</v>
+            <v>44590</v>
           </cell>
           <cell r="D15">
-            <v>2184.6842105263158</v>
+            <v>2229.5</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>41342</v>
+            <v>44337</v>
           </cell>
           <cell r="D16">
-            <v>2175.8947368421054</v>
+            <v>2216.85</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>46139</v>
+            <v>49325</v>
           </cell>
           <cell r="D17">
-            <v>2428.3684210526317</v>
+            <v>2466.25</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>2586</v>
+            <v>2775</v>
           </cell>
           <cell r="D18">
-            <v>136.10526315789474</v>
+            <v>138.75</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>4256</v>
+            <v>4589</v>
           </cell>
           <cell r="D19">
-            <v>224</v>
+            <v>229.45</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>2917</v>
+            <v>3088</v>
           </cell>
           <cell r="D20">
-            <v>153.52631578947367</v>
+            <v>154.4</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>9375</v>
+            <v>9953</v>
           </cell>
           <cell r="D21">
-            <v>493.42105263157896</v>
+            <v>497.65</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>15649</v>
+            <v>16438</v>
           </cell>
           <cell r="D22">
-            <v>823.63157894736844</v>
+            <v>821.9</v>
           </cell>
         </row>
         <row r="23">
@@ -671,206 +666,206 @@
             <v>110</v>
           </cell>
           <cell r="D23">
-            <v>5.7894736842105265</v>
+            <v>5.5</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>1010</v>
+            <v>1072</v>
           </cell>
           <cell r="D24">
-            <v>53.157894736842103</v>
+            <v>53.6</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>13088</v>
+            <v>13906</v>
           </cell>
           <cell r="D25">
-            <v>688.84210526315792</v>
+            <v>695.3</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>20780</v>
+            <v>22452</v>
           </cell>
           <cell r="D26">
-            <v>1093.6842105263158</v>
+            <v>1122.5999999999999</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>9054</v>
+            <v>9668</v>
           </cell>
           <cell r="D27">
-            <v>476.5263157894737</v>
+            <v>483.4</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>7176</v>
+            <v>7541</v>
           </cell>
           <cell r="D28">
-            <v>377.68421052631578</v>
+            <v>377.05</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>2114</v>
+            <v>2227</v>
           </cell>
           <cell r="D29">
-            <v>111.26315789473684</v>
+            <v>111.35</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>2365</v>
+            <v>2500</v>
           </cell>
           <cell r="D30">
-            <v>124.47368421052632</v>
+            <v>125</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>15225</v>
+            <v>16134</v>
           </cell>
           <cell r="D31">
-            <v>801.31578947368416</v>
+            <v>806.7</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>12504</v>
+            <v>13159</v>
           </cell>
           <cell r="D32">
-            <v>658.10526315789468</v>
+            <v>657.95</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>15988</v>
+            <v>16913</v>
           </cell>
           <cell r="D33">
-            <v>841.47368421052636</v>
+            <v>845.65</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>10679</v>
+            <v>11479</v>
           </cell>
           <cell r="D34">
-            <v>562.0526315789474</v>
+            <v>573.95000000000005</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>4051</v>
+            <v>4339</v>
           </cell>
           <cell r="D35">
-            <v>213.21052631578948</v>
+            <v>216.95</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>4486</v>
+            <v>5475</v>
           </cell>
           <cell r="D36">
-            <v>236.10526315789474</v>
+            <v>273.75</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>6922</v>
+            <v>7601</v>
           </cell>
           <cell r="D37">
-            <v>364.31578947368422</v>
+            <v>380.05</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>5205</v>
+            <v>5558</v>
           </cell>
           <cell r="D38">
-            <v>273.94736842105266</v>
+            <v>277.89999999999998</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>7928</v>
+            <v>8573</v>
           </cell>
           <cell r="D39">
-            <v>417.26315789473682</v>
+            <v>428.65</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>4630</v>
+            <v>4918</v>
           </cell>
           <cell r="D40">
-            <v>243.68421052631578</v>
+            <v>245.9</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>5010</v>
+            <v>5380</v>
           </cell>
           <cell r="D41">
-            <v>263.68421052631578</v>
+            <v>269</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>976</v>
+            <v>1013</v>
           </cell>
           <cell r="D42">
-            <v>51.368421052631582</v>
+            <v>50.65</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1621</v>
+            <v>1667</v>
           </cell>
           <cell r="D43">
-            <v>85.315789473684205</v>
+            <v>83.35</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>654</v>
+            <v>688</v>
           </cell>
           <cell r="D44">
-            <v>34.421052631578945</v>
+            <v>34.4</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>787</v>
+            <v>795</v>
           </cell>
           <cell r="D45">
-            <v>41.421052631578945</v>
+            <v>39.75</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>10</v>
+            <v>18</v>
           </cell>
           <cell r="D46">
-            <v>0.52631578947368418</v>
+            <v>0.9</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>55</v>
+            <v>69</v>
           </cell>
           <cell r="D47">
-            <v>2.8947368421052633</v>
+            <v>3.45</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="3">
           <cell r="K3">
-            <v>465642</v>
+            <v>499746</v>
           </cell>
         </row>
       </sheetData>
@@ -892,6 +887,7 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1236,11 +1232,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>21538</v>
+        <v>23127</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1133.578947368421</v>
+        <v>1156.3499999999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1252,11 +1248,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1466</v>
+        <v>1569</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>77.15789473684211</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1268,11 +1264,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>10333</v>
+        <v>11440</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>543.84210526315792</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,11 +1280,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1808</v>
+        <v>1950</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>95.15789473684211</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1300,11 +1296,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>17.315789473684209</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1316,11 +1312,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>23882</v>
+        <v>26238</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1256.9473684210527</v>
+        <v>1311.9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1332,11 +1328,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2304</v>
+        <v>2433</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>121.26315789473684</v>
+        <v>121.65</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1348,11 +1344,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>5468</v>
+        <v>6009</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>287.78947368421052</v>
+        <v>300.45</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1364,11 +1360,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>12751</v>
+        <v>13501</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>671.10526315789468</v>
+        <v>675.05</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1380,11 +1376,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>7473</v>
+        <v>8241</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>393.31578947368422</v>
+        <v>412.05</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,11 +1392,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>62089</v>
+        <v>66529</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3267.8421052631579</v>
+        <v>3326.45</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1412,11 +1408,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>41509</v>
+        <v>44590</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2184.6842105263158</v>
+        <v>2229.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1428,11 +1424,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>41342</v>
+        <v>44337</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2175.8947368421054</v>
+        <v>2216.85</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1444,11 +1440,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>46139</v>
+        <v>49325</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2428.3684210526317</v>
+        <v>2466.25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1460,11 +1456,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>2586</v>
+        <v>2775</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>136.10526315789474</v>
+        <v>138.75</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,11 +1472,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>4256</v>
+        <v>4589</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>224</v>
+        <v>229.45</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,11 +1488,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>2917</v>
+        <v>3088</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>153.52631578947367</v>
+        <v>154.4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,11 +1504,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>9375</v>
+        <v>9953</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>493.42105263157896</v>
+        <v>497.65</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,11 +1520,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>15649</v>
+        <v>16438</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>823.63157894736844</v>
+        <v>821.9</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1544,7 +1540,7 @@
       </c>
       <c r="D21" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>5.7894736842105265</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1556,11 +1552,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>1010</v>
+        <v>1072</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>53.157894736842103</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1572,11 +1568,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>13088</v>
+        <v>13906</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>688.84210526315792</v>
+        <v>695.3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1588,11 +1584,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>20780</v>
+        <v>22452</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>1093.6842105263158</v>
+        <v>1122.5999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,11 +1600,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>9054</v>
+        <v>9668</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>476.5263157894737</v>
+        <v>483.4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,11 +1616,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>7176</v>
+        <v>7541</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>377.68421052631578</v>
+        <v>377.05</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,11 +1632,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>2114</v>
+        <v>2227</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>111.26315789473684</v>
+        <v>111.35</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1652,11 +1648,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>2365</v>
+        <v>2500</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>124.47368421052632</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1668,11 +1664,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>15225</v>
+        <v>16134</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>801.31578947368416</v>
+        <v>806.7</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1684,11 +1680,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>12504</v>
+        <v>13159</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>658.10526315789468</v>
+        <v>657.95</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1700,11 +1696,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>15988</v>
+        <v>16913</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>841.47368421052636</v>
+        <v>845.65</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,11 +1712,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>10679</v>
+        <v>11479</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>562.0526315789474</v>
+        <v>573.95000000000005</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1732,11 +1728,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>4051</v>
+        <v>4339</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>213.21052631578948</v>
+        <v>216.95</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,11 +1744,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>4486</v>
+        <v>5475</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>236.10526315789474</v>
+        <v>273.75</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1764,11 +1760,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>6922</v>
+        <v>7601</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>364.31578947368422</v>
+        <v>380.05</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1780,11 +1776,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>5205</v>
+        <v>5558</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>273.94736842105266</v>
+        <v>277.89999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1796,11 +1792,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>7928</v>
+        <v>8573</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>417.26315789473682</v>
+        <v>428.65</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,11 +1808,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>4630</v>
+        <v>4918</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>243.68421052631578</v>
+        <v>245.9</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1828,11 +1824,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>5010</v>
+        <v>5380</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>263.68421052631578</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1844,11 +1840,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>976</v>
+        <v>1013</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>51.368421052631582</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1860,11 +1856,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1621</v>
+        <v>1667</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>85.315789473684205</v>
+        <v>83.35</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,11 +1872,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>654</v>
+        <v>688</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>34.421052631578945</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1892,11 +1888,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>41.421052631578945</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1906,11 +1902,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.52631578947368418</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1920,11 +1916,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[2]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>2.8947368421052633</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1981,30 +1977,30 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VENTAS JULIO'!$G$117</f>
-        <v>469155</v>
+        <v>503437</v>
       </c>
       <c r="B3" s="3">
         <f>'[2]DESV. VTS BY SKU'!$K$3</f>
-        <v>465642</v>
+        <v>499746</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">A3/E5</f>
-        <v>24692.36842105263</v>
+        <v>25171.85</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">C3*22</f>
-        <v>543232.10526315786</v>
+        <v>553780.69999999995</v>
       </c>
       <c r="E3" s="4">
         <v>696207</v>
       </c>
       <c r="F3" s="6">
         <f>A3/E3</f>
-        <v>0.67387285677966469</v>
+        <v>0.72311395892313635</v>
       </c>
       <c r="G3" s="7">
         <f>A3-E3</f>
-        <v>-227052</v>
+        <v>-192770</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2030,25 +2026,25 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>A3-B3</f>
-        <v>3513</v>
+        <v>3691</v>
       </c>
       <c r="B5" s="17">
         <v>46204</v>
       </c>
       <c r="C5" s="17">
         <f ca="1">TODAY()-1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="D5" s="17">
         <v>46234</v>
       </c>
       <c r="E5" s="19">
         <f ca="1">NETWORKDAYS(B5,C5)-1</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="18">
-        <f ca="1">NETWORKDAYS(C5,D5)</f>
-        <v>4</v>
+        <f ca="1">NETWORKDAYS(C5,D5)-1</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AEABC1-5FED-40DD-8921-A04FB8E73A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65421E34-B1C0-46A8-86A9-F80C1CFD698D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -451,36 +451,6 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="VENTAS JULIO"/>
-      <sheetName val="VENTAS DIARIA POR SKU"/>
-      <sheetName val="DESPACHO"/>
-      <sheetName val="RELACION DE VIAJES"/>
-      <sheetName val="RELACION DE VIAJES SITES "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="117">
-          <cell r="G117">
-            <v>503437</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
       <sheetName val="INVENTARIO NACIONAL 03-07-26"/>
       <sheetName val="VINCULO VTS BY SKU JUNIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -504,6 +474,7 @@
       <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 29-07-26"/>
       <sheetName val="INVENTARIO NACIONAL 30-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 31-07-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -514,7 +485,7 @@
             <v>23127</v>
           </cell>
           <cell r="D4">
-            <v>1156.3499999999999</v>
+            <v>1051.2272727272727</v>
           </cell>
         </row>
         <row r="5">
@@ -522,7 +493,7 @@
             <v>1569</v>
           </cell>
           <cell r="D5">
-            <v>78.45</v>
+            <v>71.318181818181813</v>
           </cell>
         </row>
         <row r="6">
@@ -530,7 +501,7 @@
             <v>11440</v>
           </cell>
           <cell r="D6">
-            <v>572</v>
+            <v>520</v>
           </cell>
         </row>
         <row r="7">
@@ -538,7 +509,7 @@
             <v>1950</v>
           </cell>
           <cell r="D7">
-            <v>97.5</v>
+            <v>88.63636363636364</v>
           </cell>
         </row>
         <row r="8">
@@ -546,7 +517,7 @@
             <v>359</v>
           </cell>
           <cell r="D8">
-            <v>17.95</v>
+            <v>16.318181818181817</v>
           </cell>
         </row>
         <row r="9">
@@ -554,7 +525,7 @@
             <v>26238</v>
           </cell>
           <cell r="D9">
-            <v>1311.9</v>
+            <v>1192.6363636363637</v>
           </cell>
         </row>
         <row r="10">
@@ -562,7 +533,7 @@
             <v>2433</v>
           </cell>
           <cell r="D10">
-            <v>121.65</v>
+            <v>110.59090909090909</v>
           </cell>
         </row>
         <row r="11">
@@ -570,7 +541,7 @@
             <v>6009</v>
           </cell>
           <cell r="D11">
-            <v>300.45</v>
+            <v>273.13636363636363</v>
           </cell>
         </row>
         <row r="12">
@@ -578,7 +549,7 @@
             <v>13501</v>
           </cell>
           <cell r="D12">
-            <v>675.05</v>
+            <v>613.68181818181813</v>
           </cell>
         </row>
         <row r="13">
@@ -586,7 +557,7 @@
             <v>8241</v>
           </cell>
           <cell r="D13">
-            <v>412.05</v>
+            <v>374.59090909090907</v>
           </cell>
         </row>
         <row r="14">
@@ -594,7 +565,7 @@
             <v>66529</v>
           </cell>
           <cell r="D14">
-            <v>3326.45</v>
+            <v>3024.0454545454545</v>
           </cell>
         </row>
         <row r="15">
@@ -602,7 +573,7 @@
             <v>44590</v>
           </cell>
           <cell r="D15">
-            <v>2229.5</v>
+            <v>2026.8181818181818</v>
           </cell>
         </row>
         <row r="16">
@@ -610,7 +581,7 @@
             <v>44337</v>
           </cell>
           <cell r="D16">
-            <v>2216.85</v>
+            <v>2015.3181818181818</v>
           </cell>
         </row>
         <row r="17">
@@ -618,7 +589,7 @@
             <v>49325</v>
           </cell>
           <cell r="D17">
-            <v>2466.25</v>
+            <v>2242.0454545454545</v>
           </cell>
         </row>
         <row r="18">
@@ -626,7 +597,7 @@
             <v>2775</v>
           </cell>
           <cell r="D18">
-            <v>138.75</v>
+            <v>126.13636363636364</v>
           </cell>
         </row>
         <row r="19">
@@ -634,7 +605,7 @@
             <v>4589</v>
           </cell>
           <cell r="D19">
-            <v>229.45</v>
+            <v>208.59090909090909</v>
           </cell>
         </row>
         <row r="20">
@@ -642,7 +613,7 @@
             <v>3088</v>
           </cell>
           <cell r="D20">
-            <v>154.4</v>
+            <v>140.36363636363637</v>
           </cell>
         </row>
         <row r="21">
@@ -650,7 +621,7 @@
             <v>9953</v>
           </cell>
           <cell r="D21">
-            <v>497.65</v>
+            <v>452.40909090909093</v>
           </cell>
         </row>
         <row r="22">
@@ -658,7 +629,7 @@
             <v>16438</v>
           </cell>
           <cell r="D22">
-            <v>821.9</v>
+            <v>747.18181818181813</v>
           </cell>
         </row>
         <row r="23">
@@ -666,7 +637,7 @@
             <v>110</v>
           </cell>
           <cell r="D23">
-            <v>5.5</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="24">
@@ -674,7 +645,7 @@
             <v>1072</v>
           </cell>
           <cell r="D24">
-            <v>53.6</v>
+            <v>48.727272727272727</v>
           </cell>
         </row>
         <row r="25">
@@ -682,7 +653,7 @@
             <v>13906</v>
           </cell>
           <cell r="D25">
-            <v>695.3</v>
+            <v>632.09090909090912</v>
           </cell>
         </row>
         <row r="26">
@@ -690,7 +661,7 @@
             <v>22452</v>
           </cell>
           <cell r="D26">
-            <v>1122.5999999999999</v>
+            <v>1020.5454545454545</v>
           </cell>
         </row>
         <row r="27">
@@ -698,7 +669,7 @@
             <v>9668</v>
           </cell>
           <cell r="D27">
-            <v>483.4</v>
+            <v>439.45454545454544</v>
           </cell>
         </row>
         <row r="28">
@@ -706,7 +677,7 @@
             <v>7541</v>
           </cell>
           <cell r="D28">
-            <v>377.05</v>
+            <v>342.77272727272725</v>
           </cell>
         </row>
         <row r="29">
@@ -714,7 +685,7 @@
             <v>2227</v>
           </cell>
           <cell r="D29">
-            <v>111.35</v>
+            <v>101.22727272727273</v>
           </cell>
         </row>
         <row r="30">
@@ -722,7 +693,7 @@
             <v>2500</v>
           </cell>
           <cell r="D30">
-            <v>125</v>
+            <v>113.63636363636364</v>
           </cell>
         </row>
         <row r="31">
@@ -730,7 +701,7 @@
             <v>16134</v>
           </cell>
           <cell r="D31">
-            <v>806.7</v>
+            <v>733.36363636363637</v>
           </cell>
         </row>
         <row r="32">
@@ -738,7 +709,7 @@
             <v>13159</v>
           </cell>
           <cell r="D32">
-            <v>657.95</v>
+            <v>598.13636363636363</v>
           </cell>
         </row>
         <row r="33">
@@ -746,7 +717,7 @@
             <v>16913</v>
           </cell>
           <cell r="D33">
-            <v>845.65</v>
+            <v>768.77272727272725</v>
           </cell>
         </row>
         <row r="34">
@@ -754,7 +725,7 @@
             <v>11479</v>
           </cell>
           <cell r="D34">
-            <v>573.95000000000005</v>
+            <v>521.77272727272725</v>
           </cell>
         </row>
         <row r="35">
@@ -762,7 +733,7 @@
             <v>4339</v>
           </cell>
           <cell r="D35">
-            <v>216.95</v>
+            <v>197.22727272727272</v>
           </cell>
         </row>
         <row r="36">
@@ -770,7 +741,7 @@
             <v>5475</v>
           </cell>
           <cell r="D36">
-            <v>273.75</v>
+            <v>248.86363636363637</v>
           </cell>
         </row>
         <row r="37">
@@ -778,7 +749,7 @@
             <v>7601</v>
           </cell>
           <cell r="D37">
-            <v>380.05</v>
+            <v>345.5</v>
           </cell>
         </row>
         <row r="38">
@@ -786,7 +757,7 @@
             <v>5558</v>
           </cell>
           <cell r="D38">
-            <v>277.89999999999998</v>
+            <v>252.63636363636363</v>
           </cell>
         </row>
         <row r="39">
@@ -794,7 +765,7 @@
             <v>8573</v>
           </cell>
           <cell r="D39">
-            <v>428.65</v>
+            <v>389.68181818181819</v>
           </cell>
         </row>
         <row r="40">
@@ -802,7 +773,7 @@
             <v>4918</v>
           </cell>
           <cell r="D40">
-            <v>245.9</v>
+            <v>223.54545454545453</v>
           </cell>
         </row>
         <row r="41">
@@ -810,7 +781,7 @@
             <v>5380</v>
           </cell>
           <cell r="D41">
-            <v>269</v>
+            <v>244.54545454545453</v>
           </cell>
         </row>
         <row r="42">
@@ -818,7 +789,7 @@
             <v>1013</v>
           </cell>
           <cell r="D42">
-            <v>50.65</v>
+            <v>46.045454545454547</v>
           </cell>
         </row>
         <row r="43">
@@ -826,7 +797,7 @@
             <v>1667</v>
           </cell>
           <cell r="D43">
-            <v>83.35</v>
+            <v>75.772727272727266</v>
           </cell>
         </row>
         <row r="44">
@@ -834,7 +805,7 @@
             <v>688</v>
           </cell>
           <cell r="D44">
-            <v>34.4</v>
+            <v>31.272727272727273</v>
           </cell>
         </row>
         <row r="45">
@@ -842,7 +813,7 @@
             <v>795</v>
           </cell>
           <cell r="D45">
-            <v>39.75</v>
+            <v>36.136363636363633</v>
           </cell>
         </row>
         <row r="46">
@@ -850,7 +821,7 @@
             <v>18</v>
           </cell>
           <cell r="D46">
-            <v>0.9</v>
+            <v>0.81818181818181823</v>
           </cell>
         </row>
         <row r="47">
@@ -858,7 +829,7 @@
             <v>69</v>
           </cell>
           <cell r="D47">
-            <v>3.45</v>
+            <v>3.1363636363636362</v>
           </cell>
         </row>
       </sheetData>
@@ -888,6 +859,43 @@
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="VENTAS JULIO"/>
+      <sheetName val="VENTAS DIARIA POR SKU"/>
+      <sheetName val="DESPACHO"/>
+      <sheetName val="RELACION DE VIAJES"/>
+      <sheetName val="RELACION DE VIAJES SITES "/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="117">
+          <cell r="G117">
+            <v>503437</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="S2">
+            <v>1217</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1231,12 +1239,12 @@
         <v>4</v>
       </c>
       <c r="C2" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C4</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
         <v>23127</v>
       </c>
       <c r="D2" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1156.3499999999999</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
+        <v>1051.2272727272727</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1247,12 +1255,12 @@
         <v>5</v>
       </c>
       <c r="C3" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C5</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
         <v>1569</v>
       </c>
       <c r="D3" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>78.45</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
+        <v>71.318181818181813</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,12 +1271,12 @@
         <v>6</v>
       </c>
       <c r="C4" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C6</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
         <v>11440</v>
       </c>
       <c r="D4" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>572</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,12 +1287,12 @@
         <v>7</v>
       </c>
       <c r="C5" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C7</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
         <v>1950</v>
       </c>
       <c r="D5" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>97.5</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
+        <v>88.63636363636364</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,12 +1303,12 @@
         <v>8</v>
       </c>
       <c r="C6" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C8</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
         <v>359</v>
       </c>
       <c r="D6" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>17.95</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
+        <v>16.318181818181817</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1311,12 +1319,12 @@
         <v>9</v>
       </c>
       <c r="C7" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C9</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
         <v>26238</v>
       </c>
       <c r="D7" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1311.9</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
+        <v>1192.6363636363637</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1327,12 +1335,12 @@
         <v>10</v>
       </c>
       <c r="C8" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C10</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
         <v>2433</v>
       </c>
       <c r="D8" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>121.65</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
+        <v>110.59090909090909</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1343,12 +1351,12 @@
         <v>11</v>
       </c>
       <c r="C9" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C11</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
         <v>6009</v>
       </c>
       <c r="D9" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>300.45</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
+        <v>273.13636363636363</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1359,12 +1367,12 @@
         <v>12</v>
       </c>
       <c r="C10" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C12</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
         <v>13501</v>
       </c>
       <c r="D10" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>675.05</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
+        <v>613.68181818181813</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,12 +1383,12 @@
         <v>13</v>
       </c>
       <c r="C11" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C13</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
         <v>8241</v>
       </c>
       <c r="D11" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>412.05</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
+        <v>374.59090909090907</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1391,12 +1399,12 @@
         <v>14</v>
       </c>
       <c r="C12" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C14</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
         <v>66529</v>
       </c>
       <c r="D12" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3326.45</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
+        <v>3024.0454545454545</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1407,12 +1415,12 @@
         <v>15</v>
       </c>
       <c r="C13" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C15</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
         <v>44590</v>
       </c>
       <c r="D13" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2229.5</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
+        <v>2026.8181818181818</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1423,12 +1431,12 @@
         <v>16</v>
       </c>
       <c r="C14" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C16</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
         <v>44337</v>
       </c>
       <c r="D14" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2216.85</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
+        <v>2015.3181818181818</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1439,12 +1447,12 @@
         <v>17</v>
       </c>
       <c r="C15" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C17</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
         <v>49325</v>
       </c>
       <c r="D15" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2466.25</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
+        <v>2242.0454545454545</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1455,12 +1463,12 @@
         <v>18</v>
       </c>
       <c r="C16" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C18</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
         <v>2775</v>
       </c>
       <c r="D16" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>138.75</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
+        <v>126.13636363636364</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,12 +1479,12 @@
         <v>19</v>
       </c>
       <c r="C17" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C19</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
         <v>4589</v>
       </c>
       <c r="D17" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>229.45</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
+        <v>208.59090909090909</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1487,12 +1495,12 @@
         <v>20</v>
       </c>
       <c r="C18" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C20</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
         <v>3088</v>
       </c>
       <c r="D18" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>154.4</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
+        <v>140.36363636363637</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1503,12 +1511,12 @@
         <v>21</v>
       </c>
       <c r="C19" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C21</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
         <v>9953</v>
       </c>
       <c r="D19" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>497.65</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
+        <v>452.40909090909093</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1519,12 +1527,12 @@
         <v>22</v>
       </c>
       <c r="C20" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C22</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
         <v>16438</v>
       </c>
       <c r="D20" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>821.9</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
+        <v>747.18181818181813</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1535,12 +1543,12 @@
         <v>23</v>
       </c>
       <c r="C21" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C23</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
         <v>110</v>
       </c>
       <c r="D21" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>5.5</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1551,12 +1559,12 @@
         <v>24</v>
       </c>
       <c r="C22" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C24</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
         <v>1072</v>
       </c>
       <c r="D22" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>53.6</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
+        <v>48.727272727272727</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1567,12 +1575,12 @@
         <v>25</v>
       </c>
       <c r="C23" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C25</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
         <v>13906</v>
       </c>
       <c r="D23" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>695.3</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
+        <v>632.09090909090912</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,12 +1591,12 @@
         <v>26</v>
       </c>
       <c r="C24" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C26</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
         <v>22452</v>
       </c>
       <c r="D24" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>1122.5999999999999</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
+        <v>1020.5454545454545</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1599,12 +1607,12 @@
         <v>27</v>
       </c>
       <c r="C25" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C27</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
         <v>9668</v>
       </c>
       <c r="D25" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>483.4</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
+        <v>439.45454545454544</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,12 +1623,12 @@
         <v>28</v>
       </c>
       <c r="C26" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C28</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
         <v>7541</v>
       </c>
       <c r="D26" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>377.05</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
+        <v>342.77272727272725</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1631,12 +1639,12 @@
         <v>29</v>
       </c>
       <c r="C27" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C29</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
         <v>2227</v>
       </c>
       <c r="D27" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>111.35</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
+        <v>101.22727272727273</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1647,12 +1655,12 @@
         <v>30</v>
       </c>
       <c r="C28" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C30</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
         <v>2500</v>
       </c>
       <c r="D28" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>125</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
+        <v>113.63636363636364</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1663,12 +1671,12 @@
         <v>31</v>
       </c>
       <c r="C29" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C31</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
         <v>16134</v>
       </c>
       <c r="D29" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>806.7</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
+        <v>733.36363636363637</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1679,12 +1687,12 @@
         <v>32</v>
       </c>
       <c r="C30" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C32</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
         <v>13159</v>
       </c>
       <c r="D30" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>657.95</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
+        <v>598.13636363636363</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1695,12 +1703,12 @@
         <v>33</v>
       </c>
       <c r="C31" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C33</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
         <v>16913</v>
       </c>
       <c r="D31" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>845.65</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
+        <v>768.77272727272725</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1711,12 +1719,12 @@
         <v>34</v>
       </c>
       <c r="C32" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C34</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
         <v>11479</v>
       </c>
       <c r="D32" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>573.95000000000005</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
+        <v>521.77272727272725</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1727,12 +1735,12 @@
         <v>35</v>
       </c>
       <c r="C33" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C35</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
         <v>4339</v>
       </c>
       <c r="D33" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>216.95</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
+        <v>197.22727272727272</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1743,12 +1751,12 @@
         <v>36</v>
       </c>
       <c r="C34" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C36</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
         <v>5475</v>
       </c>
       <c r="D34" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>273.75</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
+        <v>248.86363636363637</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1759,12 +1767,12 @@
         <v>37</v>
       </c>
       <c r="C35" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C37</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
         <v>7601</v>
       </c>
       <c r="D35" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>380.05</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
+        <v>345.5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1775,12 +1783,12 @@
         <v>38</v>
       </c>
       <c r="C36" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C38</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
         <v>5558</v>
       </c>
       <c r="D36" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>277.89999999999998</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
+        <v>252.63636363636363</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1791,12 +1799,12 @@
         <v>39</v>
       </c>
       <c r="C37" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C39</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
         <v>8573</v>
       </c>
       <c r="D37" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>428.65</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
+        <v>389.68181818181819</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1807,12 +1815,12 @@
         <v>40</v>
       </c>
       <c r="C38" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C40</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
         <v>4918</v>
       </c>
       <c r="D38" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>245.9</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
+        <v>223.54545454545453</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1823,12 +1831,12 @@
         <v>41</v>
       </c>
       <c r="C39" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C41</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
         <v>5380</v>
       </c>
       <c r="D39" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>269</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
+        <v>244.54545454545453</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1839,12 +1847,12 @@
         <v>42</v>
       </c>
       <c r="C40" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C42</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
         <v>1013</v>
       </c>
       <c r="D40" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>50.65</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
+        <v>46.045454545454547</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1855,12 +1863,12 @@
         <v>43</v>
       </c>
       <c r="C41" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C43</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
         <v>1667</v>
       </c>
       <c r="D41" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>83.35</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
+        <v>75.772727272727266</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1871,12 +1879,12 @@
         <v>44</v>
       </c>
       <c r="C42" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C44</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
         <v>688</v>
       </c>
       <c r="D42" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>34.4</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
+        <v>31.272727272727273</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1887,12 +1895,12 @@
         <v>45</v>
       </c>
       <c r="C43" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C45</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
         <v>795</v>
       </c>
       <c r="D43" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>39.75</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
+        <v>36.136363636363633</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1901,12 +1909,12 @@
         <v>46</v>
       </c>
       <c r="C44" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C46</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
         <v>18</v>
       </c>
       <c r="D44" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.9</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
+        <v>0.81818181818181823</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1915,12 +1923,12 @@
         <v>47</v>
       </c>
       <c r="C45" s="13">
-        <f>'[2]VINCULO VTS BY SKU OPEN'!C47</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
         <v>69</v>
       </c>
       <c r="D45" s="12">
-        <f ca="1">'[2]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>3.45</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
+        <v>3.1363636363636362</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1976,20 +1984,20 @@
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
-        <f>'[1]VENTAS JULIO'!$G$117</f>
+        <f>'[2]VENTAS JULIO'!$G$117</f>
         <v>503437</v>
       </c>
       <c r="B3" s="3">
-        <f>'[2]DESV. VTS BY SKU'!$K$3</f>
+        <f>'[1]DESV. VTS BY SKU'!$K$3</f>
         <v>499746</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">A3/E5</f>
-        <v>25171.85</v>
+        <v>22883.5</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">C3*22</f>
-        <v>553780.69999999995</v>
+        <v>503437</v>
       </c>
       <c r="E3" s="4">
         <v>696207</v>
@@ -2033,18 +2041,18 @@
       </c>
       <c r="C5" s="17">
         <f ca="1">TODAY()-1</f>
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="D5" s="17">
         <v>46234</v>
       </c>
       <c r="E5" s="19">
         <f ca="1">NETWORKDAYS(B5,C5)-1</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="18">
         <f ca="1">NETWORKDAYS(C5,D5)-1</f>
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65421E34-B1C0-46A8-86A9-F80C1CFD698D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F4D2BA-0992-48DA-8289-1D4BF7C3A224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -482,154 +482,154 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="C4">
-            <v>23127</v>
+            <v>24608</v>
           </cell>
           <cell r="D4">
-            <v>1051.2272727272727</v>
+            <v>1118.5454545454545</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1569</v>
+            <v>1715</v>
           </cell>
           <cell r="D5">
-            <v>71.318181818181813</v>
+            <v>77.954545454545453</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>11440</v>
+            <v>12045</v>
           </cell>
           <cell r="D6">
-            <v>520</v>
+            <v>547.5</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1950</v>
+            <v>2151</v>
           </cell>
           <cell r="D7">
-            <v>88.63636363636364</v>
+            <v>97.772727272727266</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>359</v>
+            <v>367</v>
           </cell>
           <cell r="D8">
-            <v>16.318181818181817</v>
+            <v>16.681818181818183</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>26238</v>
+            <v>28488</v>
           </cell>
           <cell r="D9">
-            <v>1192.6363636363637</v>
+            <v>1294.909090909091</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2433</v>
+            <v>2688</v>
           </cell>
           <cell r="D10">
-            <v>110.59090909090909</v>
+            <v>122.18181818181819</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>6009</v>
+            <v>6682</v>
           </cell>
           <cell r="D11">
-            <v>273.13636363636363</v>
+            <v>303.72727272727275</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>13501</v>
+            <v>14564</v>
           </cell>
           <cell r="D12">
-            <v>613.68181818181813</v>
+            <v>662</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>8241</v>
+            <v>8915</v>
           </cell>
           <cell r="D13">
-            <v>374.59090909090907</v>
+            <v>405.22727272727275</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>66529</v>
+            <v>71501</v>
           </cell>
           <cell r="D14">
-            <v>3024.0454545454545</v>
+            <v>3250.0454545454545</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>44590</v>
+            <v>47928</v>
           </cell>
           <cell r="D15">
-            <v>2026.8181818181818</v>
+            <v>2178.5454545454545</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>44337</v>
+            <v>47576</v>
           </cell>
           <cell r="D16">
-            <v>2015.3181818181818</v>
+            <v>2162.5454545454545</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>49325</v>
+            <v>52903</v>
           </cell>
           <cell r="D17">
-            <v>2242.0454545454545</v>
+            <v>2404.681818181818</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>2775</v>
+            <v>2929</v>
           </cell>
           <cell r="D18">
-            <v>126.13636363636364</v>
+            <v>133.13636363636363</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>4589</v>
+            <v>4969</v>
           </cell>
           <cell r="D19">
-            <v>208.59090909090909</v>
+            <v>225.86363636363637</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>3088</v>
+            <v>3254</v>
           </cell>
           <cell r="D20">
-            <v>140.36363636363637</v>
+            <v>147.90909090909091</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>9953</v>
+            <v>10705</v>
           </cell>
           <cell r="D21">
-            <v>452.40909090909093</v>
+            <v>486.59090909090907</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>16438</v>
+            <v>17521</v>
           </cell>
           <cell r="D22">
-            <v>747.18181818181813</v>
+            <v>796.40909090909088</v>
           </cell>
         </row>
         <row r="23">
@@ -642,178 +642,178 @@
         </row>
         <row r="24">
           <cell r="C24">
-            <v>1072</v>
+            <v>1082</v>
           </cell>
           <cell r="D24">
-            <v>48.727272727272727</v>
+            <v>49.18181818181818</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>13906</v>
+            <v>15064</v>
           </cell>
           <cell r="D25">
-            <v>632.09090909090912</v>
+            <v>684.72727272727275</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>22452</v>
+            <v>24411</v>
           </cell>
           <cell r="D26">
-            <v>1020.5454545454545</v>
+            <v>1109.590909090909</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>9668</v>
+            <v>10624</v>
           </cell>
           <cell r="D27">
-            <v>439.45454545454544</v>
+            <v>482.90909090909093</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>7541</v>
+            <v>8061</v>
           </cell>
           <cell r="D28">
-            <v>342.77272727272725</v>
+            <v>366.40909090909093</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>2227</v>
+            <v>2355</v>
           </cell>
           <cell r="D29">
-            <v>101.22727272727273</v>
+            <v>107.04545454545455</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>2500</v>
+            <v>2696</v>
           </cell>
           <cell r="D30">
-            <v>113.63636363636364</v>
+            <v>122.54545454545455</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>16134</v>
+            <v>17396</v>
           </cell>
           <cell r="D31">
-            <v>733.36363636363637</v>
+            <v>790.72727272727275</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>13159</v>
+            <v>14334</v>
           </cell>
           <cell r="D32">
-            <v>598.13636363636363</v>
+            <v>651.5454545454545</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>16913</v>
+            <v>18538</v>
           </cell>
           <cell r="D33">
-            <v>768.77272727272725</v>
+            <v>842.63636363636363</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>11479</v>
+            <v>12592</v>
           </cell>
           <cell r="D34">
-            <v>521.77272727272725</v>
+            <v>572.36363636363637</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>4339</v>
+            <v>4676</v>
           </cell>
           <cell r="D35">
-            <v>197.22727272727272</v>
+            <v>212.54545454545453</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>5475</v>
+            <v>6412</v>
           </cell>
           <cell r="D36">
-            <v>248.86363636363637</v>
+            <v>291.45454545454544</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>7601</v>
+            <v>8233</v>
           </cell>
           <cell r="D37">
-            <v>345.5</v>
+            <v>374.22727272727275</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>5558</v>
+            <v>6005</v>
           </cell>
           <cell r="D38">
-            <v>252.63636363636363</v>
+            <v>272.95454545454544</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>8573</v>
+            <v>9249</v>
           </cell>
           <cell r="D39">
-            <v>389.68181818181819</v>
+            <v>420.40909090909093</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>4918</v>
+            <v>5422</v>
           </cell>
           <cell r="D40">
-            <v>223.54545454545453</v>
+            <v>246.45454545454547</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>5380</v>
+            <v>5795</v>
           </cell>
           <cell r="D41">
-            <v>244.54545454545453</v>
+            <v>263.40909090909093</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>1013</v>
+            <v>1098</v>
           </cell>
           <cell r="D42">
-            <v>46.045454545454547</v>
+            <v>49.909090909090907</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1667</v>
+            <v>1747</v>
           </cell>
           <cell r="D43">
-            <v>75.772727272727266</v>
+            <v>79.409090909090907</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>688</v>
+            <v>754</v>
           </cell>
           <cell r="D44">
-            <v>31.272727272727273</v>
+            <v>34.272727272727273</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>795</v>
+            <v>825</v>
           </cell>
           <cell r="D45">
-            <v>36.136363636363633</v>
+            <v>37.5</v>
           </cell>
         </row>
         <row r="46">
@@ -826,17 +826,17 @@
         </row>
         <row r="47">
           <cell r="C47">
-            <v>69</v>
+            <v>72</v>
           </cell>
           <cell r="D47">
-            <v>3.1363636363636362</v>
+            <v>3.2727272727272729</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="3">
           <cell r="K3">
-            <v>499746</v>
+            <v>539078</v>
           </cell>
         </row>
       </sheetData>
@@ -882,20 +882,20 @@
       <sheetData sheetId="0">
         <row r="117">
           <cell r="G117">
-            <v>503437</v>
+            <v>533354</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="2">
-          <cell r="S2">
-            <v>1217</v>
+          <cell r="W2">
+            <v>24608</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1240,11 +1240,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>23127</v>
+        <v>24608</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1051.2272727272727</v>
+        <v>1118.5454545454545</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1256,11 +1256,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1569</v>
+        <v>1715</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>71.318181818181813</v>
+        <v>77.954545454545453</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>11440</v>
+        <v>12045</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>520</v>
+        <v>547.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1288,11 +1288,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1950</v>
+        <v>2151</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>88.63636363636364</v>
+        <v>97.772727272727266</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1304,11 +1304,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>16.318181818181817</v>
+        <v>16.681818181818183</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>26238</v>
+        <v>28488</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1192.6363636363637</v>
+        <v>1294.909090909091</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1336,11 +1336,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2433</v>
+        <v>2688</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>110.59090909090909</v>
+        <v>122.18181818181819</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1352,11 +1352,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>6009</v>
+        <v>6682</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>273.13636363636363</v>
+        <v>303.72727272727275</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,11 +1368,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>13501</v>
+        <v>14564</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>613.68181818181813</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1384,11 +1384,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>8241</v>
+        <v>8915</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>374.59090909090907</v>
+        <v>405.22727272727275</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1400,11 +1400,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>66529</v>
+        <v>71501</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3024.0454545454545</v>
+        <v>3250.0454545454545</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1416,11 +1416,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>44590</v>
+        <v>47928</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2026.8181818181818</v>
+        <v>2178.5454545454545</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1432,11 +1432,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>44337</v>
+        <v>47576</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2015.3181818181818</v>
+        <v>2162.5454545454545</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1448,11 +1448,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>49325</v>
+        <v>52903</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2242.0454545454545</v>
+        <v>2404.681818181818</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>2775</v>
+        <v>2929</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>126.13636363636364</v>
+        <v>133.13636363636363</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,11 +1480,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>4589</v>
+        <v>4969</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>208.59090909090909</v>
+        <v>225.86363636363637</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,11 +1496,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>3088</v>
+        <v>3254</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>140.36363636363637</v>
+        <v>147.90909090909091</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1512,11 +1512,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>9953</v>
+        <v>10705</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>452.40909090909093</v>
+        <v>486.59090909090907</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1528,11 +1528,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>16438</v>
+        <v>17521</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>747.18181818181813</v>
+        <v>796.40909090909088</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>1072</v>
+        <v>1082</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>48.727272727272727</v>
+        <v>49.18181818181818</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,11 +1576,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>13906</v>
+        <v>15064</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>632.09090909090912</v>
+        <v>684.72727272727275</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1592,11 +1592,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>22452</v>
+        <v>24411</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>1020.5454545454545</v>
+        <v>1109.590909090909</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>9668</v>
+        <v>10624</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>439.45454545454544</v>
+        <v>482.90909090909093</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1624,11 +1624,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>7541</v>
+        <v>8061</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>342.77272727272725</v>
+        <v>366.40909090909093</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1640,11 +1640,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>2227</v>
+        <v>2355</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>101.22727272727273</v>
+        <v>107.04545454545455</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1656,11 +1656,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>2500</v>
+        <v>2696</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>113.63636363636364</v>
+        <v>122.54545454545455</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>16134</v>
+        <v>17396</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>733.36363636363637</v>
+        <v>790.72727272727275</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1688,11 +1688,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>13159</v>
+        <v>14334</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>598.13636363636363</v>
+        <v>651.5454545454545</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1704,11 +1704,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>16913</v>
+        <v>18538</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>768.77272727272725</v>
+        <v>842.63636363636363</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,11 +1720,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>11479</v>
+        <v>12592</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>521.77272727272725</v>
+        <v>572.36363636363637</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>4339</v>
+        <v>4676</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>197.22727272727272</v>
+        <v>212.54545454545453</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1752,11 +1752,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>5475</v>
+        <v>6412</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>248.86363636363637</v>
+        <v>291.45454545454544</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1768,11 +1768,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>7601</v>
+        <v>8233</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>345.5</v>
+        <v>374.22727272727275</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1784,11 +1784,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>5558</v>
+        <v>6005</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>252.63636363636363</v>
+        <v>272.95454545454544</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,11 +1800,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>8573</v>
+        <v>9249</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>389.68181818181819</v>
+        <v>420.40909090909093</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1816,11 +1816,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>4918</v>
+        <v>5422</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>223.54545454545453</v>
+        <v>246.45454545454547</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1832,11 +1832,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>5380</v>
+        <v>5795</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>244.54545454545453</v>
+        <v>263.40909090909093</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>1013</v>
+        <v>1098</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>46.045454545454547</v>
+        <v>49.909090909090907</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1864,11 +1864,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1667</v>
+        <v>1747</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>75.772727272727266</v>
+        <v>79.409090909090907</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1880,11 +1880,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>688</v>
+        <v>754</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>31.272727272727273</v>
+        <v>34.272727272727273</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1896,11 +1896,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>36.136363636363633</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1924,11 +1924,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>3.1363636363636362</v>
+        <v>3.2727272727272729</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1985,30 +1985,30 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[2]VENTAS JULIO'!$G$117</f>
-        <v>503437</v>
+        <v>533354</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]DESV. VTS BY SKU'!$K$3</f>
-        <v>499746</v>
+        <v>539078</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">A3/E5</f>
-        <v>22883.5</v>
+        <v>24243.363636363636</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">C3*22</f>
-        <v>503437</v>
+        <v>533354</v>
       </c>
       <c r="E3" s="4">
         <v>696207</v>
       </c>
       <c r="F3" s="6">
         <f>A3/E3</f>
-        <v>0.72311395892313635</v>
+        <v>0.76608537403387211</v>
       </c>
       <c r="G3" s="7">
         <f>A3-E3</f>
-        <v>-192770</v>
+        <v>-162853</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2034,7 +2034,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>A3-B3</f>
-        <v>3691</v>
+        <v>-5724</v>
       </c>
       <c r="B5" s="17">
         <v>46204</v>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F4D2BA-0992-48DA-8289-1D4BF7C3A224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83B56B7-E748-4CBF-A996-52A2DDA5F299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -18,7 +18,6 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>FORECAST</t>
   </si>
@@ -191,9 +190,6 @@
     <t>VENTA BRUTA</t>
   </si>
   <si>
-    <t>UNITS RETURN</t>
-  </si>
-  <si>
     <t>DASHBOARD</t>
   </si>
   <si>
@@ -210,21 +206,6 @@
   </si>
   <si>
     <t>DIF UNITS</t>
-  </si>
-  <si>
-    <t>INICIO DE VENTA</t>
-  </si>
-  <si>
-    <t>TRANSC. VENTA</t>
-  </si>
-  <si>
-    <t>FINAL DE VENTA</t>
-  </si>
-  <si>
-    <t>DIAS VENTA EFECT.</t>
-  </si>
-  <si>
-    <t>DIAS VENTA RESTA.</t>
   </si>
 </sst>
 </file>
@@ -411,19 +392,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -451,451 +432,428 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="INVENTARIO NACIONAL 03-07-26"/>
-      <sheetName val="VINCULO VTS BY SKU JUNIO"/>
+      <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
-      <sheetName val="INVENTARIO NACIONAL 03-07-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 06-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 07-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 08-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 09-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 10-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 13-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 14-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 15-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 16-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 17-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 20-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 21-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 22-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 23-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 27-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 28-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 29-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 30-07-26"/>
-      <sheetName val="INVENTARIO NACIONAL 31-07-26"/>
+      <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="G3">
+            <v>20879</v>
+          </cell>
+          <cell r="H3">
+            <v>20785</v>
+          </cell>
+          <cell r="I3">
+            <v>20879</v>
+          </cell>
+          <cell r="J3">
+            <v>459338</v>
+          </cell>
+          <cell r="K3">
+            <v>649023</v>
+          </cell>
+          <cell r="L3">
+            <v>3.216989228424879E-2</v>
+          </cell>
+          <cell r="M3">
+            <v>-628144</v>
+          </cell>
+        </row>
         <row r="4">
           <cell r="C4">
-            <v>24608</v>
+            <v>1224</v>
           </cell>
           <cell r="D4">
-            <v>1118.5454545454545</v>
+            <v>1224</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>UNITS RETURN</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>INICIO DE VENTA</v>
+          </cell>
+          <cell r="I4" t="str">
+            <v>TRANSC. VENTA</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>FINAL DE VENTA</v>
+          </cell>
+          <cell r="K4" t="str">
+            <v>DIAS VENTA EFECT.</v>
+          </cell>
+          <cell r="L4" t="str">
+            <v>DIAS VENTA RESTA.</v>
           </cell>
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1715</v>
+            <v>65</v>
           </cell>
           <cell r="D5">
-            <v>77.954545454545453</v>
+            <v>65</v>
+          </cell>
+          <cell r="G5">
+            <v>94</v>
+          </cell>
+          <cell r="H5">
+            <v>46237</v>
+          </cell>
+          <cell r="I5">
+            <v>46238</v>
+          </cell>
+          <cell r="J5">
+            <v>46265</v>
+          </cell>
+          <cell r="K5">
+            <v>1</v>
+          </cell>
+          <cell r="L5">
+            <v>20</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>12045</v>
+            <v>469</v>
           </cell>
           <cell r="D6">
-            <v>547.5</v>
+            <v>469</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>2151</v>
+            <v>62</v>
           </cell>
           <cell r="D7">
-            <v>97.772727272727266</v>
+            <v>62</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>367</v>
+            <v>6</v>
           </cell>
           <cell r="D8">
-            <v>16.681818181818183</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>28488</v>
+            <v>1400</v>
           </cell>
           <cell r="D9">
-            <v>1294.909090909091</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2688</v>
+            <v>74</v>
           </cell>
           <cell r="D10">
-            <v>122.18181818181819</v>
+            <v>74</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>6682</v>
+            <v>239</v>
           </cell>
           <cell r="D11">
-            <v>303.72727272727275</v>
+            <v>239</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>14564</v>
+            <v>528</v>
           </cell>
           <cell r="D12">
-            <v>662</v>
+            <v>528</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>8915</v>
+            <v>269</v>
           </cell>
           <cell r="D13">
-            <v>405.22727272727275</v>
+            <v>269</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>71501</v>
+            <v>2798</v>
           </cell>
           <cell r="D14">
-            <v>3250.0454545454545</v>
+            <v>2798</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>47928</v>
+            <v>1945</v>
           </cell>
           <cell r="D15">
-            <v>2178.5454545454545</v>
+            <v>1945</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>47576</v>
+            <v>1938</v>
           </cell>
           <cell r="D16">
-            <v>2162.5454545454545</v>
+            <v>1938</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>52903</v>
+            <v>2026</v>
           </cell>
           <cell r="D17">
-            <v>2404.681818181818</v>
+            <v>2026</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>2929</v>
+            <v>40</v>
           </cell>
           <cell r="D18">
-            <v>133.13636363636363</v>
+            <v>40</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>4969</v>
+            <v>57</v>
           </cell>
           <cell r="D19">
-            <v>225.86363636363637</v>
+            <v>57</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>3254</v>
+            <v>36</v>
           </cell>
           <cell r="D20">
-            <v>147.90909090909091</v>
+            <v>36</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>10705</v>
+            <v>244</v>
           </cell>
           <cell r="D21">
-            <v>486.59090909090907</v>
+            <v>244</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>17521</v>
+            <v>392</v>
           </cell>
           <cell r="D22">
-            <v>796.40909090909088</v>
+            <v>392</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>110</v>
+            <v>0</v>
           </cell>
           <cell r="D23">
-            <v>5</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>1082</v>
+            <v>50</v>
           </cell>
           <cell r="D24">
-            <v>49.18181818181818</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>15064</v>
+            <v>606</v>
           </cell>
           <cell r="D25">
-            <v>684.72727272727275</v>
+            <v>606</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>24411</v>
+            <v>866</v>
           </cell>
           <cell r="D26">
-            <v>1109.590909090909</v>
+            <v>866</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>10624</v>
+            <v>358</v>
           </cell>
           <cell r="D27">
-            <v>482.90909090909093</v>
+            <v>358</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>8061</v>
+            <v>188</v>
           </cell>
           <cell r="D28">
-            <v>366.40909090909093</v>
+            <v>188</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>2355</v>
+            <v>84</v>
           </cell>
           <cell r="D29">
-            <v>107.04545454545455</v>
+            <v>84</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>2696</v>
+            <v>50</v>
           </cell>
           <cell r="D30">
-            <v>122.54545454545455</v>
+            <v>50</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>17396</v>
+            <v>370</v>
           </cell>
           <cell r="D31">
-            <v>790.72727272727275</v>
+            <v>370</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>14334</v>
+            <v>402</v>
           </cell>
           <cell r="D32">
-            <v>651.5454545454545</v>
+            <v>402</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>18538</v>
+            <v>467</v>
           </cell>
           <cell r="D33">
-            <v>842.63636363636363</v>
+            <v>467</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>12592</v>
+            <v>307</v>
           </cell>
           <cell r="D34">
-            <v>572.36363636363637</v>
+            <v>307</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>4676</v>
+            <v>43</v>
           </cell>
           <cell r="D35">
-            <v>212.54545454545453</v>
+            <v>43</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>6412</v>
+            <v>315</v>
           </cell>
           <cell r="D36">
-            <v>291.45454545454544</v>
+            <v>315</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>8233</v>
+            <v>70</v>
           </cell>
           <cell r="D37">
-            <v>374.22727272727275</v>
+            <v>70</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>6005</v>
+            <v>261</v>
           </cell>
           <cell r="D38">
-            <v>272.95454545454544</v>
+            <v>261</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>9249</v>
+            <v>1192</v>
           </cell>
           <cell r="D39">
-            <v>420.40909090909093</v>
+            <v>1192</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>5422</v>
+            <v>591</v>
           </cell>
           <cell r="D40">
-            <v>246.45454545454547</v>
+            <v>591</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>5795</v>
+            <v>267</v>
           </cell>
           <cell r="D41">
-            <v>263.40909090909093</v>
+            <v>267</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>1098</v>
+            <v>13</v>
           </cell>
           <cell r="D42">
-            <v>49.909090909090907</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1747</v>
+            <v>230</v>
           </cell>
           <cell r="D43">
-            <v>79.409090909090907</v>
+            <v>230</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>754</v>
+            <v>223</v>
           </cell>
           <cell r="D44">
-            <v>34.272727272727273</v>
+            <v>223</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>825</v>
+            <v>19</v>
           </cell>
           <cell r="D45">
-            <v>37.5</v>
+            <v>19</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>18</v>
+            <v>0</v>
           </cell>
           <cell r="D46">
-            <v>0.81818181818181823</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>72</v>
+            <v>1</v>
           </cell>
           <cell r="D47">
-            <v>3.2727272727272729</v>
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3">
-        <row r="3">
-          <cell r="K3">
-            <v>539078</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="VENTAS JULIO"/>
-      <sheetName val="VENTAS DIARIA POR SKU"/>
-      <sheetName val="DESPACHO"/>
-      <sheetName val="RELACION DE VIAJES"/>
-      <sheetName val="RELACION DE VIAJES SITES "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="117">
-          <cell r="G117">
-            <v>533354</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="W2">
-            <v>24608</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1240,11 +1198,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>24608</v>
+        <v>1224</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1118.5454545454545</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1256,11 +1214,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1715</v>
+        <v>65</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>77.954545454545453</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,11 +1230,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>12045</v>
+        <v>469</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>547.5</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1288,11 +1246,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>2151</v>
+        <v>62</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>97.772727272727266</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1304,11 +1262,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>367</v>
+        <v>6</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>16.681818181818183</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1320,11 +1278,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>28488</v>
+        <v>1400</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1294.909090909091</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1336,11 +1294,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2688</v>
+        <v>74</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>122.18181818181819</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1352,11 +1310,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>6682</v>
+        <v>239</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>303.72727272727275</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,11 +1326,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>14564</v>
+        <v>528</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>662</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1384,11 +1342,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>8915</v>
+        <v>269</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>405.22727272727275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1400,11 +1358,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>71501</v>
+        <v>2798</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3250.0454545454545</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1416,11 +1374,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>47928</v>
+        <v>1945</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2178.5454545454545</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1432,11 +1390,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>47576</v>
+        <v>1938</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2162.5454545454545</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1448,11 +1406,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>52903</v>
+        <v>2026</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2404.681818181818</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,11 +1422,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>2929</v>
+        <v>40</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>133.13636363636363</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,11 +1438,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>4969</v>
+        <v>57</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>225.86363636363637</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,11 +1454,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>3254</v>
+        <v>36</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>147.90909090909091</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1512,11 +1470,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>10705</v>
+        <v>244</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>486.59090909090907</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1528,11 +1486,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>17521</v>
+        <v>392</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>796.40909090909088</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1544,11 +1502,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,11 +1518,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>1082</v>
+        <v>50</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>49.18181818181818</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,11 +1534,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>15064</v>
+        <v>606</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>684.72727272727275</v>
+        <v>606</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1592,11 +1550,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>24411</v>
+        <v>866</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>1109.590909090909</v>
+        <v>866</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,11 +1566,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>10624</v>
+        <v>358</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>482.90909090909093</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1624,11 +1582,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>8061</v>
+        <v>188</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>366.40909090909093</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1640,11 +1598,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>2355</v>
+        <v>84</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>107.04545454545455</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1656,11 +1614,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>2696</v>
+        <v>50</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>122.54545454545455</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1672,11 +1630,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>17396</v>
+        <v>370</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>790.72727272727275</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1688,11 +1646,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>14334</v>
+        <v>402</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>651.5454545454545</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1704,11 +1662,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>18538</v>
+        <v>467</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>842.63636363636363</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,11 +1678,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>12592</v>
+        <v>307</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>572.36363636363637</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1736,11 +1694,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>4676</v>
+        <v>43</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>212.54545454545453</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1752,11 +1710,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>6412</v>
+        <v>315</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>291.45454545454544</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1768,11 +1726,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>8233</v>
+        <v>70</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>374.22727272727275</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1784,11 +1742,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>6005</v>
+        <v>261</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>272.95454545454544</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,11 +1758,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>9249</v>
+        <v>1192</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>420.40909090909093</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1816,11 +1774,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>5422</v>
+        <v>591</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>246.45454545454547</v>
+        <v>591</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1832,11 +1790,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>5795</v>
+        <v>267</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>263.40909090909093</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,11 +1806,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>1098</v>
+        <v>13</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>49.909090909090907</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1864,11 +1822,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1747</v>
+        <v>230</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>79.409090909090907</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1880,11 +1838,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>754</v>
+        <v>223</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>34.272727272727273</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1896,11 +1854,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>825</v>
+        <v>19</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>37.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1910,11 +1868,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0.81818181818181823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1924,11 +1882,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>3.2727272727272729</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1949,28 +1907,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="A1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
@@ -1979,80 +1937,97 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
-        <f>'[2]VENTAS JULIO'!$G$117</f>
-        <v>533354</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
+        <v>20879</v>
       </c>
       <c r="B3" s="3">
-        <f>'[1]DESV. VTS BY SKU'!$K$3</f>
-        <v>539078</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
+        <v>20785</v>
       </c>
       <c r="C3" s="4">
-        <f ca="1">A3/E5</f>
-        <v>24243.363636363636</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
+        <v>20879</v>
       </c>
       <c r="D3" s="5">
-        <f ca="1">C3*22</f>
-        <v>533354</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
+        <v>459338</v>
       </c>
       <c r="E3" s="4">
-        <v>696207</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
+        <v>649023</v>
       </c>
       <c r="F3" s="6">
-        <f>A3/E3</f>
-        <v>0.76608537403387211</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
+        <v>3.216989228424879E-2</v>
       </c>
       <c r="G3" s="7">
-        <f>A3-E3</f>
-        <v>-162853</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
+        <v>-628144</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>61</v>
+      <c r="A4" s="19" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G4</f>
+        <v>UNITS RETURN</v>
+      </c>
+      <c r="B4" s="19" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H4</f>
+        <v>INICIO DE VENTA</v>
+      </c>
+      <c r="C4" s="19" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!I4</f>
+        <v>TRANSC. VENTA</v>
+      </c>
+      <c r="D4" s="19" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!J4</f>
+        <v>FINAL DE VENTA</v>
+      </c>
+      <c r="E4" s="19" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!K4</f>
+        <v>DIAS VENTA EFECT.</v>
+      </c>
+      <c r="F4" s="19" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!L4</f>
+        <v>DIAS VENTA RESTA.</v>
+      </c>
+      <c r="G4" s="11">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!M4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <f>A3-B3</f>
-        <v>-5724</v>
-      </c>
-      <c r="B5" s="17">
-        <v>46204</v>
-      </c>
-      <c r="C5" s="17">
-        <f ca="1">TODAY()-1</f>
-        <v>46236</v>
-      </c>
-      <c r="D5" s="17">
-        <v>46234</v>
-      </c>
-      <c r="E5" s="19">
-        <f ca="1">NETWORKDAYS(B5,C5)-1</f>
-        <v>22</v>
-      </c>
-      <c r="F5" s="18">
-        <f ca="1">NETWORKDAYS(C5,D5)-1</f>
-        <v>-2</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
+        <v>94</v>
+      </c>
+      <c r="B5" s="16">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
+        <v>46237</v>
+      </c>
+      <c r="C5" s="16">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
+        <v>46238</v>
+      </c>
+      <c r="D5" s="16">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
+        <v>46265</v>
+      </c>
+      <c r="E5" s="20">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="17">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
+        <v>20</v>
+      </c>
+      <c r="G5" s="11">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83B56B7-E748-4CBF-A996-52A2DDA5F299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013C1D55-B555-4E59-BA95-67BD0B753B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -398,13 +398,13 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -436,39 +436,40 @@
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="G3">
-            <v>20879</v>
+            <v>43250</v>
           </cell>
           <cell r="H3">
-            <v>20785</v>
+            <v>43017</v>
           </cell>
           <cell r="I3">
-            <v>20879</v>
+            <v>21625</v>
           </cell>
           <cell r="J3">
-            <v>459338</v>
+            <v>475750</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>3.216989228424879E-2</v>
+            <v>6.6638624517158865E-2</v>
           </cell>
           <cell r="M3">
-            <v>-628144</v>
+            <v>-605773</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>1224</v>
+            <v>2301</v>
           </cell>
           <cell r="D4">
-            <v>1224</v>
+            <v>1150.5</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -491,164 +492,164 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>65</v>
+            <v>231</v>
           </cell>
           <cell r="D5">
-            <v>65</v>
+            <v>115.5</v>
           </cell>
           <cell r="G5">
-            <v>94</v>
+            <v>233</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46238</v>
+            <v>46239</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="L5">
-            <v>20</v>
+            <v>19</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>469</v>
+            <v>870</v>
           </cell>
           <cell r="D6">
-            <v>469</v>
+            <v>435</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>62</v>
+            <v>184</v>
           </cell>
           <cell r="D7">
-            <v>62</v>
+            <v>92</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>6</v>
+            <v>9</v>
           </cell>
           <cell r="D8">
-            <v>6</v>
+            <v>4.5</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>1400</v>
+            <v>2829</v>
           </cell>
           <cell r="D9">
-            <v>1400</v>
+            <v>1414.5</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>74</v>
+            <v>279</v>
           </cell>
           <cell r="D10">
-            <v>74</v>
+            <v>139.5</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>239</v>
+            <v>606</v>
           </cell>
           <cell r="D11">
-            <v>239</v>
+            <v>303</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>528</v>
+            <v>1093</v>
           </cell>
           <cell r="D12">
-            <v>528</v>
+            <v>546.5</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>269</v>
+            <v>729</v>
           </cell>
           <cell r="D13">
-            <v>269</v>
+            <v>364.5</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>2798</v>
+            <v>5778</v>
           </cell>
           <cell r="D14">
-            <v>2798</v>
+            <v>2889</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>1945</v>
+            <v>3629</v>
           </cell>
           <cell r="D15">
-            <v>1945</v>
+            <v>1814.5</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>1938</v>
+            <v>3582</v>
           </cell>
           <cell r="D16">
-            <v>1938</v>
+            <v>1791</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>2026</v>
+            <v>4350</v>
           </cell>
           <cell r="D17">
-            <v>2026</v>
+            <v>2175</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>40</v>
+            <v>138</v>
           </cell>
           <cell r="D18">
-            <v>40</v>
+            <v>69</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>57</v>
+            <v>277</v>
           </cell>
           <cell r="D19">
-            <v>57</v>
+            <v>138.5</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>36</v>
+            <v>156</v>
           </cell>
           <cell r="D20">
-            <v>36</v>
+            <v>78</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>244</v>
+            <v>744</v>
           </cell>
           <cell r="D21">
-            <v>244</v>
+            <v>372</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>392</v>
+            <v>1184</v>
           </cell>
           <cell r="D22">
-            <v>392</v>
+            <v>592</v>
           </cell>
         </row>
         <row r="23">
@@ -661,178 +662,178 @@
         </row>
         <row r="24">
           <cell r="C24">
-            <v>50</v>
+            <v>70</v>
           </cell>
           <cell r="D24">
-            <v>50</v>
+            <v>35</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>606</v>
+            <v>1016</v>
           </cell>
           <cell r="D25">
-            <v>606</v>
+            <v>508</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>866</v>
+            <v>1482</v>
           </cell>
           <cell r="D26">
-            <v>866</v>
+            <v>741</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>358</v>
+            <v>832</v>
           </cell>
           <cell r="D27">
-            <v>358</v>
+            <v>416</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>188</v>
+            <v>426</v>
           </cell>
           <cell r="D28">
-            <v>188</v>
+            <v>213</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>84</v>
+            <v>210</v>
           </cell>
           <cell r="D29">
-            <v>84</v>
+            <v>105</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>50</v>
+            <v>109</v>
           </cell>
           <cell r="D30">
-            <v>50</v>
+            <v>54.5</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>370</v>
+            <v>869</v>
           </cell>
           <cell r="D31">
-            <v>370</v>
+            <v>434.5</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>402</v>
+            <v>1054</v>
           </cell>
           <cell r="D32">
-            <v>402</v>
+            <v>527</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>467</v>
+            <v>1443</v>
           </cell>
           <cell r="D33">
-            <v>467</v>
+            <v>721.5</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>307</v>
+            <v>903</v>
           </cell>
           <cell r="D34">
-            <v>307</v>
+            <v>451.5</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>43</v>
+            <v>148</v>
           </cell>
           <cell r="D35">
-            <v>43</v>
+            <v>74</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>315</v>
+            <v>982</v>
           </cell>
           <cell r="D36">
-            <v>315</v>
+            <v>491</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>70</v>
+            <v>225</v>
           </cell>
           <cell r="D37">
-            <v>70</v>
+            <v>112.5</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>261</v>
+            <v>575</v>
           </cell>
           <cell r="D38">
-            <v>261</v>
+            <v>287.5</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>1192</v>
+            <v>1632</v>
           </cell>
           <cell r="D39">
-            <v>1192</v>
+            <v>816</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>591</v>
+            <v>896</v>
           </cell>
           <cell r="D40">
-            <v>591</v>
+            <v>448</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>267</v>
+            <v>494</v>
           </cell>
           <cell r="D41">
-            <v>267</v>
+            <v>247</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>13</v>
+            <v>63</v>
           </cell>
           <cell r="D42">
-            <v>13</v>
+            <v>31.5</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>230</v>
+            <v>272</v>
           </cell>
           <cell r="D43">
-            <v>230</v>
+            <v>136</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>223</v>
+            <v>235</v>
           </cell>
           <cell r="D44">
-            <v>223</v>
+            <v>117.5</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>19</v>
+            <v>111</v>
           </cell>
           <cell r="D45">
-            <v>19</v>
+            <v>55.5</v>
           </cell>
         </row>
         <row r="46">
@@ -848,12 +849,13 @@
             <v>1</v>
           </cell>
           <cell r="D47">
-            <v>1</v>
+            <v>0.5</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1198,11 +1200,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>1224</v>
+        <v>2301</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1224</v>
+        <v>1150.5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1214,11 +1216,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>65</v>
+        <v>231</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>65</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1230,11 +1232,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>469</v>
+        <v>870</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>469</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1246,11 +1248,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1262,11 +1264,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1278,11 +1280,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>1400</v>
+        <v>2829</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1400</v>
+        <v>1414.5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1294,11 +1296,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>74</v>
+        <v>279</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>74</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1310,11 +1312,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>239</v>
+        <v>606</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>239</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,11 +1328,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>528</v>
+        <v>1093</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>528</v>
+        <v>546.5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1342,11 +1344,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>269</v>
+        <v>729</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>269</v>
+        <v>364.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1358,11 +1360,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>2798</v>
+        <v>5778</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2798</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1374,11 +1376,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>1945</v>
+        <v>3629</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1945</v>
+        <v>1814.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1390,11 +1392,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>1938</v>
+        <v>3582</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1938</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1406,11 +1408,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>2026</v>
+        <v>4350</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2026</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1422,11 +1424,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1438,11 +1440,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>57</v>
+        <v>277</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>57</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1454,11 +1456,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>36</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1470,11 +1472,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>244</v>
+        <v>744</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>244</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1486,11 +1488,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>392</v>
+        <v>1184</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>392</v>
+        <v>592</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,11 +1520,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1534,11 +1536,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>606</v>
+        <v>1016</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>606</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,11 +1552,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>866</v>
+        <v>1482</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>866</v>
+        <v>741</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,11 +1568,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>358</v>
+        <v>832</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>358</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1582,11 +1584,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>188</v>
+        <v>426</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>188</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1598,11 +1600,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1614,11 +1616,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>50</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1630,11 +1632,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>370</v>
+        <v>869</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>370</v>
+        <v>434.5</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1646,11 +1648,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>402</v>
+        <v>1054</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>402</v>
+        <v>527</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,11 +1664,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>467</v>
+        <v>1443</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>467</v>
+        <v>721.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1678,11 +1680,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>307</v>
+        <v>903</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>307</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1694,11 +1696,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1710,11 +1712,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>315</v>
+        <v>982</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>315</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1726,11 +1728,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>70</v>
+        <v>225</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>70</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1742,11 +1744,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>261</v>
+        <v>575</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>261</v>
+        <v>287.5</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1758,11 +1760,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>1192</v>
+        <v>1632</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>1192</v>
+        <v>816</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1774,11 +1776,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>591</v>
+        <v>896</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>591</v>
+        <v>448</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1790,11 +1792,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>267</v>
+        <v>494</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>267</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1806,11 +1808,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>13</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1822,11 +1824,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>230</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1838,11 +1840,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>223</v>
+        <v>117.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1854,11 +1856,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>19</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,7 +1888,7 @@
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1907,15 +1909,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1943,19 +1945,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>20879</v>
+        <v>43250</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>20785</v>
+        <v>43017</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>20879</v>
+        <v>21625</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>459338</v>
+        <v>475750</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1963,35 +1965,35 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>3.216989228424879E-2</v>
+        <v>6.6638624517158865E-2</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-628144</v>
+        <v>-605773</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="str">
+      <c r="A4" s="18" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G4</f>
         <v>UNITS RETURN</v>
       </c>
-      <c r="B4" s="19" t="str">
+      <c r="B4" s="18" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H4</f>
         <v>INICIO DE VENTA</v>
       </c>
-      <c r="C4" s="19" t="str">
+      <c r="C4" s="18" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!I4</f>
         <v>TRANSC. VENTA</v>
       </c>
-      <c r="D4" s="19" t="str">
+      <c r="D4" s="18" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J4</f>
         <v>FINAL DE VENTA</v>
       </c>
-      <c r="E4" s="19" t="str">
+      <c r="E4" s="18" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K4</f>
         <v>DIAS VENTA EFECT.</v>
       </c>
-      <c r="F4" s="19" t="str">
+      <c r="F4" s="18" t="str">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L4</f>
         <v>DIAS VENTA RESTA.</v>
       </c>
@@ -2003,7 +2005,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>94</v>
+        <v>233</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2011,19 +2013,19 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
         <v>46265</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013C1D55-B555-4E59-BA95-67BD0B753B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0701136-DA14-4844-8C5E-697B82567B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -437,39 +437,40 @@
       <sheetName val="DESV. VTS BY SKU"/>
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="G3">
-            <v>43250</v>
+            <v>74722</v>
           </cell>
           <cell r="H3">
-            <v>43017</v>
+            <v>73432</v>
           </cell>
           <cell r="I3">
-            <v>21625</v>
+            <v>24907.333333333332</v>
           </cell>
           <cell r="J3">
-            <v>475750</v>
+            <v>547961.33333333326</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>6.6638624517158865E-2</v>
+            <v>0.11512997228141375</v>
           </cell>
           <cell r="M3">
-            <v>-605773</v>
+            <v>-574301</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>2301</v>
+            <v>3803</v>
           </cell>
           <cell r="D4">
-            <v>1150.5</v>
+            <v>1267.6666666666667</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -492,164 +493,164 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>231</v>
+            <v>323</v>
           </cell>
           <cell r="D5">
-            <v>115.5</v>
+            <v>107.66666666666667</v>
           </cell>
           <cell r="G5">
-            <v>233</v>
+            <v>1290</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46239</v>
+            <v>46240</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>2</v>
+            <v>3</v>
           </cell>
           <cell r="L5">
-            <v>19</v>
+            <v>18</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>870</v>
+            <v>1304</v>
           </cell>
           <cell r="D6">
-            <v>435</v>
+            <v>434.66666666666669</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>184</v>
+            <v>397</v>
           </cell>
           <cell r="D7">
-            <v>92</v>
+            <v>132.33333333333334</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>9</v>
+            <v>20</v>
           </cell>
           <cell r="D8">
-            <v>4.5</v>
+            <v>6.666666666666667</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>2829</v>
+            <v>4143</v>
           </cell>
           <cell r="D9">
-            <v>1414.5</v>
+            <v>1381</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>279</v>
+            <v>424</v>
           </cell>
           <cell r="D10">
-            <v>139.5</v>
+            <v>141.33333333333334</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>606</v>
+            <v>1037</v>
           </cell>
           <cell r="D11">
-            <v>303</v>
+            <v>345.66666666666669</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>1093</v>
+            <v>1984</v>
           </cell>
           <cell r="D12">
-            <v>546.5</v>
+            <v>661.33333333333337</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>729</v>
+            <v>1190</v>
           </cell>
           <cell r="D13">
-            <v>364.5</v>
+            <v>396.66666666666669</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>5778</v>
+            <v>9967</v>
           </cell>
           <cell r="D14">
-            <v>2889</v>
+            <v>3322.3333333333335</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>3629</v>
+            <v>6337</v>
           </cell>
           <cell r="D15">
-            <v>1814.5</v>
+            <v>2112.3333333333335</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>3582</v>
+            <v>6298</v>
           </cell>
           <cell r="D16">
-            <v>1791</v>
+            <v>2099.3333333333335</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>4350</v>
+            <v>7322</v>
           </cell>
           <cell r="D17">
-            <v>2175</v>
+            <v>2440.6666666666665</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>138</v>
+            <v>213</v>
           </cell>
           <cell r="D18">
-            <v>69</v>
+            <v>71</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>277</v>
+            <v>623</v>
           </cell>
           <cell r="D19">
-            <v>138.5</v>
+            <v>207.66666666666666</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>156</v>
+            <v>395</v>
           </cell>
           <cell r="D20">
-            <v>78</v>
+            <v>131.66666666666666</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>744</v>
+            <v>1576</v>
           </cell>
           <cell r="D21">
-            <v>372</v>
+            <v>525.33333333333337</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>1184</v>
+            <v>2435</v>
           </cell>
           <cell r="D22">
-            <v>592</v>
+            <v>811.66666666666663</v>
           </cell>
         </row>
         <row r="23">
@@ -662,90 +663,90 @@
         </row>
         <row r="24">
           <cell r="C24">
-            <v>70</v>
+            <v>190</v>
           </cell>
           <cell r="D24">
-            <v>35</v>
+            <v>63.333333333333336</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>1016</v>
+            <v>1817</v>
           </cell>
           <cell r="D25">
-            <v>508</v>
+            <v>605.66666666666663</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>1482</v>
+            <v>2550</v>
           </cell>
           <cell r="D26">
-            <v>741</v>
+            <v>850</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>832</v>
+            <v>1729</v>
           </cell>
           <cell r="D27">
-            <v>416</v>
+            <v>576.33333333333337</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>426</v>
+            <v>885</v>
           </cell>
           <cell r="D28">
-            <v>213</v>
+            <v>295</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>210</v>
+            <v>394</v>
           </cell>
           <cell r="D29">
-            <v>105</v>
+            <v>131.33333333333334</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>109</v>
+            <v>225</v>
           </cell>
           <cell r="D30">
-            <v>54.5</v>
+            <v>75</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>869</v>
+            <v>1321</v>
           </cell>
           <cell r="D31">
-            <v>434.5</v>
+            <v>440.33333333333331</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>1054</v>
+            <v>1890</v>
           </cell>
           <cell r="D32">
-            <v>527</v>
+            <v>630</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1443</v>
+            <v>2599</v>
           </cell>
           <cell r="D33">
-            <v>721.5</v>
+            <v>866.33333333333337</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>903</v>
+            <v>1695</v>
           </cell>
           <cell r="D34">
-            <v>451.5</v>
+            <v>565</v>
           </cell>
         </row>
         <row r="35">
@@ -753,87 +754,87 @@
             <v>148</v>
           </cell>
           <cell r="D35">
-            <v>74</v>
+            <v>49.333333333333336</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>982</v>
+            <v>1914</v>
           </cell>
           <cell r="D36">
-            <v>491</v>
+            <v>638</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>225</v>
+            <v>491</v>
           </cell>
           <cell r="D37">
-            <v>112.5</v>
+            <v>163.66666666666666</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>575</v>
+            <v>937</v>
           </cell>
           <cell r="D38">
-            <v>287.5</v>
+            <v>312.33333333333331</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>1632</v>
+            <v>2067</v>
           </cell>
           <cell r="D39">
-            <v>816</v>
+            <v>689</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>896</v>
+            <v>1121</v>
           </cell>
           <cell r="D40">
-            <v>448</v>
+            <v>373.66666666666669</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>494</v>
+            <v>712</v>
           </cell>
           <cell r="D41">
-            <v>247</v>
+            <v>237.33333333333334</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>63</v>
+            <v>148</v>
           </cell>
           <cell r="D42">
-            <v>31.5</v>
+            <v>49.333333333333336</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>272</v>
+            <v>353</v>
           </cell>
           <cell r="D43">
-            <v>136</v>
+            <v>117.66666666666667</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>235</v>
+            <v>285</v>
           </cell>
           <cell r="D44">
-            <v>117.5</v>
+            <v>95</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>111</v>
+            <v>165</v>
           </cell>
           <cell r="D45">
-            <v>55.5</v>
+            <v>55</v>
           </cell>
         </row>
         <row r="46">
@@ -846,16 +847,17 @@
         </row>
         <row r="47">
           <cell r="C47">
-            <v>1</v>
+            <v>5</v>
           </cell>
           <cell r="D47">
-            <v>0.5</v>
+            <v>1.6666666666666667</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1200,11 +1202,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>2301</v>
+        <v>3803</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1150.5</v>
+        <v>1267.6666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,11 +1218,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>231</v>
+        <v>323</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>115.5</v>
+        <v>107.66666666666667</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1232,11 +1234,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>870</v>
+        <v>1304</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>435</v>
+        <v>434.66666666666669</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1248,11 +1250,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>184</v>
+        <v>397</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>92</v>
+        <v>132.33333333333334</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1264,11 +1266,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>4.5</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1280,11 +1282,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>2829</v>
+        <v>4143</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1414.5</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1296,11 +1298,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>279</v>
+        <v>424</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>139.5</v>
+        <v>141.33333333333334</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1312,11 +1314,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>606</v>
+        <v>1037</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>303</v>
+        <v>345.66666666666669</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1328,11 +1330,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>1093</v>
+        <v>1984</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>546.5</v>
+        <v>661.33333333333337</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1344,11 +1346,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>729</v>
+        <v>1190</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>364.5</v>
+        <v>396.66666666666669</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1360,11 +1362,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>5778</v>
+        <v>9967</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2889</v>
+        <v>3322.3333333333335</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1376,11 +1378,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>3629</v>
+        <v>6337</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1814.5</v>
+        <v>2112.3333333333335</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1392,11 +1394,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>3582</v>
+        <v>6298</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1791</v>
+        <v>2099.3333333333335</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1408,11 +1410,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>4350</v>
+        <v>7322</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2175</v>
+        <v>2440.6666666666665</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,11 +1426,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>138</v>
+        <v>213</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1440,11 +1442,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>277</v>
+        <v>623</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>138.5</v>
+        <v>207.66666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1456,11 +1458,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>156</v>
+        <v>395</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>78</v>
+        <v>131.66666666666666</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1472,11 +1474,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>744</v>
+        <v>1576</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>372</v>
+        <v>525.33333333333337</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1488,11 +1490,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1184</v>
+        <v>2435</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>592</v>
+        <v>811.66666666666663</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,11 +1522,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>35</v>
+        <v>63.333333333333336</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,11 +1538,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>1016</v>
+        <v>1817</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>508</v>
+        <v>605.66666666666663</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1552,11 +1554,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>1482</v>
+        <v>2550</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>741</v>
+        <v>850</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1568,11 +1570,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>832</v>
+        <v>1729</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>416</v>
+        <v>576.33333333333337</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1584,11 +1586,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>426</v>
+        <v>885</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>213</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,11 +1602,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>210</v>
+        <v>394</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>105</v>
+        <v>131.33333333333334</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1616,11 +1618,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>54.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,11 +1634,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>869</v>
+        <v>1321</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>434.5</v>
+        <v>440.33333333333331</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1648,11 +1650,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1054</v>
+        <v>1890</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>527</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,11 +1666,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1443</v>
+        <v>2599</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>721.5</v>
+        <v>866.33333333333337</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1680,11 +1682,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>903</v>
+        <v>1695</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>451.5</v>
+        <v>565</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1700,7 +1702,7 @@
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>74</v>
+        <v>49.333333333333336</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1712,11 +1714,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>982</v>
+        <v>1914</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>491</v>
+        <v>638</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1728,11 +1730,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>225</v>
+        <v>491</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>112.5</v>
+        <v>163.66666666666666</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1744,11 +1746,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>575</v>
+        <v>937</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>287.5</v>
+        <v>312.33333333333331</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1760,11 +1762,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>1632</v>
+        <v>2067</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>816</v>
+        <v>689</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1776,11 +1778,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>896</v>
+        <v>1121</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>448</v>
+        <v>373.66666666666669</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1792,11 +1794,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>494</v>
+        <v>712</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>247</v>
+        <v>237.33333333333334</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1808,11 +1810,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>31.5</v>
+        <v>49.333333333333336</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1824,11 +1826,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>272</v>
+        <v>353</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>136</v>
+        <v>117.66666666666667</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1840,11 +1842,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>117.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1856,11 +1858,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>55.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,11 +1886,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>0.5</v>
+        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1945,19 +1947,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>43250</v>
+        <v>74722</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>43017</v>
+        <v>73432</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>21625</v>
+        <v>24907.333333333332</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>475750</v>
+        <v>547961.33333333326</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1965,11 +1967,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>6.6638624517158865E-2</v>
+        <v>0.11512997228141375</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-605773</v>
+        <v>-574301</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2005,7 +2007,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>233</v>
+        <v>1290</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2013,7 +2015,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2021,11 +2023,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0701136-DA14-4844-8C5E-697B82567B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAC5458-83DC-4E0A-8A42-6E7E99365637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -438,39 +438,40 @@
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="G3">
-            <v>74722</v>
+            <v>102896</v>
           </cell>
           <cell r="H3">
-            <v>73432</v>
+            <v>101356</v>
           </cell>
           <cell r="I3">
-            <v>24907.333333333332</v>
+            <v>25724</v>
           </cell>
           <cell r="J3">
-            <v>547961.33333333326</v>
+            <v>565928</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.11512997228141375</v>
+            <v>0.15853983603046426</v>
           </cell>
           <cell r="M3">
-            <v>-574301</v>
+            <v>-546127</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>3803</v>
+            <v>4972</v>
           </cell>
           <cell r="D4">
-            <v>1267.6666666666667</v>
+            <v>1243</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -493,164 +494,164 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>323</v>
+            <v>425</v>
           </cell>
           <cell r="D5">
-            <v>107.66666666666667</v>
+            <v>106.25</v>
           </cell>
           <cell r="G5">
-            <v>1290</v>
+            <v>1540</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46240</v>
+            <v>46241</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>3</v>
+            <v>4</v>
           </cell>
           <cell r="L5">
-            <v>18</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>1304</v>
+            <v>1730</v>
           </cell>
           <cell r="D6">
-            <v>434.66666666666669</v>
+            <v>432.5</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>397</v>
+            <v>467</v>
           </cell>
           <cell r="D7">
-            <v>132.33333333333334</v>
+            <v>116.75</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>20</v>
+            <v>41</v>
           </cell>
           <cell r="D8">
-            <v>6.666666666666667</v>
+            <v>10.25</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>4143</v>
+            <v>5740</v>
           </cell>
           <cell r="D9">
-            <v>1381</v>
+            <v>1435</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>424</v>
+            <v>557</v>
           </cell>
           <cell r="D10">
-            <v>141.33333333333334</v>
+            <v>139.25</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>1037</v>
+            <v>1477</v>
           </cell>
           <cell r="D11">
-            <v>345.66666666666669</v>
+            <v>369.25</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>1984</v>
+            <v>3231</v>
           </cell>
           <cell r="D12">
-            <v>661.33333333333337</v>
+            <v>807.75</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>1190</v>
+            <v>1816</v>
           </cell>
           <cell r="D13">
-            <v>396.66666666666669</v>
+            <v>454</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>9967</v>
+            <v>14035</v>
           </cell>
           <cell r="D14">
-            <v>3322.3333333333335</v>
+            <v>3508.75</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>6337</v>
+            <v>9098</v>
           </cell>
           <cell r="D15">
-            <v>2112.3333333333335</v>
+            <v>2274.5</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>6298</v>
+            <v>8901</v>
           </cell>
           <cell r="D16">
-            <v>2099.3333333333335</v>
+            <v>2225.25</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>7322</v>
+            <v>10019</v>
           </cell>
           <cell r="D17">
-            <v>2440.6666666666665</v>
+            <v>2504.75</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>213</v>
+            <v>294</v>
           </cell>
           <cell r="D18">
-            <v>71</v>
+            <v>73.5</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>623</v>
+            <v>922</v>
           </cell>
           <cell r="D19">
-            <v>207.66666666666666</v>
+            <v>230.5</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>395</v>
+            <v>526</v>
           </cell>
           <cell r="D20">
-            <v>131.66666666666666</v>
+            <v>131.5</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>1576</v>
+            <v>2077</v>
           </cell>
           <cell r="D21">
-            <v>525.33333333333337</v>
+            <v>519.25</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>2435</v>
+            <v>3221</v>
           </cell>
           <cell r="D22">
-            <v>811.66666666666663</v>
+            <v>805.25</v>
           </cell>
         </row>
         <row r="23">
@@ -663,178 +664,178 @@
         </row>
         <row r="24">
           <cell r="C24">
-            <v>190</v>
+            <v>202</v>
           </cell>
           <cell r="D24">
-            <v>63.333333333333336</v>
+            <v>50.5</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>1817</v>
+            <v>2482</v>
           </cell>
           <cell r="D25">
-            <v>605.66666666666663</v>
+            <v>620.5</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>2550</v>
+            <v>3820</v>
           </cell>
           <cell r="D26">
-            <v>850</v>
+            <v>955</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>1729</v>
+            <v>2193</v>
           </cell>
           <cell r="D27">
-            <v>576.33333333333337</v>
+            <v>548.25</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>885</v>
+            <v>1394</v>
           </cell>
           <cell r="D28">
-            <v>295</v>
+            <v>348.5</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>394</v>
+            <v>508</v>
           </cell>
           <cell r="D29">
-            <v>131.33333333333334</v>
+            <v>127</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>225</v>
+            <v>419</v>
           </cell>
           <cell r="D30">
-            <v>75</v>
+            <v>104.75</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>1321</v>
+            <v>1564</v>
           </cell>
           <cell r="D31">
-            <v>440.33333333333331</v>
+            <v>391</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>1890</v>
+            <v>2733</v>
           </cell>
           <cell r="D32">
-            <v>630</v>
+            <v>683.25</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>2599</v>
+            <v>3540</v>
           </cell>
           <cell r="D33">
-            <v>866.33333333333337</v>
+            <v>885</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>1695</v>
+            <v>2178</v>
           </cell>
           <cell r="D34">
-            <v>565</v>
+            <v>544.5</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>148</v>
+            <v>168</v>
           </cell>
           <cell r="D35">
-            <v>49.333333333333336</v>
+            <v>42</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>1914</v>
+            <v>2772</v>
           </cell>
           <cell r="D36">
-            <v>638</v>
+            <v>693</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>491</v>
+            <v>636</v>
           </cell>
           <cell r="D37">
-            <v>163.66666666666666</v>
+            <v>159</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>937</v>
+            <v>1200</v>
           </cell>
           <cell r="D38">
-            <v>312.33333333333331</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>2067</v>
+            <v>2509</v>
           </cell>
           <cell r="D39">
-            <v>689</v>
+            <v>627.25</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>1121</v>
+            <v>1347</v>
           </cell>
           <cell r="D40">
-            <v>373.66666666666669</v>
+            <v>336.75</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>712</v>
+            <v>1021</v>
           </cell>
           <cell r="D41">
-            <v>237.33333333333334</v>
+            <v>255.25</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>148</v>
+            <v>189</v>
           </cell>
           <cell r="D42">
-            <v>49.333333333333336</v>
+            <v>47.25</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>353</v>
+            <v>399</v>
           </cell>
           <cell r="D43">
-            <v>117.66666666666667</v>
+            <v>99.75</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>285</v>
+            <v>322</v>
           </cell>
           <cell r="D44">
-            <v>95</v>
+            <v>80.5</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>165</v>
+            <v>201</v>
           </cell>
           <cell r="D45">
-            <v>55</v>
+            <v>50.25</v>
           </cell>
         </row>
         <row r="46">
@@ -847,10 +848,10 @@
         </row>
         <row r="47">
           <cell r="C47">
-            <v>5</v>
+            <v>10</v>
           </cell>
           <cell r="D47">
-            <v>1.6666666666666667</v>
+            <v>2.5</v>
           </cell>
         </row>
       </sheetData>
@@ -858,6 +859,7 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1202,11 +1204,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>3803</v>
+        <v>4972</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1267.6666666666667</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1218,11 +1220,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>323</v>
+        <v>425</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>107.66666666666667</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1234,11 +1236,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>1304</v>
+        <v>1730</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>434.66666666666669</v>
+        <v>432.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1250,11 +1252,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>397</v>
+        <v>467</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>132.33333333333334</v>
+        <v>116.75</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1266,11 +1268,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>6.666666666666667</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1282,11 +1284,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>4143</v>
+        <v>5740</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1381</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1298,11 +1300,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>424</v>
+        <v>557</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>141.33333333333334</v>
+        <v>139.25</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1314,11 +1316,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>1037</v>
+        <v>1477</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>345.66666666666669</v>
+        <v>369.25</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1330,11 +1332,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>1984</v>
+        <v>3231</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>661.33333333333337</v>
+        <v>807.75</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1346,11 +1348,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>1190</v>
+        <v>1816</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>396.66666666666669</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1362,11 +1364,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>9967</v>
+        <v>14035</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3322.3333333333335</v>
+        <v>3508.75</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1378,11 +1380,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>6337</v>
+        <v>9098</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2112.3333333333335</v>
+        <v>2274.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1394,11 +1396,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>6298</v>
+        <v>8901</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2099.3333333333335</v>
+        <v>2225.25</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,11 +1412,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>7322</v>
+        <v>10019</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2440.6666666666665</v>
+        <v>2504.75</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1426,11 +1428,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>71</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1442,11 +1444,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>623</v>
+        <v>922</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>207.66666666666666</v>
+        <v>230.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1458,11 +1460,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>395</v>
+        <v>526</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>131.66666666666666</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1474,11 +1476,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>1576</v>
+        <v>2077</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>525.33333333333337</v>
+        <v>519.25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1490,11 +1492,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2435</v>
+        <v>3221</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>811.66666666666663</v>
+        <v>805.25</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1522,11 +1524,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>63.333333333333336</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,11 +1540,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>1817</v>
+        <v>2482</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>605.66666666666663</v>
+        <v>620.5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1554,11 +1556,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>2550</v>
+        <v>3820</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>850</v>
+        <v>955</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1570,11 +1572,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>1729</v>
+        <v>2193</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>576.33333333333337</v>
+        <v>548.25</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1586,11 +1588,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>885</v>
+        <v>1394</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>295</v>
+        <v>348.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1602,11 +1604,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>394</v>
+        <v>508</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>131.33333333333334</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1618,11 +1620,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>225</v>
+        <v>419</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>75</v>
+        <v>104.75</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,11 +1636,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1321</v>
+        <v>1564</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>440.33333333333331</v>
+        <v>391</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1650,11 +1652,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1890</v>
+        <v>2733</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>630</v>
+        <v>683.25</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1666,11 +1668,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2599</v>
+        <v>3540</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>866.33333333333337</v>
+        <v>885</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1682,11 +1684,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>1695</v>
+        <v>2178</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>565</v>
+        <v>544.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1698,11 +1700,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>49.333333333333336</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1714,11 +1716,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>1914</v>
+        <v>2772</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>638</v>
+        <v>693</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,11 +1732,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>491</v>
+        <v>636</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>163.66666666666666</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1746,11 +1748,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>937</v>
+        <v>1200</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>312.33333333333331</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1762,11 +1764,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>2067</v>
+        <v>2509</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>689</v>
+        <v>627.25</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1778,11 +1780,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1121</v>
+        <v>1347</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>373.66666666666669</v>
+        <v>336.75</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1794,11 +1796,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>712</v>
+        <v>1021</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>237.33333333333334</v>
+        <v>255.25</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1810,11 +1812,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>49.333333333333336</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1826,11 +1828,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>353</v>
+        <v>399</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>117.66666666666667</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1842,11 +1844,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>285</v>
+        <v>322</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>95</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1858,11 +1860,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>55</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,11 +1888,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>1.6666666666666667</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,19 +1949,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>74722</v>
+        <v>102896</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>73432</v>
+        <v>101356</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>24907.333333333332</v>
+        <v>25724</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>547961.33333333326</v>
+        <v>565928</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1967,11 +1969,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.11512997228141375</v>
+        <v>0.15853983603046426</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-574301</v>
+        <v>-546127</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2007,7 +2009,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>1290</v>
+        <v>1540</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2015,7 +2017,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2023,11 +2025,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/VINCULO VTS BY SKU.xlsx
+++ b/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAC5458-83DC-4E0A-8A42-6E7E99365637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB1F6DA-2E10-464F-B951-F9B733965CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -439,39 +439,40 @@
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="G3">
-            <v>102896</v>
+            <v>117531</v>
           </cell>
           <cell r="H3">
-            <v>101356</v>
+            <v>115833</v>
           </cell>
           <cell r="I3">
-            <v>25724</v>
+            <v>23506.2</v>
           </cell>
           <cell r="J3">
-            <v>565928</v>
+            <v>517136.4</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.15853983603046426</v>
+            <v>0.18108911394511443</v>
           </cell>
           <cell r="M3">
-            <v>-546127</v>
+            <v>-531492</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>4972</v>
+            <v>5573</v>
           </cell>
           <cell r="D4">
-            <v>1243</v>
+            <v>1114.5999999999999</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -494,164 +495,164 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>425</v>
+            <v>469</v>
           </cell>
           <cell r="D5">
-            <v>106.25</v>
+            <v>93.8</v>
           </cell>
           <cell r="G5">
-            <v>1540</v>
+            <v>1698</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46241</v>
+            <v>46244</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="L5">
-            <v>17</v>
+            <v>16</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>1730</v>
+            <v>1969</v>
           </cell>
           <cell r="D6">
-            <v>432.5</v>
+            <v>393.8</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>467</v>
+            <v>523</v>
           </cell>
           <cell r="D7">
-            <v>116.75</v>
+            <v>104.6</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>41</v>
+            <v>42</v>
           </cell>
           <cell r="D8">
-            <v>10.25</v>
+            <v>8.4</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>5740</v>
+            <v>6506</v>
           </cell>
           <cell r="D9">
-            <v>1435</v>
+            <v>1301.2</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>557</v>
+            <v>617</v>
           </cell>
           <cell r="D10">
-            <v>139.25</v>
+            <v>123.4</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>1477</v>
+            <v>1635</v>
           </cell>
           <cell r="D11">
-            <v>369.25</v>
+            <v>327</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>3231</v>
+            <v>3728</v>
           </cell>
           <cell r="D12">
-            <v>807.75</v>
+            <v>745.6</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>1816</v>
+            <v>2116</v>
           </cell>
           <cell r="D13">
-            <v>454</v>
+            <v>423.2</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>14035</v>
+            <v>15669</v>
           </cell>
           <cell r="D14">
-            <v>3508.75</v>
+            <v>3133.8</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>9098</v>
+            <v>10437</v>
           </cell>
           <cell r="D15">
-            <v>2274.5</v>
+            <v>2087.4</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>8901</v>
+            <v>10105</v>
           </cell>
           <cell r="D16">
-            <v>2225.25</v>
+            <v>2021</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>10019</v>
+            <v>11379</v>
           </cell>
           <cell r="D17">
-            <v>2504.75</v>
+            <v>2275.8000000000002</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>294</v>
+            <v>310</v>
           </cell>
           <cell r="D18">
-            <v>73.5</v>
+            <v>62</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>922</v>
+            <v>1041</v>
           </cell>
           <cell r="D19">
-            <v>230.5</v>
+            <v>208.2</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>526</v>
+            <v>628</v>
           </cell>
           <cell r="D20">
-            <v>131.5</v>
+            <v>125.6</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>2077</v>
+            <v>2422</v>
           </cell>
           <cell r="D21">
-            <v>519.25</v>
+            <v>484.4</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>3221</v>
+            <v>3655</v>
           </cell>
           <cell r="D22">
-            <v>805.25</v>
+            <v>731</v>
           </cell>
         </row>
         <row r="23">
@@ -664,178 +665,178 @@
         </row>
         <row r="24">
           <cell r="C24">
-            <v>202</v>
+            <v>402</v>
           </cell>
           <cell r="D24">
-            <v>50.5</v>
+            <v>80.400000000000006</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>2482</v>
+            <v>2877</v>
           </cell>
           <cell r="D25">
-            <v>620.5</v>
+            <v>575.4</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>3820</v>
+            <v>4413</v>
           </cell>
           <cell r="D26">
-            <v>955</v>
+            <v>882.6</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>2193</v>
+            <v>2401</v>
           </cell>
           <cell r="D27">
-            <v>548.25</v>
+            <v>480.2</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>1394</v>
+            <v>1658</v>
           </cell>
           <cell r="D28">
-            <v>348.5</v>
+            <v>331.6</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>508</v>
+            <v>582</v>
           </cell>
           <cell r="D29">
-            <v>127</v>
+            <v>116.4</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>419</v>
+            <v>513</v>
           </cell>
           <cell r="D30">
-            <v>104.75</v>
+            <v>102.6</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>1564</v>
+            <v>2032</v>
           </cell>
           <cell r="D31">
-            <v>391</v>
+            <v>406.4</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>2733</v>
+            <v>3158</v>
           </cell>
           <cell r="D32">
-            <v>683.25</v>
+            <v>631.6</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>3540</v>
+            <v>4100</v>
           </cell>
           <cell r="D33">
-            <v>885</v>
+            <v>820</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>2178</v>
+            <v>2473</v>
           </cell>
           <cell r="D34">
-            <v>544.5</v>
+            <v>494.6</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>168</v>
+            <v>172</v>
           </cell>
           <cell r="D35">
-            <v>42</v>
+            <v>34.4</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>2772</v>
+            <v>3237</v>
           </cell>
           <cell r="D36">
-            <v>693</v>
+            <v>647.4</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>636</v>
+            <v>662</v>
           </cell>
           <cell r="D37">
-            <v>159</v>
+            <v>132.4</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>1200</v>
+            <v>1428</v>
           </cell>
           <cell r="D38">
-            <v>300</v>
+            <v>285.60000000000002</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>2509</v>
+            <v>2874</v>
           </cell>
           <cell r="D39">
-            <v>627.25</v>
+            <v>574.79999999999995</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>1347</v>
+            <v>1561</v>
           </cell>
           <cell r="D40">
-            <v>336.75</v>
+            <v>312.2</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>1021</v>
+            <v>1252</v>
           </cell>
           <cell r="D41">
-            <v>255.25</v>
+            <v>250.4</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>189</v>
+            <v>205</v>
           </cell>
           <cell r="D42">
-            <v>47.25</v>
+            <v>41</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>399</v>
+            <v>452</v>
           </cell>
           <cell r="D43">
-            <v>99.75</v>
+            <v>90.4</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>322</v>
+            <v>331</v>
           </cell>
           <cell r="D44">
-            <v>80.5</v>
+            <v>66.2</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>201</v>
+            <v>216</v>
           </cell>
           <cell r="D45">
-            <v>50.25</v>
+            <v>43.2</v>
           </cell>
         </row>
         <row r="46">
@@ -851,7 +852,7 @@
             <v>10</v>
           </cell>
           <cell r="D47">
-            <v>2.5</v>
+            <v>2</v>
           </cell>
         </row>
       </sheetData>
@@ -860,6 +861,7 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1204,11 +1206,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>4972</v>
+        <v>5573</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1243</v>
+        <v>1114.5999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1220,11 +1222,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>106.25</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1236,11 +1238,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>1730</v>
+        <v>1969</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>432.5</v>
+        <v>393.8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1252,11 +1254,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>467</v>
+        <v>523</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>116.75</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1268,11 +1270,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>10.25</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,11 +1286,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>5740</v>
+        <v>6506</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1435</v>
+        <v>1301.2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1300,11 +1302,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>557</v>
+        <v>617</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>139.25</v>
+        <v>123.4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1316,11 +1318,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>1477</v>
+        <v>1635</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>369.25</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1332,11 +1334,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>3231</v>
+        <v>3728</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>807.75</v>
+        <v>745.6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1348,11 +1350,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>1816</v>
+        <v>2116</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>454</v>
+        <v>423.2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1364,11 +1366,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>14035</v>
+        <v>15669</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3508.75</v>
+        <v>3133.8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1380,11 +1382,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>9098</v>
+        <v>10437</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2274.5</v>
+        <v>2087.4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,11 +1398,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>8901</v>
+        <v>10105</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2225.25</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1412,11 +1414,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>10019</v>
+        <v>11379</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2504.75</v>
+        <v>2275.8000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1428,11 +1430,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>73.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1444,11 +1446,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>922</v>
+        <v>1041</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>230.5</v>
+        <v>208.2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1460,11 +1462,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>526</v>
+        <v>628</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>131.5</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,11 +1478,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>2077</v>
+        <v>2422</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>519.25</v>
+        <v>484.4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,11 +1494,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>3221</v>
+        <v>3655</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>805.25</v>
+        <v>731</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,11 +1526,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>50.5</v>
+        <v>80.400000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1540,11 +1542,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>2482</v>
+        <v>2877</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>620.5</v>
+        <v>575.4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1556,11 +1558,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>3820</v>
+        <v>4413</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>955</v>
+        <v>882.6</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1572,11 +1574,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>2193</v>
+        <v>2401</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>548.25</v>
+        <v>480.2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1588,11 +1590,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>1394</v>
+        <v>1658</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>348.5</v>
+        <v>331.6</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,11 +1606,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>508</v>
+        <v>582</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>127</v>
+        <v>116.4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,11 +1622,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>419</v>
+        <v>513</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>104.75</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,11 +1638,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1564</v>
+        <v>2032</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>391</v>
+        <v>406.4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1652,11 +1654,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>2733</v>
+        <v>3158</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>683.25</v>
+        <v>631.6</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1668,11 +1670,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>3540</v>
+        <v>4100</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>885</v>
+        <v>820</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1684,11 +1686,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>2178</v>
+        <v>2473</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>544.5</v>
+        <v>494.6</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1700,11 +1702,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>42</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,11 +1718,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>2772</v>
+        <v>3237</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>693</v>
+        <v>647.4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1732,11 +1734,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>636</v>
+        <v>662</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>159</v>
+        <v>132.4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,11 +1750,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>1200</v>
+        <v>1428</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>300</v>
+        <v>285.60000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1764,11 +1766,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>2509</v>
+        <v>2874</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>627.25</v>
+        <v>574.79999999999995</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1780,11 +1782,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1347</v>
+        <v>1561</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>336.75</v>
+        <v>312.2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1796,11 +1798,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>1021</v>
+        <v>1252</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>255.25</v>
+        <v>250.4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,11 +1814,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>47.25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1828,11 +1830,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>399</v>
+        <v>452</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>99.75</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1844,11 +1846,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>80.5</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1860,11 +1862,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>50.25</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1892,7 +1894,7 @@
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1949,19 +1951,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>102896</v>
+        <v>117531</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>101356</v>
+        <v>115833</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>25724</v>
+        <v>23506.2</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>565928</v>
+        <v>517136.4</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1969,11 +1971,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.15853983603046426</v>
+        <v>0.18108911394511443</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-546127</v>
+        <v>-531492</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2009,7 +2011,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>1540</v>
+        <v>1698</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2017,7 +2019,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2025,11 +2027,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>
